--- a/References.xlsx
+++ b/References.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\these\02-Littérature\00-En cours\deconv\Webserver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E595C38F-6A9B-434E-82B7-36860BF96676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{E595C38F-6A9B-434E-82B7-36860BF96676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{609532A6-7192-4377-80FC-56E906A3F990}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3AEBAFF5-EA2C-45CF-A685-CF92E1A46251}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,13 +38,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
+    <t>WL</t>
+  </si>
+  <si>
     <t>DNA Parallel</t>
+  </si>
+  <si>
+    <t>Double stranded RNA</t>
   </si>
   <si>
     <t>DNA Parallel Quadruplex</t>
   </si>
   <si>
     <t>Z-DNA</t>
+  </si>
+  <si>
+    <t>Double stranded DNA</t>
   </si>
   <si>
     <t>RNA quadruplex</t>
@@ -65,34 +71,25 @@
     <t>rand_RNA_stacked</t>
   </si>
   <si>
+    <t>DNA Cruciform</t>
+  </si>
+  <si>
     <t>DNA Hybrid Quadruplex</t>
   </si>
   <si>
     <t>DNA i-motif</t>
   </si>
   <si>
-    <t>WL</t>
+    <t>AU rich RNA</t>
   </si>
   <si>
-    <t>DNA Cruciform</t>
+    <t>DNA antiparallel quadruplex 1</t>
   </si>
   <si>
-    <t>Z-RNA</t>
-  </si>
-  <si>
-    <t>DNA antiparallel quadruplex</t>
+    <t>DNA antiparallel quadruplex 2</t>
   </si>
   <si>
     <t>AT rich DNA</t>
-  </si>
-  <si>
-    <t>AU rich RNA</t>
-  </si>
-  <si>
-    <t>Double stranded DNA</t>
-  </si>
-  <si>
-    <t>Double stranded RNA</t>
   </si>
   <si>
     <t>A-DNA</t>
@@ -102,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6050 +146,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Feuil1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>7CLS</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>8DUT</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>rpsO-polyA</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>6R9K</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>6R9L</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>7CLS-2</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>7O5E</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>7PNE</v>
-          </cell>
-          <cell r="J1" t="str">
-            <v>8ABD</v>
-          </cell>
-          <cell r="K1" t="str">
-            <v>8DUT-2</v>
-          </cell>
-          <cell r="L1" t="str">
-            <v>8S4N</v>
-          </cell>
-          <cell r="M1" t="str">
-            <v>8R4E</v>
-          </cell>
-          <cell r="N1" t="str">
-            <v>8R4W</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2">
-            <v>2.6375707474030563E-2</v>
-          </cell>
-          <cell r="C2">
-            <v>-0.2170670935233685</v>
-          </cell>
-          <cell r="D2">
-            <v>-5.5869737664949681E-2</v>
-          </cell>
-          <cell r="E2">
-            <v>7.6732868405093996E-2</v>
-          </cell>
-          <cell r="F2">
-            <v>1.9320800485142509E-2</v>
-          </cell>
-          <cell r="G2">
-            <v>0.15924596173989747</v>
-          </cell>
-          <cell r="H2">
-            <v>-1.7801914580265088E-2</v>
-          </cell>
-          <cell r="I2">
-            <v>3.9358269080828234E-2</v>
-          </cell>
-          <cell r="J2">
-            <v>4.9603821339532367E-2</v>
-          </cell>
-          <cell r="K2">
-            <v>5.6436913346692333E-2</v>
-          </cell>
-          <cell r="L2">
-            <v>-2.6857538747937441E-2</v>
-          </cell>
-          <cell r="M2">
-            <v>-0.24941540842974</v>
-          </cell>
-          <cell r="N2">
-            <v>-0.33915504370361998</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>-7.9848427624332197E-2</v>
-          </cell>
-          <cell r="C3">
-            <v>-6.4403028128059425E-2</v>
-          </cell>
-          <cell r="D3">
-            <v>1.6486424828154045E-2</v>
-          </cell>
-          <cell r="E3">
-            <v>9.7957853244390575E-2</v>
-          </cell>
-          <cell r="F3">
-            <v>0.12104836264402667</v>
-          </cell>
-          <cell r="G3">
-            <v>8.0886947093739087E-2</v>
-          </cell>
-          <cell r="H3">
-            <v>-9.5581737849779053E-2</v>
-          </cell>
-          <cell r="I3">
-            <v>1.2605042016806733E-2</v>
-          </cell>
-          <cell r="J3">
-            <v>3.5664396772454685E-2</v>
-          </cell>
-          <cell r="K3">
-            <v>8.8743260078571994E-3</v>
-          </cell>
-          <cell r="L3">
-            <v>-6.7923653517988347E-2</v>
-          </cell>
-          <cell r="M3">
-            <v>-0.182146805640899</v>
-          </cell>
-          <cell r="N3">
-            <v>-0.28953574577710001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>-0.17087446401473372</v>
-          </cell>
-          <cell r="C4">
-            <v>0.15806130939693375</v>
-          </cell>
-          <cell r="D4">
-            <v>3.8625199139504213E-2</v>
-          </cell>
-          <cell r="E4">
-            <v>0.1158474833232262</v>
-          </cell>
-          <cell r="F4">
-            <v>3.3798514251061243E-2</v>
-          </cell>
-          <cell r="G4">
-            <v>-3.8380124777183597E-2</v>
-          </cell>
-          <cell r="H4">
-            <v>-1.744455514164428E-2</v>
-          </cell>
-          <cell r="I4">
-            <v>-5.2943342285367734E-2</v>
-          </cell>
-          <cell r="J4">
-            <v>-1.396058638231925E-2</v>
-          </cell>
-          <cell r="K4">
-            <v>-1.1590975756057692E-2</v>
-          </cell>
-          <cell r="L4">
-            <v>-1.8404565134612937E-2</v>
-          </cell>
-          <cell r="M4">
-            <v>-0.10467748261836</v>
-          </cell>
-          <cell r="N4">
-            <v>-0.22390000689846901</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>4.2888236340519026E-2</v>
-          </cell>
-          <cell r="C5">
-            <v>4.9601752846098246E-2</v>
-          </cell>
-          <cell r="D5">
-            <v>-6.8116144173964721E-3</v>
-          </cell>
-          <cell r="E5">
-            <v>-3.4546694966646446E-2</v>
-          </cell>
-          <cell r="F5">
-            <v>-5.5894481503941787E-2</v>
-          </cell>
-          <cell r="G5">
-            <v>-5.7618138633147721E-2</v>
-          </cell>
-          <cell r="H5">
-            <v>4.660021224984838E-2</v>
-          </cell>
-          <cell r="I5">
-            <v>2.0109590227843754E-2</v>
-          </cell>
-          <cell r="J5">
-            <v>-3.2385052388653052E-2</v>
-          </cell>
-          <cell r="K5">
-            <v>-3.9452476138371086E-2</v>
-          </cell>
-          <cell r="L5">
-            <v>1.7906201080288273E-2</v>
-          </cell>
-          <cell r="M5">
-            <v>-0.130219836524639</v>
-          </cell>
-          <cell r="N5">
-            <v>-0.10562630558067999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>8.4769966431545829E-2</v>
-          </cell>
-          <cell r="C6">
-            <v>4.0720218720493251E-2</v>
-          </cell>
-          <cell r="D6">
-            <v>5.9289567576913949E-3</v>
-          </cell>
-          <cell r="E6">
-            <v>-0.25599151000606429</v>
-          </cell>
-          <cell r="F6">
-            <v>-0.11827319587628866</v>
-          </cell>
-          <cell r="G6">
-            <v>-0.1441346454233052</v>
-          </cell>
-          <cell r="H6">
-            <v>8.4227995321840055E-2</v>
-          </cell>
-          <cell r="I6">
-            <v>-1.9129559040110877E-2</v>
-          </cell>
-          <cell r="J6">
-            <v>-3.892257934101475E-2</v>
-          </cell>
-          <cell r="K6">
-            <v>-1.426778746012076E-2</v>
-          </cell>
-          <cell r="L6">
-            <v>9.527955632025048E-2</v>
-          </cell>
-          <cell r="M6">
-            <v>-0.20755190214954</v>
-          </cell>
-          <cell r="N6">
-            <v>-1.5932214821734001E-3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>9.6688981392970663E-2</v>
-          </cell>
-          <cell r="C7">
-            <v>3.3086840687903352E-2</v>
-          </cell>
-          <cell r="D7">
-            <v>1.6407713569966398E-3</v>
-          </cell>
-          <cell r="E7">
-            <v>-0.22852031534263192</v>
-          </cell>
-          <cell r="F7">
-            <v>-0.10192010309278351</v>
-          </cell>
-          <cell r="G7">
-            <v>-0.16597409816785194</v>
-          </cell>
-          <cell r="H7">
-            <v>7.6119726241011848E-2</v>
-          </cell>
-          <cell r="I7">
-            <v>-0.12150762366802388</v>
-          </cell>
-          <cell r="J7">
-            <v>-7.6610087763627779E-2</v>
-          </cell>
-          <cell r="K7">
-            <v>-3.2177769135444431E-3</v>
-          </cell>
-          <cell r="L7">
-            <v>0.26554130762830186</v>
-          </cell>
-          <cell r="M7">
-            <v>-0.1048771297422</v>
-          </cell>
-          <cell r="N7">
-            <v>1.2737686148872E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>6.2440384948599437E-2</v>
-          </cell>
-          <cell r="C8">
-            <v>2.8708857169824298E-2</v>
-          </cell>
-          <cell r="D8">
-            <v>-2.5164456118398959E-2</v>
-          </cell>
-          <cell r="E8">
-            <v>-9.4145694360218329E-2</v>
-          </cell>
-          <cell r="F8">
-            <v>-6.4837780473013959E-2</v>
-          </cell>
-          <cell r="G8">
-            <v>-8.3428661999007656E-2</v>
-          </cell>
-          <cell r="H8">
-            <v>4.5547084813306743E-3</v>
-          </cell>
-          <cell r="I8">
-            <v>-0.23429621848739493</v>
-          </cell>
-          <cell r="J8">
-            <v>-7.3281576376254959E-2</v>
-          </cell>
-          <cell r="K8">
-            <v>3.9988786023149737E-2</v>
-          </cell>
-          <cell r="L8">
-            <v>0.44416877036117736</v>
-          </cell>
-          <cell r="M8">
-            <v>-3.4222012615223903E-2</v>
-          </cell>
-          <cell r="N8">
-            <v>-1.8749410430518001E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>7.9808516956842435E-3</v>
-          </cell>
-          <cell r="C9">
-            <v>4.2441894686656489E-2</v>
-          </cell>
-          <cell r="D9">
-            <v>4.4324564954869028E-3</v>
-          </cell>
-          <cell r="E9">
-            <v>-8.0390388114008504E-2</v>
-          </cell>
-          <cell r="F9">
-            <v>-4.8773120072771382E-2</v>
-          </cell>
-          <cell r="G9">
-            <v>7.0251483911277723E-2</v>
-          </cell>
-          <cell r="H9">
-            <v>-9.499696785930864E-2</v>
-          </cell>
-          <cell r="I9">
-            <v>-0.3418901065580871</v>
-          </cell>
-          <cell r="J9">
-            <v>-6.1737369238932679E-2</v>
-          </cell>
-          <cell r="K9">
-            <v>1.1189835077912833E-2</v>
-          </cell>
-          <cell r="L9">
-            <v>0.63130209288222605</v>
-          </cell>
-          <cell r="M9">
-            <v>7.4655546370919895E-2</v>
-          </cell>
-          <cell r="N9">
-            <v>-2.8987265029860002E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>-2.6975824080095356E-2</v>
-          </cell>
-          <cell r="C10">
-            <v>4.781759917015449E-2</v>
-          </cell>
-          <cell r="D10">
-            <v>-5.1063024589695361E-3</v>
-          </cell>
-          <cell r="E10">
-            <v>3.5260764099454223E-2</v>
-          </cell>
-          <cell r="F10">
-            <v>3.6231807155852017E-2</v>
-          </cell>
-          <cell r="G10">
-            <v>8.8048082400720346E-2</v>
-          </cell>
-          <cell r="H10">
-            <v>5.8082279303473948E-2</v>
-          </cell>
-          <cell r="I10">
-            <v>-0.23866033526812783</v>
-          </cell>
-          <cell r="J10">
-            <v>-6.1444562361026876E-2</v>
-          </cell>
-          <cell r="K10">
-            <v>1.6711132570464315E-2</v>
-          </cell>
-          <cell r="L10">
-            <v>1.046855211756244</v>
-          </cell>
-          <cell r="M10">
-            <v>7.6527238156920002E-2</v>
-          </cell>
-          <cell r="N10">
-            <v>-7.0022235748559994E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>-7.4533025879546799E-2</v>
-          </cell>
-          <cell r="C11">
-            <v>4.0077458528040122E-2</v>
-          </cell>
-          <cell r="D11">
-            <v>5.5919187010111115E-3</v>
-          </cell>
-          <cell r="E11">
-            <v>9.7225591267434686E-3</v>
-          </cell>
-          <cell r="F11">
-            <v>4.6601728320194047E-2</v>
-          </cell>
-          <cell r="G11">
-            <v>7.6958946652700436E-2</v>
-          </cell>
-          <cell r="H11">
-            <v>0.20341982153686211</v>
-          </cell>
-          <cell r="I11">
-            <v>-3.9239149267954576E-2</v>
-          </cell>
-          <cell r="J11">
-            <v>-5.9696322687150458E-3</v>
-          </cell>
-          <cell r="K11">
-            <v>4.1480137830569253E-2</v>
-          </cell>
-          <cell r="L11">
-            <v>1.3883676858420184</v>
-          </cell>
-          <cell r="M11">
-            <v>3.8944914888563E-3</v>
-          </cell>
-          <cell r="N11">
-            <v>-1.8167913226409E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>-8.2793660093902766E-2</v>
-          </cell>
-          <cell r="C12">
-            <v>3.520959733643414E-2</v>
-          </cell>
-          <cell r="D12">
-            <v>2.3198581619810865E-2</v>
-          </cell>
-          <cell r="E12">
-            <v>-0.13113023044269256</v>
-          </cell>
-          <cell r="F12">
-            <v>0.14465357792601574</v>
-          </cell>
-          <cell r="G12">
-            <v>-8.4112042192697134E-2</v>
-          </cell>
-          <cell r="H12">
-            <v>0.44732305293251307</v>
-          </cell>
-          <cell r="I12">
-            <v>5.6679372780039872E-2</v>
-          </cell>
-          <cell r="J12">
-            <v>-5.4008532107000864E-2</v>
-          </cell>
-          <cell r="K12">
-            <v>1.726750566878477E-2</v>
-          </cell>
-          <cell r="L12">
-            <v>1.86848600984388</v>
-          </cell>
-          <cell r="M12">
-            <v>-8.4107589890220005E-2</v>
-          </cell>
-          <cell r="N12">
-            <v>3.7977225281566003E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>-4.6094490401853594E-2</v>
-          </cell>
-          <cell r="C13">
-            <v>1.5214545671342505E-2</v>
-          </cell>
-          <cell r="D13">
-            <v>6.9592062461389381E-3</v>
-          </cell>
-          <cell r="E13">
-            <v>-3.2575803517283203E-2</v>
-          </cell>
-          <cell r="F13">
-            <v>0.14413053365676165</v>
-          </cell>
-          <cell r="G13">
-            <v>-0.11947553154345149</v>
-          </cell>
-          <cell r="H13">
-            <v>0.6180596465390279</v>
-          </cell>
-          <cell r="I13">
-            <v>4.0598198042103462E-2</v>
-          </cell>
-          <cell r="J13">
-            <v>-0.15294422966781213</v>
-          </cell>
-          <cell r="K13">
-            <v>6.1786416998444386E-2</v>
-          </cell>
-          <cell r="L13">
-            <v>2.3844787891181407</v>
-          </cell>
-          <cell r="M13">
-            <v>-6.4660712233679998E-3</v>
-          </cell>
-          <cell r="N13">
-            <v>0.16612761955164901</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>-3.7246557606028019E-2</v>
-          </cell>
-          <cell r="C14">
-            <v>3.4266926660751817E-2</v>
-          </cell>
-          <cell r="D14">
-            <v>-6.8001726806172225E-3</v>
-          </cell>
-          <cell r="E14">
-            <v>3.0667070952092174E-2</v>
-          </cell>
-          <cell r="F14">
-            <v>0.26139099454214676</v>
-          </cell>
-          <cell r="G14">
-            <v>-0.21669354245915792</v>
-          </cell>
-          <cell r="H14">
-            <v>0.9223945248202372</v>
-          </cell>
-          <cell r="I14">
-            <v>3.5129515723815313E-2</v>
-          </cell>
-          <cell r="J14">
-            <v>-0.1843289914763156</v>
-          </cell>
-          <cell r="K14">
-            <v>7.1216539338729679E-2</v>
-          </cell>
-          <cell r="L14">
-            <v>2.9231244799526142</v>
-          </cell>
-          <cell r="M14">
-            <v>4.8776911840421999E-3</v>
-          </cell>
-          <cell r="N14">
-            <v>0.17733306393674</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>-4.2500782415243687E-2</v>
-          </cell>
-          <cell r="C15">
-            <v>5.2820010260390071E-2</v>
-          </cell>
-          <cell r="D15">
-            <v>-5.0084558823740299E-3</v>
-          </cell>
-          <cell r="E15">
-            <v>2.223771983020012E-2</v>
-          </cell>
-          <cell r="F15">
-            <v>0.22610445724681622</v>
-          </cell>
-          <cell r="G15">
-            <v>-0.19872466324861712</v>
-          </cell>
-          <cell r="H15">
-            <v>1.2126137052759243</v>
-          </cell>
-          <cell r="I15">
-            <v>-2.2865589534782987E-2</v>
-          </cell>
-          <cell r="J15">
-            <v>-0.16062986405902563</v>
-          </cell>
-          <cell r="K15">
-            <v>4.4514338400084376E-2</v>
-          </cell>
-          <cell r="L15">
-            <v>3.5662644379257338</v>
-          </cell>
-          <cell r="M15">
-            <v>0.114485147576999</v>
-          </cell>
-          <cell r="N15">
-            <v>0.28101206138314999</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>-2.4574192380872772E-2</v>
-          </cell>
-          <cell r="C16">
-            <v>6.2479151573879621E-2</v>
-          </cell>
-          <cell r="D16">
-            <v>-4.5566650966502587E-3</v>
-          </cell>
-          <cell r="E16">
-            <v>5.7607640994542159E-2</v>
-          </cell>
-          <cell r="F16">
-            <v>0.30610748938750759</v>
-          </cell>
-          <cell r="G16">
-            <v>-0.20472003234283401</v>
-          </cell>
-          <cell r="H16">
-            <v>1.5190764965780121</v>
-          </cell>
-          <cell r="I16">
-            <v>6.1514554275318378E-2</v>
-          </cell>
-          <cell r="J16">
-            <v>-0.187703300822047</v>
-          </cell>
-          <cell r="K16">
-            <v>3.7799135510322462E-2</v>
-          </cell>
-          <cell r="L16">
-            <v>4.3410909712722301</v>
-          </cell>
-          <cell r="M16">
-            <v>0.24208461560123901</v>
-          </cell>
-          <cell r="N16">
-            <v>0.51047099288636999</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>-4.7076817195858767E-2</v>
-          </cell>
-          <cell r="C17">
-            <v>5.4426080618106165E-2</v>
-          </cell>
-          <cell r="D17">
-            <v>1.9815378416962542E-2</v>
-          </cell>
-          <cell r="E17">
-            <v>0.25792601576713164</v>
-          </cell>
-          <cell r="F17">
-            <v>0.27037371134020616</v>
-          </cell>
-          <cell r="G17">
-            <v>-9.5608908980649415E-2</v>
-          </cell>
-          <cell r="H17">
-            <v>1.7954886078142591</v>
-          </cell>
-          <cell r="I17">
-            <v>0.14846118859915103</v>
-          </cell>
-          <cell r="J17">
-            <v>-4.5110041439256107E-2</v>
-          </cell>
-          <cell r="K17">
-            <v>7.4213662100878014E-2</v>
-          </cell>
-          <cell r="L17">
-            <v>4.9865226634887945</v>
-          </cell>
-          <cell r="M17">
-            <v>0.52704345104711903</v>
-          </cell>
-          <cell r="N17">
-            <v>0.74280708900320003</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>-2.3992137536738123E-2</v>
-          </cell>
-          <cell r="C18">
-            <v>6.1492615429232345E-2</v>
-          </cell>
-          <cell r="D18">
-            <v>-4.8060555041745112E-3</v>
-          </cell>
-          <cell r="E18">
-            <v>0.41804578532443915</v>
-          </cell>
-          <cell r="F18">
-            <v>0.39814812007277139</v>
-          </cell>
-          <cell r="G18">
-            <v>3.3526976863847688E-2</v>
-          </cell>
-          <cell r="H18">
-            <v>2.094046175171099</v>
-          </cell>
-          <cell r="I18">
-            <v>0.24960473880273759</v>
-          </cell>
-          <cell r="J18">
-            <v>4.869839043864968E-2</v>
-          </cell>
-          <cell r="K18">
-            <v>6.2577410222269106E-2</v>
-          </cell>
-          <cell r="L18">
-            <v>5.630411842272272</v>
-          </cell>
-          <cell r="M18">
-            <v>0.74187623424420002</v>
-          </cell>
-          <cell r="N18">
-            <v>0.96449026415020001</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>1.0885969574645438E-2</v>
-          </cell>
-          <cell r="C19">
-            <v>6.0454524251339681E-2</v>
-          </cell>
-          <cell r="D19">
-            <v>1.3049169282590145E-3</v>
-          </cell>
-          <cell r="E19">
-            <v>0.59827622801698011</v>
-          </cell>
-          <cell r="F19">
-            <v>0.23079669496664645</v>
-          </cell>
-          <cell r="G19">
-            <v>0.12018992226693863</v>
-          </cell>
-          <cell r="H19">
-            <v>2.1491661613098842</v>
-          </cell>
-          <cell r="I19">
-            <v>0.22462747985792253</v>
-          </cell>
-          <cell r="J19">
-            <v>7.6756220099723729E-2</v>
-          </cell>
-          <cell r="K19">
-            <v>7.5754450984786573E-2</v>
-          </cell>
-          <cell r="L19">
-            <v>6.2214148462070025</v>
-          </cell>
-          <cell r="M19">
-            <v>0.98731741711499998</v>
-          </cell>
-          <cell r="N19">
-            <v>1.2417626853446999</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>3.6225194100754643E-2</v>
-          </cell>
-          <cell r="C20">
-            <v>7.5197516131309983E-2</v>
-          </cell>
-          <cell r="D20">
-            <v>4.9323420299485221E-3</v>
-          </cell>
-          <cell r="E20">
-            <v>0.66393723468768961</v>
-          </cell>
-          <cell r="F20">
-            <v>0.2161741964827168</v>
-          </cell>
-          <cell r="G20">
-            <v>3.1206929819725452E-2</v>
-          </cell>
-          <cell r="H20">
-            <v>2.4099302607640993</v>
-          </cell>
-          <cell r="I20">
-            <v>0.19449016720090101</v>
-          </cell>
-          <cell r="J20">
-            <v>0.17959106108078965</v>
-          </cell>
-          <cell r="K20">
-            <v>6.8668470021356828E-2</v>
-          </cell>
-          <cell r="L20">
-            <v>6.7577688027980312</v>
-          </cell>
-          <cell r="M20">
-            <v>1.2063677458031901</v>
-          </cell>
-          <cell r="N20">
-            <v>1.3416211855172999</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>2.758176706097637E-2</v>
-          </cell>
-          <cell r="C21">
-            <v>0.11124933921000979</v>
-          </cell>
-          <cell r="D21">
-            <v>-8.539218035410745E-3</v>
-          </cell>
-          <cell r="E21">
-            <v>0.70350667070952111</v>
-          </cell>
-          <cell r="F21">
-            <v>0.19968693147362038</v>
-          </cell>
-          <cell r="G21">
-            <v>-5.0660294577062309E-2</v>
-          </cell>
-          <cell r="H21">
-            <v>2.7882439573767646</v>
-          </cell>
-          <cell r="I21">
-            <v>0.15332344277917354</v>
-          </cell>
-          <cell r="J21">
-            <v>0.1981260738831615</v>
-          </cell>
-          <cell r="K21">
-            <v>0.11401256855274608</v>
-          </cell>
-          <cell r="L21">
-            <v>7.2685611082121646</v>
-          </cell>
-          <cell r="M21">
-            <v>1.40794895115539</v>
-          </cell>
-          <cell r="N21">
-            <v>1.53743009341309</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>2.1894933921660087E-3</v>
-          </cell>
-          <cell r="C22">
-            <v>0.1095270515739607</v>
-          </cell>
-          <cell r="D22">
-            <v>-9.0765851213908677E-3</v>
-          </cell>
-          <cell r="E22">
-            <v>0.68766373559733174</v>
-          </cell>
-          <cell r="F22">
-            <v>0.24489614918132202</v>
-          </cell>
-          <cell r="G22">
-            <v>-8.1418720252862148E-2</v>
-          </cell>
-          <cell r="H22">
-            <v>3.1261110629818929</v>
-          </cell>
-          <cell r="I22">
-            <v>0.13795698691847874</v>
-          </cell>
-          <cell r="J22">
-            <v>0.10220303972104304</v>
-          </cell>
-          <cell r="K22">
-            <v>0.11854842032061594</v>
-          </cell>
-          <cell r="L22">
-            <v>7.9353676294300985</v>
-          </cell>
-          <cell r="M22">
-            <v>1.6410369682385999</v>
-          </cell>
-          <cell r="N22">
-            <v>1.8136244201388001</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>-5.721645728842778E-2</v>
-          </cell>
-          <cell r="C23">
-            <v>0.10316131568932452</v>
-          </cell>
-          <cell r="D23">
-            <v>1.3367565199172704E-2</v>
-          </cell>
-          <cell r="E23">
-            <v>0.78666312916919356</v>
-          </cell>
-          <cell r="F23">
-            <v>0.35760839902971492</v>
-          </cell>
-          <cell r="G23">
-            <v>-0.15485624896631564</v>
-          </cell>
-          <cell r="H23">
-            <v>3.5081066447197431</v>
-          </cell>
-          <cell r="I23">
-            <v>0.20453413324092523</v>
-          </cell>
-          <cell r="J23">
-            <v>9.5486005828448225E-2</v>
-          </cell>
-          <cell r="K23">
-            <v>0.1307840967516545</v>
-          </cell>
-          <cell r="L23">
-            <v>8.5757310632236603</v>
-          </cell>
-          <cell r="M23">
-            <v>1.9416306690702001</v>
-          </cell>
-          <cell r="N23">
-            <v>2.0722997117465001</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>-0.11485911389465797</v>
-          </cell>
-          <cell r="C24">
-            <v>9.5337184033726152E-2</v>
-          </cell>
-          <cell r="D24">
-            <v>4.2550898482750982E-2</v>
-          </cell>
-          <cell r="E24">
-            <v>0.78992268041237124</v>
-          </cell>
-          <cell r="F24">
-            <v>0.55572089144936332</v>
-          </cell>
-          <cell r="G24">
-            <v>-0.1978575169524229</v>
-          </cell>
-          <cell r="H24">
-            <v>4.0085722948973395</v>
-          </cell>
-          <cell r="I24">
-            <v>0.32311790695659709</v>
-          </cell>
-          <cell r="J24">
-            <v>0.16018746630954783</v>
-          </cell>
-          <cell r="K24">
-            <v>0.14197335506367495</v>
-          </cell>
-          <cell r="L24">
-            <v>9.2844058061968493</v>
-          </cell>
-          <cell r="M24">
-            <v>2.1262418688959999</v>
-          </cell>
-          <cell r="N24">
-            <v>2.3051681170073</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>-0.1327420061179076</v>
-          </cell>
-          <cell r="C25">
-            <v>8.5164240016026849E-2</v>
-          </cell>
-          <cell r="D25">
-            <v>-1.4798637138989656E-3</v>
-          </cell>
-          <cell r="E25">
-            <v>0.76066252274105528</v>
-          </cell>
-          <cell r="F25">
-            <v>0.48101652516676774</v>
-          </cell>
-          <cell r="G25">
-            <v>-0.21397150706580662</v>
-          </cell>
-          <cell r="H25">
-            <v>4.450723382136359</v>
-          </cell>
-          <cell r="I25">
-            <v>0.19765767131594902</v>
-          </cell>
-          <cell r="J25">
-            <v>0.11991684775284682</v>
-          </cell>
-          <cell r="K25">
-            <v>0.14431955631871754</v>
-          </cell>
-          <cell r="L25">
-            <v>10.08166489204169</v>
-          </cell>
-          <cell r="M25">
-            <v>2.3144716728414001</v>
-          </cell>
-          <cell r="N25">
-            <v>2.4666801446144002</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>-0.14347768435417019</v>
-          </cell>
-          <cell r="C26">
-            <v>7.9979027011300663E-2</v>
-          </cell>
-          <cell r="D26">
-            <v>2.1119341867156721E-2</v>
-          </cell>
-          <cell r="E26">
-            <v>0.67075955124317777</v>
-          </cell>
-          <cell r="F26">
-            <v>0.40500075803517283</v>
-          </cell>
-          <cell r="G26">
-            <v>-0.32064198687910023</v>
-          </cell>
-          <cell r="H26">
-            <v>4.9230875855496823</v>
-          </cell>
-          <cell r="I26">
-            <v>0.11892488954344627</v>
-          </cell>
-          <cell r="J26">
-            <v>0.22308332912202677</v>
-          </cell>
-          <cell r="K26">
-            <v>0.16518406247528147</v>
-          </cell>
-          <cell r="L26">
-            <v>10.769625883199121</v>
-          </cell>
-          <cell r="M26">
-            <v>2.4831734924862001</v>
-          </cell>
-          <cell r="N26">
-            <v>2.6163331330647002</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>-0.14226288520500047</v>
-          </cell>
-          <cell r="C27">
-            <v>9.7128502985477039E-2</v>
-          </cell>
-          <cell r="D27">
-            <v>4.7315000952068059E-2</v>
-          </cell>
-          <cell r="E27">
-            <v>0.67341267434808982</v>
-          </cell>
-          <cell r="F27">
-            <v>0.39568450576106728</v>
-          </cell>
-          <cell r="G27">
-            <v>-0.33626784828270573</v>
-          </cell>
-          <cell r="H27">
-            <v>5.4463484362817276</v>
-          </cell>
-          <cell r="I27">
-            <v>0.12541150480810881</v>
-          </cell>
-          <cell r="J27">
-            <v>0.27322419732497805</v>
-          </cell>
-          <cell r="K27">
-            <v>0.21659862202388802</v>
-          </cell>
-          <cell r="L27">
-            <v>11.372528276474819</v>
-          </cell>
-          <cell r="M27">
-            <v>2.5230405275279901</v>
-          </cell>
-          <cell r="N27">
-            <v>2.7025806905687002</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>-0.13423821917069834</v>
-          </cell>
-          <cell r="C28">
-            <v>9.8350968943281214E-2</v>
-          </cell>
-          <cell r="D28">
-            <v>4.8882321619510005E-2</v>
-          </cell>
-          <cell r="E28">
-            <v>0.76596876895087951</v>
-          </cell>
-          <cell r="F28">
-            <v>0.43818753790175863</v>
-          </cell>
-          <cell r="G28">
-            <v>-0.20802207949721591</v>
-          </cell>
-          <cell r="H28">
-            <v>5.8488109676860427</v>
-          </cell>
-          <cell r="I28">
-            <v>0.24743350948626874</v>
-          </cell>
-          <cell r="J28">
-            <v>0.40085310541742464</v>
-          </cell>
-          <cell r="K28">
-            <v>0.22349921395048386</v>
-          </cell>
-          <cell r="L28">
-            <v>11.977634260369216</v>
-          </cell>
-          <cell r="M28">
-            <v>2.6570536594055998</v>
-          </cell>
-          <cell r="N28">
-            <v>2.780809920461</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>-0.1388824225366625</v>
-          </cell>
-          <cell r="C29">
-            <v>0.1168391281535951</v>
-          </cell>
-          <cell r="D29">
-            <v>0.10105466861993598</v>
-          </cell>
-          <cell r="E29">
-            <v>0.88460127349909046</v>
-          </cell>
-          <cell r="F29">
-            <v>0.56099681625227404</v>
-          </cell>
-          <cell r="G29">
-            <v>-0.12509188305125235</v>
-          </cell>
-          <cell r="H29">
-            <v>6.1747660920038099</v>
-          </cell>
-          <cell r="I29">
-            <v>0.38216884692021141</v>
-          </cell>
-          <cell r="J29">
-            <v>0.45116242588100519</v>
-          </cell>
-          <cell r="K29">
-            <v>0.2577137906372769</v>
-          </cell>
-          <cell r="L29">
-            <v>12.332412349979551</v>
-          </cell>
-          <cell r="M29">
-            <v>2.7185699294388002</v>
-          </cell>
-          <cell r="N29">
-            <v>2.8784448507917002</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30">
-            <v>-0.13641961390186996</v>
-          </cell>
-          <cell r="C30">
-            <v>0.13174202801803903</v>
-          </cell>
-          <cell r="D30">
-            <v>0.16573993568780615</v>
-          </cell>
-          <cell r="E30">
-            <v>1.0087674348089752</v>
-          </cell>
-          <cell r="F30">
-            <v>0.7068427835051545</v>
-          </cell>
-          <cell r="G30">
-            <v>-3.3197346417479807E-3</v>
-          </cell>
-          <cell r="H30">
-            <v>6.5337498917092596</v>
-          </cell>
-          <cell r="I30">
-            <v>0.50751537728493457</v>
-          </cell>
-          <cell r="J30">
-            <v>0.5138898364328548</v>
-          </cell>
-          <cell r="K30">
-            <v>0.28865316100667071</v>
-          </cell>
-          <cell r="L30">
-            <v>12.738313741943672</v>
-          </cell>
-          <cell r="M30">
-            <v>2.7974929330817999</v>
-          </cell>
-          <cell r="N30">
-            <v>2.9669159781376</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>-8.1435532124255472E-2</v>
-          </cell>
-          <cell r="C31">
-            <v>0.16113713510920857</v>
-          </cell>
-          <cell r="D31">
-            <v>0.21265105648298455</v>
-          </cell>
-          <cell r="E31">
-            <v>1.0734278350515465</v>
-          </cell>
-          <cell r="F31">
-            <v>0.72359536082474218</v>
-          </cell>
-          <cell r="G31">
-            <v>0.16904873477038423</v>
-          </cell>
-          <cell r="H31">
-            <v>6.9360499870051093</v>
-          </cell>
-          <cell r="I31">
-            <v>0.53567096941869541</v>
-          </cell>
-          <cell r="J31">
-            <v>0.58669279782359673</v>
-          </cell>
-          <cell r="K31">
-            <v>0.36441548072613184</v>
-          </cell>
-          <cell r="L31">
-            <v>13.106754093389933</v>
-          </cell>
-          <cell r="M31">
-            <v>2.8673694264258001</v>
-          </cell>
-          <cell r="N31">
-            <v>2.9525638455216998</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32">
-            <v>-4.5531662594611888E-2</v>
-          </cell>
-          <cell r="C32">
-            <v>0.18419708981003935</v>
-          </cell>
-          <cell r="D32">
-            <v>0.22505942274882482</v>
-          </cell>
-          <cell r="E32">
-            <v>1.0704714978775016</v>
-          </cell>
-          <cell r="F32">
-            <v>0.7778706791995148</v>
-          </cell>
-          <cell r="G32">
-            <v>0.26659982174688057</v>
-          </cell>
-          <cell r="H32">
-            <v>7.2609222039331174</v>
-          </cell>
-          <cell r="I32">
-            <v>0.61531880793554539</v>
-          </cell>
-          <cell r="J32">
-            <v>0.77072689256114801</v>
-          </cell>
-          <cell r="K32">
-            <v>0.45523550999288109</v>
-          </cell>
-          <cell r="L32">
-            <v>13.465498646113923</v>
-          </cell>
-          <cell r="M32">
-            <v>2.9246431950774001</v>
-          </cell>
-          <cell r="N32">
-            <v>2.9991240503930001</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>1.6838223218711978E-2</v>
-          </cell>
-          <cell r="C33">
-            <v>0.20005681613895504</v>
-          </cell>
-          <cell r="D33">
-            <v>0.32288627221194571</v>
-          </cell>
-          <cell r="E33">
-            <v>1.1853138265615526</v>
-          </cell>
-          <cell r="F33">
-            <v>0.79568450576106742</v>
-          </cell>
-          <cell r="G33">
-            <v>0.53040754727382988</v>
-          </cell>
-          <cell r="H33">
-            <v>7.5841700597764863</v>
-          </cell>
-          <cell r="I33">
-            <v>0.68619509659533917</v>
-          </cell>
-          <cell r="J33">
-            <v>0.99513688851829374</v>
-          </cell>
-          <cell r="K33">
-            <v>0.58070269036570255</v>
-          </cell>
-          <cell r="L33">
-            <v>13.885503018037712</v>
-          </cell>
-          <cell r="M33">
-            <v>2.9892165616944002</v>
-          </cell>
-          <cell r="N33">
-            <v>3.0388114030256999</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34">
-            <v>8.3691504453073995E-2</v>
-          </cell>
-          <cell r="C34">
-            <v>0.24441162101255087</v>
-          </cell>
-          <cell r="D34">
-            <v>0.43313135150709436</v>
-          </cell>
-          <cell r="E34">
-            <v>1.2711992116434203</v>
-          </cell>
-          <cell r="F34">
-            <v>0.80978395997574293</v>
-          </cell>
-          <cell r="G34">
-            <v>0.81150077181763047</v>
-          </cell>
-          <cell r="H34">
-            <v>7.8841354067400129</v>
-          </cell>
-          <cell r="I34">
-            <v>0.89860738109676874</v>
-          </cell>
-          <cell r="J34">
-            <v>1.2492892367428066</v>
-          </cell>
-          <cell r="K34">
-            <v>0.68602426206923828</v>
-          </cell>
-          <cell r="L34">
-            <v>14.227059563935859</v>
-          </cell>
-          <cell r="M34">
-            <v>3.1433191854084002</v>
-          </cell>
-          <cell r="N34">
-            <v>3.1268782449458001</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35">
-            <v>0.14398574423814006</v>
-          </cell>
-          <cell r="C35">
-            <v>0.26196654673970848</v>
-          </cell>
-          <cell r="D35">
-            <v>0.47874048156531818</v>
-          </cell>
-          <cell r="E35">
-            <v>1.4303107944208613</v>
-          </cell>
-          <cell r="F35">
-            <v>0.91909263189811996</v>
-          </cell>
-          <cell r="G35">
-            <v>1.027311088446625</v>
-          </cell>
-          <cell r="H35">
-            <v>8.1960127349908998</v>
-          </cell>
-          <cell r="I35">
-            <v>1.0858962141557653</v>
-          </cell>
-          <cell r="J35">
-            <v>1.418583758675291</v>
-          </cell>
-          <cell r="K35">
-            <v>0.78498081017480947</v>
-          </cell>
-          <cell r="L35">
-            <v>14.356189974191549</v>
-          </cell>
-          <cell r="M35">
-            <v>3.1363315360740001</v>
-          </cell>
-          <cell r="N35">
-            <v>3.1805134447686001</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36">
-            <v>0.20354586079636958</v>
-          </cell>
-          <cell r="C36">
-            <v>0.3044513893905007</v>
-          </cell>
-          <cell r="D36">
-            <v>0.52204153713530133</v>
-          </cell>
-          <cell r="E36">
-            <v>1.5418177683444514</v>
-          </cell>
-          <cell r="F36">
-            <v>1.0765365372953304</v>
-          </cell>
-          <cell r="G36">
-            <v>1.2365747376738883</v>
-          </cell>
-          <cell r="H36">
-            <v>8.4835246469721888</v>
-          </cell>
-          <cell r="I36">
-            <v>1.2736723555401541</v>
-          </cell>
-          <cell r="J36">
-            <v>1.561610256215888</v>
-          </cell>
-          <cell r="K36">
-            <v>0.862514625135128</v>
-          </cell>
-          <cell r="L36">
-            <v>14.485320384447235</v>
-          </cell>
-          <cell r="M36">
-            <v>3.1727671361748002</v>
-          </cell>
-          <cell r="N36">
-            <v>3.1667003593871001</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37">
-            <v>0.27122503066092268</v>
-          </cell>
-          <cell r="C37">
-            <v>0.36284838721757418</v>
-          </cell>
-          <cell r="D37">
-            <v>0.60404722643116482</v>
-          </cell>
-          <cell r="E37">
-            <v>1.5743374772589449</v>
-          </cell>
-          <cell r="F37">
-            <v>1.1988834141904183</v>
-          </cell>
-          <cell r="G37">
-            <v>1.4531316040943083</v>
-          </cell>
-          <cell r="H37">
-            <v>8.7098522914320338</v>
-          </cell>
-          <cell r="I37">
-            <v>1.4730897513644634</v>
-          </cell>
-          <cell r="J37">
-            <v>1.7972854971026209</v>
-          </cell>
-          <cell r="K37">
-            <v>0.93656724595934304</v>
-          </cell>
-          <cell r="L37">
-            <v>14.364122900418858</v>
-          </cell>
-          <cell r="M37">
-            <v>3.1866800451174</v>
-          </cell>
-          <cell r="N37">
-            <v>3.0808570873089001</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38">
-            <v>0.29866725604505151</v>
-          </cell>
-          <cell r="C38">
-            <v>0.43331275808059422</v>
-          </cell>
-          <cell r="D38">
-            <v>0.67372345799069877</v>
-          </cell>
-          <cell r="E38">
-            <v>1.6208808368708307</v>
-          </cell>
-          <cell r="F38">
-            <v>1.4012030018192843</v>
-          </cell>
-          <cell r="G38">
-            <v>1.7121269548119149</v>
-          </cell>
-          <cell r="H38">
-            <v>8.8982781772502779</v>
-          </cell>
-          <cell r="I38">
-            <v>1.6577796066880361</v>
-          </cell>
-          <cell r="J38">
-            <v>2.0306971607371471</v>
-          </cell>
-          <cell r="K38">
-            <v>1.0287673936114115</v>
-          </cell>
-          <cell r="L38">
-            <v>14.169766207849719</v>
-          </cell>
-          <cell r="M38">
-            <v>3.1232296935720001</v>
-          </cell>
-          <cell r="N38">
-            <v>2.9768209710696998</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39">
-            <v>0.36075310608608785</v>
-          </cell>
-          <cell r="C39">
-            <v>0.48409883489803662</v>
-          </cell>
-          <cell r="D39">
-            <v>0.73050800854113174</v>
-          </cell>
-          <cell r="E39">
-            <v>1.7470936931473622</v>
-          </cell>
-          <cell r="F39">
-            <v>1.5355268344451181</v>
-          </cell>
-          <cell r="G39">
-            <v>2.1196857140231908</v>
-          </cell>
-          <cell r="H39">
-            <v>9.0661288226630816</v>
-          </cell>
-          <cell r="I39">
-            <v>1.7615762799965347</v>
-          </cell>
-          <cell r="J39">
-            <v>2.2461581303483587</v>
-          </cell>
-          <cell r="K39">
-            <v>1.1754513193107814</v>
-          </cell>
-          <cell r="L39">
-            <v>13.800885138279719</v>
-          </cell>
-          <cell r="M39">
-            <v>3.1072579236647999</v>
-          </cell>
-          <cell r="N39">
-            <v>2.8629472428026999</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40">
-            <v>0.44363911422082758</v>
-          </cell>
-          <cell r="C40">
-            <v>0.53731411497687753</v>
-          </cell>
-          <cell r="D40">
-            <v>0.81117225283528116</v>
-          </cell>
-          <cell r="E40">
-            <v>2.0417419648271684</v>
-          </cell>
-          <cell r="F40">
-            <v>1.7764304123711339</v>
-          </cell>
-          <cell r="G40">
-            <v>2.6021291600051448</v>
-          </cell>
-          <cell r="H40">
-            <v>9.1332690808282049</v>
-          </cell>
-          <cell r="I40">
-            <v>1.9911526466256608</v>
-          </cell>
-          <cell r="J40">
-            <v>2.5684810027963074</v>
-          </cell>
-          <cell r="K40">
-            <v>1.2806492983230946</v>
-          </cell>
-          <cell r="L40">
-            <v>13.143333697660317</v>
-          </cell>
-          <cell r="M40">
-            <v>3.1356452490857998</v>
-          </cell>
-          <cell r="N40">
-            <v>2.8716393794574002</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41">
-            <v>0.58004620141683916</v>
-          </cell>
-          <cell r="C41">
-            <v>0.55998085332244318</v>
-          </cell>
-          <cell r="D41">
-            <v>0.90387004788008807</v>
-          </cell>
-          <cell r="E41">
-            <v>2.3732307459066107</v>
-          </cell>
-          <cell r="F41">
-            <v>2.1148173135233472</v>
-          </cell>
-          <cell r="G41">
-            <v>2.9826972729110381</v>
-          </cell>
-          <cell r="H41">
-            <v>9.1505955990643653</v>
-          </cell>
-          <cell r="I41">
-            <v>2.2942584250194917</v>
-          </cell>
-          <cell r="J41">
-            <v>2.9484461331783569</v>
-          </cell>
-          <cell r="K41">
-            <v>1.3786171048988849</v>
-          </cell>
-          <cell r="L41">
-            <v>12.37163626299237</v>
-          </cell>
-          <cell r="M41">
-            <v>3.1098159024390002</v>
-          </cell>
-          <cell r="N41">
-            <v>2.8338386921451</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42">
-            <v>0.71391881556782777</v>
-          </cell>
-          <cell r="C42">
-            <v>0.59668104648026765</v>
-          </cell>
-          <cell r="D42">
-            <v>0.97636725936969726</v>
-          </cell>
-          <cell r="E42">
-            <v>2.6213356579745302</v>
-          </cell>
-          <cell r="F42">
-            <v>2.5570550333535476</v>
-          </cell>
-          <cell r="G42">
-            <v>3.4234487843872312</v>
-          </cell>
-          <cell r="H42">
-            <v>9.093201507407084</v>
-          </cell>
-          <cell r="I42">
-            <v>2.6462574720609888</v>
-          </cell>
-          <cell r="J42">
-            <v>3.240974012027491</v>
-          </cell>
-          <cell r="K42">
-            <v>1.4656881558652148</v>
-          </cell>
-          <cell r="L42">
-            <v>11.450976102500459</v>
-          </cell>
-          <cell r="M42">
-            <v>3.1545493361244001</v>
-          </cell>
-          <cell r="N42">
-            <v>2.8093794238842</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43">
-            <v>0.84396350146459309</v>
-          </cell>
-          <cell r="C43">
-            <v>0.61836911300829445</v>
-          </cell>
-          <cell r="D43">
-            <v>1.0658889861016243</v>
-          </cell>
-          <cell r="E43">
-            <v>2.8811901152213464</v>
-          </cell>
-          <cell r="F43">
-            <v>2.9729131291691933</v>
-          </cell>
-          <cell r="G43">
-            <v>3.8735608817097593</v>
-          </cell>
-          <cell r="H43">
-            <v>8.9551308152126801</v>
-          </cell>
-          <cell r="I43">
-            <v>3.0265204019752225</v>
-          </cell>
-          <cell r="J43">
-            <v>3.5702981815578463</v>
-          </cell>
-          <cell r="K43">
-            <v>1.5144042749887943</v>
-          </cell>
-          <cell r="L43">
-            <v>10.289683846446755</v>
-          </cell>
-          <cell r="M43">
-            <v>3.1674640094478002</v>
-          </cell>
-          <cell r="N43">
-            <v>2.8272353635237</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44">
-            <v>0.95032397373365451</v>
-          </cell>
-          <cell r="C44">
-            <v>0.68408867318447886</v>
-          </cell>
-          <cell r="D44">
-            <v>1.1964826024448085</v>
-          </cell>
-          <cell r="E44">
-            <v>3.0665297149787749</v>
-          </cell>
-          <cell r="F44">
-            <v>3.2737014857489384</v>
-          </cell>
-          <cell r="G44">
-            <v>4.2997259587996393</v>
-          </cell>
-          <cell r="H44">
-            <v>8.9009854457246789</v>
-          </cell>
-          <cell r="I44">
-            <v>3.3704517889630075</v>
-          </cell>
-          <cell r="J44">
-            <v>3.8491393142308468</v>
-          </cell>
-          <cell r="K44">
-            <v>1.5838427686740317</v>
-          </cell>
-          <cell r="L44">
-            <v>9.2354860944617609</v>
-          </cell>
-          <cell r="M44">
-            <v>3.112311491487</v>
-          </cell>
-          <cell r="N44">
-            <v>2.7999460972821999</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45">
-            <v>1.0726254074997388</v>
-          </cell>
-          <cell r="C45">
-            <v>0.75637057742293079</v>
-          </cell>
-          <cell r="D45">
-            <v>1.227552835940356</v>
-          </cell>
-          <cell r="E45">
-            <v>3.3445012128562768</v>
-          </cell>
-          <cell r="F45">
-            <v>3.5208967556094599</v>
-          </cell>
-          <cell r="G45">
-            <v>4.691779453112078</v>
-          </cell>
-          <cell r="H45">
-            <v>8.853337520575236</v>
-          </cell>
-          <cell r="I45">
-            <v>3.651033093649831</v>
-          </cell>
-          <cell r="J45">
-            <v>4.1548275259416467</v>
-          </cell>
-          <cell r="K45">
-            <v>1.6673296315949062</v>
-          </cell>
-          <cell r="L45">
-            <v>8.0248334085492257</v>
-          </cell>
-          <cell r="M45">
-            <v>3.1425705086939999</v>
-          </cell>
-          <cell r="N45">
-            <v>2.7555420813485001</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>1.1816951440583159</v>
-          </cell>
-          <cell r="C46">
-            <v>0.84031790020083008</v>
-          </cell>
-          <cell r="D46">
-            <v>1.3634727780256337</v>
-          </cell>
-          <cell r="E46">
-            <v>3.8206231049120687</v>
-          </cell>
-          <cell r="F46">
-            <v>3.9315244087325651</v>
-          </cell>
-          <cell r="G46">
-            <v>5.104219499421137</v>
-          </cell>
-          <cell r="H46">
-            <v>8.630800051979552</v>
-          </cell>
-          <cell r="I46">
-            <v>4.0734211210257296</v>
-          </cell>
-          <cell r="J46">
-            <v>4.6129123921905517</v>
-          </cell>
-          <cell r="K46">
-            <v>1.7357381861866217</v>
-          </cell>
-          <cell r="L46">
-            <v>6.718104171661472</v>
-          </cell>
-          <cell r="M46">
-            <v>3.1576064327081901</v>
-          </cell>
-          <cell r="N46">
-            <v>2.7884913435512</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47">
-            <v>1.3250589227848306</v>
-          </cell>
-          <cell r="C47">
-            <v>0.90439468982614368</v>
-          </cell>
-          <cell r="D47">
-            <v>1.4572752924836139</v>
-          </cell>
-          <cell r="E47">
-            <v>4.2873453608247418</v>
-          </cell>
-          <cell r="F47">
-            <v>4.3197900242571263</v>
-          </cell>
-          <cell r="G47">
-            <v>5.4056533344359297</v>
-          </cell>
-          <cell r="H47">
-            <v>8.3097180109157041</v>
-          </cell>
-          <cell r="I47">
-            <v>4.4343541540327465</v>
-          </cell>
-          <cell r="J47">
-            <v>5.1168478581295052</v>
-          </cell>
-          <cell r="K47">
-            <v>1.8311105462467374</v>
-          </cell>
-          <cell r="L47">
-            <v>5.408289907907541</v>
-          </cell>
-          <cell r="M47">
-            <v>3.2766460302978002</v>
-          </cell>
-          <cell r="N47">
-            <v>2.9345057631692999</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48">
-            <v>1.4789101761804391</v>
-          </cell>
-          <cell r="C48">
-            <v>0.96814816822601613</v>
-          </cell>
-          <cell r="D48">
-            <v>1.4997872627584736</v>
-          </cell>
-          <cell r="E48">
-            <v>4.7198802304426932</v>
-          </cell>
-          <cell r="F48">
-            <v>4.8135741358399029</v>
-          </cell>
-          <cell r="G48">
-            <v>5.8617378300898606</v>
-          </cell>
-          <cell r="H48">
-            <v>7.9799727107337768</v>
-          </cell>
-          <cell r="I48">
-            <v>4.8295612059256694</v>
-          </cell>
-          <cell r="J48">
-            <v>5.502814100296475</v>
-          </cell>
-          <cell r="K48">
-            <v>1.9027325108102409</v>
-          </cell>
-          <cell r="L48">
-            <v>4.0753379426572831</v>
-          </cell>
-          <cell r="M48">
-            <v>3.3537597318809902</v>
-          </cell>
-          <cell r="N48">
-            <v>3.1604339352872</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49">
-            <v>1.6342296760297208</v>
-          </cell>
-          <cell r="C49">
-            <v>1.0089552877610193</v>
-          </cell>
-          <cell r="D49">
-            <v>1.5663663345346439</v>
-          </cell>
-          <cell r="E49">
-            <v>5.0932883565797455</v>
-          </cell>
-          <cell r="F49">
-            <v>5.2442139175257738</v>
-          </cell>
-          <cell r="G49">
-            <v>6.3171332028594005</v>
-          </cell>
-          <cell r="H49">
-            <v>7.5966234947587266</v>
-          </cell>
-          <cell r="I49">
-            <v>5.1882201334141902</v>
-          </cell>
-          <cell r="J49">
-            <v>5.7907621833097496</v>
-          </cell>
-          <cell r="K49">
-            <v>1.969184181124265</v>
-          </cell>
-          <cell r="L49">
-            <v>2.7539768640613764</v>
-          </cell>
-          <cell r="M49">
-            <v>3.4801613171621999</v>
-          </cell>
-          <cell r="N49">
-            <v>3.3187790603921998</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50">
-            <v>1.7710737413369486</v>
-          </cell>
-          <cell r="C50">
-            <v>1.0404999775942927</v>
-          </cell>
-          <cell r="D50">
-            <v>1.6387649103623607</v>
-          </cell>
-          <cell r="E50">
-            <v>5.4099954517889639</v>
-          </cell>
-          <cell r="F50">
-            <v>5.6702296846573681</v>
-          </cell>
-          <cell r="G50">
-            <v>6.7845882261058126</v>
-          </cell>
-          <cell r="H50">
-            <v>7.2338495191891177</v>
-          </cell>
-          <cell r="I50">
-            <v>5.566533830026855</v>
-          </cell>
-          <cell r="J50">
-            <v>6.0908177725557557</v>
-          </cell>
-          <cell r="K50">
-            <v>2.0148516805310202</v>
-          </cell>
-          <cell r="L50">
-            <v>1.7277206411214689</v>
-          </cell>
-          <cell r="M50">
-            <v>3.5122296364290002</v>
-          </cell>
-          <cell r="N50">
-            <v>3.4695775242156</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51">
-            <v>1.8904561613201349</v>
-          </cell>
-          <cell r="C51">
-            <v>1.0710834718924769</v>
-          </cell>
-          <cell r="D51">
-            <v>1.6841373148320307</v>
-          </cell>
-          <cell r="E51">
-            <v>5.6874363250454829</v>
-          </cell>
-          <cell r="F51">
-            <v>6.1133770466949668</v>
-          </cell>
-          <cell r="G51">
-            <v>7.1561403146075664</v>
-          </cell>
-          <cell r="H51">
-            <v>6.8115156371827057</v>
-          </cell>
-          <cell r="I51">
-            <v>5.8350948626873427</v>
-          </cell>
-          <cell r="J51">
-            <v>6.3440225768142291</v>
-          </cell>
-          <cell r="K51">
-            <v>2.0654834863685503</v>
-          </cell>
-          <cell r="L51">
-            <v>0.72015086662811856</v>
-          </cell>
-          <cell r="M51">
-            <v>3.7058249568276</v>
-          </cell>
-          <cell r="N51">
-            <v>3.5249646275502</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52">
-            <v>1.9768030360956754</v>
-          </cell>
-          <cell r="C52">
-            <v>1.1277940084625391</v>
-          </cell>
-          <cell r="D52">
-            <v>1.7476586810896078</v>
-          </cell>
-          <cell r="E52">
-            <v>6.1104199514857491</v>
-          </cell>
-          <cell r="F52">
-            <v>6.5418943298969072</v>
-          </cell>
-          <cell r="G52">
-            <v>7.4444233879118649</v>
-          </cell>
-          <cell r="H52">
-            <v>6.2484037945074924</v>
-          </cell>
-          <cell r="I52">
-            <v>6.1296456727020701</v>
-          </cell>
-          <cell r="J52">
-            <v>6.5914368346135692</v>
-          </cell>
-          <cell r="K52">
-            <v>2.0951457322619773</v>
-          </cell>
-          <cell r="L52">
-            <v>-0.34520586824996119</v>
-          </cell>
-          <cell r="M52">
-            <v>3.7758886193502001</v>
-          </cell>
-          <cell r="N52">
-            <v>3.5637760284270001</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53">
-            <v>2.0738121767847946</v>
-          </cell>
-          <cell r="C53">
-            <v>1.1522608039010866</v>
-          </cell>
-          <cell r="D53">
-            <v>1.7898747443787941</v>
-          </cell>
-          <cell r="E53">
-            <v>6.4289463311097634</v>
-          </cell>
-          <cell r="F53">
-            <v>6.7860574590661011</v>
-          </cell>
-          <cell r="G53">
-            <v>7.6655169799878706</v>
-          </cell>
-          <cell r="H53">
-            <v>5.7069500996274787</v>
-          </cell>
-          <cell r="I53">
-            <v>6.2872086979121544</v>
-          </cell>
-          <cell r="J53">
-            <v>6.8757000244255764</v>
-          </cell>
-          <cell r="K53">
-            <v>2.0951457322619773</v>
-          </cell>
-          <cell r="L53">
-            <v>-1.3272051772039433</v>
-          </cell>
-          <cell r="M53">
-            <v>3.8802666312828</v>
-          </cell>
-          <cell r="N53">
-            <v>3.7760258769720001</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54">
-            <v>2.1945929267238604</v>
-          </cell>
-          <cell r="C54">
-            <v>1.2151754207430661</v>
-          </cell>
-          <cell r="D54">
-            <v>1.8378116760576366</v>
-          </cell>
-          <cell r="E54">
-            <v>6.7668784111582783</v>
-          </cell>
-          <cell r="F54">
-            <v>6.9982315039417831</v>
-          </cell>
-          <cell r="G54">
-            <v>7.9888304665821339</v>
-          </cell>
-          <cell r="H54">
-            <v>5.2421121025729862</v>
-          </cell>
-          <cell r="I54">
-            <v>6.4404400935631978</v>
-          </cell>
-          <cell r="J54">
-            <v>7.0841596969543819</v>
-          </cell>
-          <cell r="K54">
-            <v>2.0831984387771247</v>
-          </cell>
-          <cell r="L54">
-            <v>-2.1462357383615154</v>
-          </cell>
-          <cell r="M54">
-            <v>3.9247505060634</v>
-          </cell>
-          <cell r="N54">
-            <v>3.9723738321022002</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55">
-            <v>2.2884558250122513</v>
-          </cell>
-          <cell r="C55">
-            <v>1.2384188764096864</v>
-          </cell>
-          <cell r="D55">
-            <v>1.8302167300920427</v>
-          </cell>
-          <cell r="E55">
-            <v>7.1184551243177694</v>
-          </cell>
-          <cell r="F55">
-            <v>7.281281837477259</v>
-          </cell>
-          <cell r="G55">
-            <v>8.2248550544866479</v>
-          </cell>
-          <cell r="H55">
-            <v>4.7319544312570372</v>
-          </cell>
-          <cell r="I55">
-            <v>6.6109980074504024</v>
-          </cell>
-          <cell r="J55">
-            <v>7.2531383708981858</v>
-          </cell>
-          <cell r="K55">
-            <v>2.0315778914098139</v>
-          </cell>
-          <cell r="L55">
-            <v>-2.9214148462070035</v>
-          </cell>
-          <cell r="M55">
-            <v>4.07716860717</v>
-          </cell>
-          <cell r="N55">
-            <v>4.1086180205967997</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56">
-            <v>2.3316292624000177</v>
-          </cell>
-          <cell r="C56">
-            <v>1.2430500912605542</v>
-          </cell>
-          <cell r="D56">
-            <v>1.8315976293585272</v>
-          </cell>
-          <cell r="E56">
-            <v>7.4482762280169812</v>
-          </cell>
-          <cell r="F56">
-            <v>7.6922885081867793</v>
-          </cell>
-          <cell r="G56">
-            <v>8.4666223330944348</v>
-          </cell>
-          <cell r="H56">
-            <v>4.219197782205665</v>
-          </cell>
-          <cell r="I56">
-            <v>6.8871393918392094</v>
-          </cell>
-          <cell r="J56">
-            <v>7.3715813666531886</v>
-          </cell>
-          <cell r="K56">
-            <v>1.9499449188572786</v>
-          </cell>
-          <cell r="L56">
-            <v>-3.3843451633830228</v>
-          </cell>
-          <cell r="M56">
-            <v>4.0538348495712002</v>
-          </cell>
-          <cell r="N56">
-            <v>4.2472205407418997</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57">
-            <v>2.3408931983577217</v>
-          </cell>
-          <cell r="C57">
-            <v>1.2378072065237196</v>
-          </cell>
-          <cell r="D57">
-            <v>1.8718409794099011</v>
-          </cell>
-          <cell r="E57">
-            <v>7.4566146149181325</v>
-          </cell>
-          <cell r="F57">
-            <v>7.9545686779866589</v>
-          </cell>
-          <cell r="G57">
-            <v>8.4132153095539977</v>
-          </cell>
-          <cell r="H57">
-            <v>3.6835376418608674</v>
-          </cell>
-          <cell r="I57">
-            <v>7.0257515377284925</v>
-          </cell>
-          <cell r="J57">
-            <v>7.2531383708981858</v>
-          </cell>
-          <cell r="K57">
-            <v>1.8260432459066103</v>
-          </cell>
-          <cell r="L57">
-            <v>-3.8120621024722525</v>
-          </cell>
-          <cell r="M57">
-            <v>4.0636300365846001</v>
-          </cell>
-          <cell r="N57">
-            <v>4.2854255134799999</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58">
-            <v>2.3073332794166204</v>
-          </cell>
-          <cell r="C58">
-            <v>1.2180590073483235</v>
-          </cell>
-          <cell r="D58">
-            <v>1.8783509330946826</v>
-          </cell>
-          <cell r="E58">
-            <v>7.4482762280169812</v>
-          </cell>
-          <cell r="F58">
-            <v>8.0091472104305641</v>
-          </cell>
-          <cell r="G58">
-            <v>8.3029556480511602</v>
-          </cell>
-          <cell r="H58">
-            <v>3.0958979468075882</v>
-          </cell>
-          <cell r="I58">
-            <v>6.9039244563804898</v>
-          </cell>
-          <cell r="J58">
-            <v>7.0362560853379144</v>
-          </cell>
-          <cell r="K58">
-            <v>1.6931605040604318</v>
-          </cell>
-          <cell r="L58">
-            <v>-4.2494748402837521</v>
-          </cell>
-          <cell r="M58">
-            <v>3.8870047217124002</v>
-          </cell>
-          <cell r="N58">
-            <v>4.3644633142239</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59">
-            <v>2.2489530037586638</v>
-          </cell>
-          <cell r="C59">
-            <v>1.1374933452256775</v>
-          </cell>
-          <cell r="D59">
-            <v>1.9315155548537279</v>
-          </cell>
-          <cell r="E59">
-            <v>7.2335248635536695</v>
-          </cell>
-          <cell r="F59">
-            <v>7.8264607337780481</v>
-          </cell>
-          <cell r="G59">
-            <v>8.0066328077622799</v>
-          </cell>
-          <cell r="H59">
-            <v>2.4747964134107248</v>
-          </cell>
-          <cell r="I59">
-            <v>6.6256172572121628</v>
-          </cell>
-          <cell r="J59">
-            <v>6.6446045793747039</v>
-          </cell>
-          <cell r="K59">
-            <v>1.5061235646768794</v>
-          </cell>
-          <cell r="L59">
-            <v>-4.4325050770727863</v>
-          </cell>
-          <cell r="M59">
-            <v>3.6016965037998001</v>
-          </cell>
-          <cell r="N59">
-            <v>4.3736944981130002</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60">
-            <v>2.1638296676945181</v>
-          </cell>
-          <cell r="C60">
-            <v>1.0897830941205098</v>
-          </cell>
-          <cell r="D60">
-            <v>1.8953162669398695</v>
-          </cell>
-          <cell r="E60">
-            <v>7.1360415403274713</v>
-          </cell>
-          <cell r="F60">
-            <v>7.5080859611886002</v>
-          </cell>
-          <cell r="G60">
-            <v>7.6718339397614717</v>
-          </cell>
-          <cell r="H60">
-            <v>1.8818504721476215</v>
-          </cell>
-          <cell r="I60">
-            <v>6.2909988737763145</v>
-          </cell>
-          <cell r="J60">
-            <v>6.2161041413988265</v>
-          </cell>
-          <cell r="K60">
-            <v>1.3356068483534158</v>
-          </cell>
-          <cell r="L60">
-            <v>-4.5735348766694406</v>
-          </cell>
-          <cell r="M60">
-            <v>3.2867531659422</v>
-          </cell>
-          <cell r="N60">
-            <v>4.2100936624726</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61">
-            <v>2.0523128537131523</v>
-          </cell>
-          <cell r="C61">
-            <v>0.99777046698911176</v>
-          </cell>
-          <cell r="D61">
-            <v>1.8871295070029479</v>
-          </cell>
-          <cell r="E61">
-            <v>6.9325090964220744</v>
-          </cell>
-          <cell r="F61">
-            <v>7.269077471194664</v>
-          </cell>
-          <cell r="G61">
-            <v>7.2365379844533866</v>
-          </cell>
-          <cell r="H61">
-            <v>1.2563631638222295</v>
-          </cell>
-          <cell r="I61">
-            <v>5.8637919085159833</v>
-          </cell>
-          <cell r="J61">
-            <v>5.846561994643217</v>
-          </cell>
-          <cell r="K61">
-            <v>1.1247577171276399</v>
-          </cell>
-          <cell r="L61">
-            <v>-4.752907153031436</v>
-          </cell>
-          <cell r="M61">
-            <v>2.9936462322546</v>
-          </cell>
-          <cell r="N61">
-            <v>3.9617950301270999</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62">
-            <v>1.8929032387429194</v>
-          </cell>
-          <cell r="C62">
-            <v>0.84634721764818954</v>
-          </cell>
-          <cell r="D62">
-            <v>1.7858306822412786</v>
-          </cell>
-          <cell r="E62">
-            <v>6.5008838690115232</v>
-          </cell>
-          <cell r="F62">
-            <v>7.0039925712553064</v>
-          </cell>
-          <cell r="G62">
-            <v>6.7547262344487926</v>
-          </cell>
-          <cell r="H62">
-            <v>0.58796565017759672</v>
-          </cell>
-          <cell r="I62">
-            <v>5.4143853417655725</v>
-          </cell>
-          <cell r="J62">
-            <v>5.3312033597803365</v>
-          </cell>
-          <cell r="K62">
-            <v>0.9115191272048937</v>
-          </cell>
-          <cell r="L62">
-            <v>-4.8110819453650562</v>
-          </cell>
-          <cell r="M62">
-            <v>2.6795763505638002</v>
-          </cell>
-          <cell r="N62">
-            <v>3.7071625927773999</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63">
-            <v>1.7339655601328046</v>
-          </cell>
-          <cell r="C63">
-            <v>0.70935937761600731</v>
-          </cell>
-          <cell r="D63">
-            <v>1.7262547424593426</v>
-          </cell>
-          <cell r="E63">
-            <v>5.8949105518496063</v>
-          </cell>
-          <cell r="F63">
-            <v>6.4961848089751362</v>
-          </cell>
-          <cell r="G63">
-            <v>6.0535436995791745</v>
-          </cell>
-          <cell r="H63">
-            <v>-0.15115654509226367</v>
-          </cell>
-          <cell r="I63">
-            <v>4.9769449016720086</v>
-          </cell>
-          <cell r="J63">
-            <v>4.6024367672326649</v>
-          </cell>
-          <cell r="K63">
-            <v>0.63306479388034909</v>
-          </cell>
-          <cell r="L63">
-            <v>-4.8013861466427858</v>
-          </cell>
-          <cell r="M63">
-            <v>2.3309425605582001</v>
-          </cell>
-          <cell r="N63">
-            <v>3.3452597557821</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64">
-            <v>1.548826673974399</v>
-          </cell>
-          <cell r="C64">
-            <v>0.54991451462772645</v>
-          </cell>
-          <cell r="D64">
-            <v>1.5856989242652058</v>
-          </cell>
-          <cell r="E64">
-            <v>5.2901500909642216</v>
-          </cell>
-          <cell r="F64">
-            <v>5.863073832625834</v>
-          </cell>
-          <cell r="G64">
-            <v>5.4512502986199154</v>
-          </cell>
-          <cell r="H64">
-            <v>-0.98698778480464322</v>
-          </cell>
-          <cell r="I64">
-            <v>4.4452373732998343</v>
-          </cell>
-          <cell r="J64">
-            <v>3.8220816698672593</v>
-          </cell>
-          <cell r="K64">
-            <v>0.35570219599493769</v>
-          </cell>
-          <cell r="L64">
-            <v>-4.7886053210543391</v>
-          </cell>
-          <cell r="M64">
-            <v>1.9435023608562001</v>
-          </cell>
-          <cell r="N64">
-            <v>3.0408328301547001</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65">
-            <v>1.3137499292666575</v>
-          </cell>
-          <cell r="C65">
-            <v>0.40307005129030388</v>
-          </cell>
-          <cell r="D65">
-            <v>1.4607275406497873</v>
-          </cell>
-          <cell r="E65">
-            <v>4.6896346270466953</v>
-          </cell>
-          <cell r="F65">
-            <v>5.1881193147362037</v>
-          </cell>
-          <cell r="G65">
-            <v>4.6793178142859766</v>
-          </cell>
-          <cell r="H65">
-            <v>-1.7638114008489991</v>
-          </cell>
-          <cell r="I65">
-            <v>3.8306874296110189</v>
-          </cell>
-          <cell r="J65">
-            <v>3.0604142451654197</v>
-          </cell>
-          <cell r="K65">
-            <v>3.5148072283597433E-2</v>
-          </cell>
-          <cell r="L65">
-            <v>-4.8287106703146376</v>
-          </cell>
-          <cell r="M65">
-            <v>1.5809556619080001</v>
-          </cell>
-          <cell r="N65">
-            <v>2.6471935872341001</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66">
-            <v>1.0567543625005098</v>
-          </cell>
-          <cell r="C66">
-            <v>0.25590227672743993</v>
-          </cell>
-          <cell r="D66">
-            <v>1.3117876911949458</v>
-          </cell>
-          <cell r="E66">
-            <v>4.1471088538508187</v>
-          </cell>
-          <cell r="F66">
-            <v>4.385435870224379</v>
-          </cell>
-          <cell r="G66">
-            <v>3.8409998254222022</v>
-          </cell>
-          <cell r="H66">
-            <v>-2.5254743134367139</v>
-          </cell>
-          <cell r="I66">
-            <v>3.2477042363337083</v>
-          </cell>
-          <cell r="J66">
-            <v>2.3402808309750012</v>
-          </cell>
-          <cell r="K66">
-            <v>-0.27565046833390461</v>
-          </cell>
-          <cell r="L66">
-            <v>-4.8815968451633838</v>
-          </cell>
-          <cell r="M66">
-            <v>1.15277497099739</v>
-          </cell>
-          <cell r="N66">
-            <v>2.1631291707428999</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67">
-            <v>0.79954904624098011</v>
-          </cell>
-          <cell r="C67">
-            <v>0.11086748243834388</v>
-          </cell>
-          <cell r="D67">
-            <v>1.151800647608358</v>
-          </cell>
-          <cell r="E67">
-            <v>3.3858141297756221</v>
-          </cell>
-          <cell r="F67">
-            <v>3.5257481807155848</v>
-          </cell>
-          <cell r="G67">
-            <v>2.919757382803168</v>
-          </cell>
-          <cell r="H67">
-            <v>-3.083171619163128</v>
-          </cell>
-          <cell r="I67">
-            <v>2.5143052066187299</v>
-          </cell>
-          <cell r="J67">
-            <v>1.6635765152280841</v>
-          </cell>
-          <cell r="K67">
-            <v>-0.59188296760882753</v>
-          </cell>
-          <cell r="L67">
-            <v>-4.9071584963402772</v>
-          </cell>
-          <cell r="M67">
-            <v>0.71654600540699998</v>
-          </cell>
-          <cell r="N67">
-            <v>1.6897109371311001</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68">
-            <v>0.54213398048806849</v>
-          </cell>
-          <cell r="C68">
-            <v>-9.8071086279746478E-2</v>
-          </cell>
-          <cell r="D68">
-            <v>0.9969426584400809</v>
-          </cell>
-          <cell r="E68">
-            <v>2.4343283808368712</v>
-          </cell>
-          <cell r="F68">
-            <v>2.6991108247422679</v>
-          </cell>
-          <cell r="G68">
-            <v>2.0131013745704465</v>
-          </cell>
-          <cell r="H68">
-            <v>-3.5599215975049803</v>
-          </cell>
-          <cell r="I68">
-            <v>1.7597894828034306</v>
-          </cell>
-          <cell r="J68">
-            <v>0.79241512111717516</v>
-          </cell>
-          <cell r="K68">
-            <v>-0.88193441512642734</v>
-          </cell>
-          <cell r="L68">
-            <v>-4.8106412272413168</v>
-          </cell>
-          <cell r="M68">
-            <v>0.32119478842283999</v>
-          </cell>
-          <cell r="N68">
-            <v>1.1670372624759999</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69">
-            <v>0.30366628563732007</v>
-          </cell>
-          <cell r="C69">
-            <v>-0.29970369511706296</v>
-          </cell>
-          <cell r="D69">
-            <v>0.78061492478156791</v>
-          </cell>
-          <cell r="E69">
-            <v>1.6622695573074593</v>
-          </cell>
-          <cell r="F69">
-            <v>1.8124370830806547</v>
-          </cell>
-          <cell r="G69">
-            <v>1.0729654795376442</v>
-          </cell>
-          <cell r="H69">
-            <v>-4.0894091657281457</v>
-          </cell>
-          <cell r="I69">
-            <v>1.0406306852637961</v>
-          </cell>
-          <cell r="J69">
-            <v>2.2019763661478328E-2</v>
-          </cell>
-          <cell r="K69">
-            <v>-1.1853956696416801</v>
-          </cell>
-          <cell r="L69">
-            <v>-4.6462533670864659</v>
-          </cell>
-          <cell r="M69">
-            <v>-0.13458711735863901</v>
-          </cell>
-          <cell r="N69">
-            <v>0.53423623783298002</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70">
-            <v>6.4628771329550805E-2</v>
-          </cell>
-          <cell r="C70">
-            <v>-0.50502379955261734</v>
-          </cell>
-          <cell r="D70">
-            <v>0.5811045714754044</v>
-          </cell>
-          <cell r="E70">
-            <v>0.87171467556094617</v>
-          </cell>
-          <cell r="F70">
-            <v>0.86042070952092176</v>
-          </cell>
-          <cell r="G70">
-            <v>0.2443411525809949</v>
-          </cell>
-          <cell r="H70">
-            <v>-4.5984297842848463</v>
-          </cell>
-          <cell r="I70">
-            <v>0.25166226284328164</v>
-          </cell>
-          <cell r="J70">
-            <v>-0.89568709571457428</v>
-          </cell>
-          <cell r="K70">
-            <v>-1.4894954863949168</v>
-          </cell>
-          <cell r="L70">
-            <v>-4.5669241048133475</v>
-          </cell>
-          <cell r="M70">
-            <v>-0.52402378829903995</v>
-          </cell>
-          <cell r="N70">
-            <v>3.6971902189410003E-2</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71">
-            <v>-0.21030736877052703</v>
-          </cell>
-          <cell r="C71">
-            <v>-0.64332236076900762</v>
-          </cell>
-          <cell r="D71">
-            <v>0.41669865023611669</v>
-          </cell>
-          <cell r="E71">
-            <v>-2.0194057004244981E-3</v>
-          </cell>
-          <cell r="F71">
-            <v>6.8971346270466929E-2</v>
-          </cell>
-          <cell r="G71">
-            <v>-0.49273894187478173</v>
-          </cell>
-          <cell r="H71">
-            <v>-4.8517759681192052</v>
-          </cell>
-          <cell r="I71">
-            <v>-0.59662241185133835</v>
-          </cell>
-          <cell r="J71">
-            <v>-1.6994149442423014</v>
-          </cell>
-          <cell r="K71">
-            <v>-1.7323551246473492</v>
-          </cell>
-          <cell r="L71">
-            <v>-4.7136832400186162</v>
-          </cell>
-          <cell r="M71">
-            <v>-0.84506884137899996</v>
-          </cell>
-          <cell r="N71">
-            <v>-0.45938279124610998</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72">
-            <v>-0.46136003322418817</v>
-          </cell>
-          <cell r="C72">
-            <v>-0.80460223341517645</v>
-          </cell>
-          <cell r="D72">
-            <v>0.15770112924372043</v>
-          </cell>
-          <cell r="E72">
-            <v>-0.89039872650090979</v>
-          </cell>
-          <cell r="F72">
-            <v>-0.66585278956943594</v>
-          </cell>
-          <cell r="G72">
-            <v>-1.1848307973611187</v>
-          </cell>
-          <cell r="H72">
-            <v>-5.0987871437234675</v>
-          </cell>
-          <cell r="I72">
-            <v>-1.3894134973577059</v>
-          </cell>
-          <cell r="J72">
-            <v>-2.4344984965635734</v>
-          </cell>
-          <cell r="K72">
-            <v>-1.9145719490732196</v>
-          </cell>
-          <cell r="L72">
-            <v>-4.74894068991778</v>
-          </cell>
-          <cell r="M72">
-            <v>-1.2620193815736001</v>
-          </cell>
-          <cell r="N72">
-            <v>-0.8613300996669</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73">
-            <v>-0.68874596317459402</v>
-          </cell>
-          <cell r="C73">
-            <v>-0.92042629539301501</v>
-          </cell>
-          <cell r="D73">
-            <v>6.8449861496705511E-4</v>
-          </cell>
-          <cell r="E73">
-            <v>-1.8903380836870831</v>
-          </cell>
-          <cell r="F73">
-            <v>-1.4979783201940571</v>
-          </cell>
-          <cell r="G73">
-            <v>-1.846561047099252</v>
-          </cell>
-          <cell r="H73">
-            <v>-5.1547193104045723</v>
-          </cell>
-          <cell r="I73">
-            <v>-2.063252620635883</v>
-          </cell>
-          <cell r="J73">
-            <v>-3.2075364488578932</v>
-          </cell>
-          <cell r="K73">
-            <v>-2.0510800765285948</v>
-          </cell>
-          <cell r="L73">
-            <v>-4.6083516084448641</v>
-          </cell>
-          <cell r="M73">
-            <v>-1.5639232666553999</v>
-          </cell>
-          <cell r="N73">
-            <v>-1.1718213066812999</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74">
-            <v>-0.86336241641500866</v>
-          </cell>
-          <cell r="C74">
-            <v>-0.96525295989292503</v>
-          </cell>
-          <cell r="D74">
-            <v>-0.22064554263632891</v>
-          </cell>
-          <cell r="E74">
-            <v>-2.7676121892055798</v>
-          </cell>
-          <cell r="F74">
-            <v>-2.2181875379017586</v>
-          </cell>
-          <cell r="G74">
-            <v>-2.4384601778855872</v>
-          </cell>
-          <cell r="H74">
-            <v>-5.1815212683011334</v>
-          </cell>
-          <cell r="I74">
-            <v>-2.5319349389240231</v>
-          </cell>
-          <cell r="J74">
-            <v>-3.9065080478067506</v>
-          </cell>
-          <cell r="K74">
-            <v>-2.1298704171830098</v>
-          </cell>
-          <cell r="L74">
-            <v>-4.3232510541977529</v>
-          </cell>
-          <cell r="M74">
-            <v>-1.8180990111941999</v>
-          </cell>
-          <cell r="N74">
-            <v>-1.5682905475825</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75">
-            <v>-0.99672813595698706</v>
-          </cell>
-          <cell r="C75">
-            <v>-1.0116524898138817</v>
-          </cell>
-          <cell r="D75">
-            <v>-0.34975962405115363</v>
-          </cell>
-          <cell r="E75">
-            <v>-3.2556352334748331</v>
-          </cell>
-          <cell r="F75">
-            <v>-2.9457496967859309</v>
-          </cell>
-          <cell r="G75">
-            <v>-2.8947743811676498</v>
-          </cell>
-          <cell r="H75">
-            <v>-5.2613315429264471</v>
-          </cell>
-          <cell r="I75">
-            <v>-2.9718660660140341</v>
-          </cell>
-          <cell r="J75">
-            <v>-4.286367895525907</v>
-          </cell>
-          <cell r="K75">
-            <v>-2.1914607749756114</v>
-          </cell>
-          <cell r="L75">
-            <v>-4.044408697307742</v>
-          </cell>
-          <cell r="M75">
-            <v>-2.0383971344064</v>
-          </cell>
-          <cell r="N75">
-            <v>-1.9522943211882</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76">
-            <v>-1.0684100253202402</v>
-          </cell>
-          <cell r="C76">
-            <v>-1.0016036274016216</v>
-          </cell>
-          <cell r="D76">
-            <v>-0.47903152252500331</v>
-          </cell>
-          <cell r="E76">
-            <v>-3.6272240751970894</v>
-          </cell>
-          <cell r="F76">
-            <v>-3.5614258641600971</v>
-          </cell>
-          <cell r="G76">
-            <v>-3.3091669423158199</v>
-          </cell>
-          <cell r="H76">
-            <v>-5.327876202027201</v>
-          </cell>
-          <cell r="I76">
-            <v>-3.3340444425192759</v>
-          </cell>
-          <cell r="J76">
-            <v>-4.8062010435617539</v>
-          </cell>
-          <cell r="K76">
-            <v>-2.2213290086877424</v>
-          </cell>
-          <cell r="L76">
-            <v>-3.8471873369342937</v>
-          </cell>
-          <cell r="M76">
-            <v>-2.222010098613</v>
-          </cell>
-          <cell r="N76">
-            <v>-2.1805134440523002</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77">
-            <v>-1.1433255527064723</v>
-          </cell>
-          <cell r="C77">
-            <v>-0.97914660444552915</v>
-          </cell>
-          <cell r="D77">
-            <v>-0.58897083126829086</v>
-          </cell>
-          <cell r="E77">
-            <v>-3.8797255912674355</v>
-          </cell>
-          <cell r="F77">
-            <v>-3.9822111885991505</v>
-          </cell>
-          <cell r="G77">
-            <v>-3.5547243967877682</v>
-          </cell>
-          <cell r="H77">
-            <v>-5.1255349562505392</v>
-          </cell>
-          <cell r="I77">
-            <v>-3.7211838343584858</v>
-          </cell>
-          <cell r="J77">
-            <v>-5.2003793334344044</v>
-          </cell>
-          <cell r="K77">
-            <v>-2.2052619588288032</v>
-          </cell>
-          <cell r="L77">
-            <v>-3.7757028572637399</v>
-          </cell>
-          <cell r="M77">
-            <v>-2.2749165864305998</v>
-          </cell>
-          <cell r="N77">
-            <v>-2.3403409490519</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78">
-            <v>-1.1967767152699547</v>
-          </cell>
-          <cell r="C78">
-            <v>-0.95135931534032137</v>
-          </cell>
-          <cell r="D78">
-            <v>-0.67318595939050452</v>
-          </cell>
-          <cell r="E78">
-            <v>-3.920280473013948</v>
-          </cell>
-          <cell r="F78">
-            <v>-4.0790122801697999</v>
-          </cell>
-          <cell r="G78">
-            <v>-3.6607344671701854</v>
-          </cell>
-          <cell r="H78">
-            <v>-4.8919518322793012</v>
-          </cell>
-          <cell r="I78">
-            <v>-3.9485402408386037</v>
-          </cell>
-          <cell r="J78">
-            <v>-5.3560397505222017</v>
-          </cell>
-          <cell r="K78">
-            <v>-2.0987662565586525</v>
-          </cell>
-          <cell r="L78">
-            <v>-3.7204368045468006</v>
-          </cell>
-          <cell r="M78">
-            <v>-2.3622622031106002</v>
-          </cell>
-          <cell r="N78">
-            <v>-2.3861599639759001</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79">
-            <v>-1.2193247858085066</v>
-          </cell>
-          <cell r="C79">
-            <v>-0.92601870577896872</v>
-          </cell>
-          <cell r="D79">
-            <v>-0.71004610623902842</v>
-          </cell>
-          <cell r="E79">
-            <v>-4.0032095209217715</v>
-          </cell>
-          <cell r="F79">
-            <v>-4.084091115827774</v>
-          </cell>
-          <cell r="G79">
-            <v>-3.7018521326056191</v>
-          </cell>
-          <cell r="H79">
-            <v>-4.5850558780213104</v>
-          </cell>
-          <cell r="I79">
-            <v>-3.9162154552542665</v>
-          </cell>
-          <cell r="J79">
-            <v>-5.4681657865036044</v>
-          </cell>
-          <cell r="K79">
-            <v>-1.9817239779708389</v>
-          </cell>
-          <cell r="L79">
-            <v>-3.6250654025695628</v>
-          </cell>
-          <cell r="M79">
-            <v>-2.3677524990162002</v>
-          </cell>
-          <cell r="N79">
-            <v>-2.4770568038766001</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80">
-            <v>-1.2245510440186009</v>
-          </cell>
-          <cell r="C80">
-            <v>-0.85873501832296284</v>
-          </cell>
-          <cell r="D80">
-            <v>-0.70826080075880804</v>
-          </cell>
-          <cell r="E80">
-            <v>-3.9158080654942387</v>
-          </cell>
-          <cell r="F80">
-            <v>-4.0420959672528802</v>
-          </cell>
-          <cell r="G80">
-            <v>-3.7321735395189002</v>
-          </cell>
-          <cell r="H80">
-            <v>-4.2700381183401177</v>
-          </cell>
-          <cell r="I80">
-            <v>-3.8152343411591438</v>
-          </cell>
-          <cell r="J80">
-            <v>-5.31355819604474</v>
-          </cell>
-          <cell r="K80">
-            <v>-1.8628896053602975</v>
-          </cell>
-          <cell r="L80">
-            <v>-3.4993725936790443</v>
-          </cell>
-          <cell r="M80">
-            <v>-2.3666918736708</v>
-          </cell>
-          <cell r="N80">
-            <v>-2.5696381663848</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81">
-            <v>-1.1692296151391344</v>
-          </cell>
-          <cell r="C81">
-            <v>-0.80102833365290282</v>
-          </cell>
-          <cell r="D81">
-            <v>-0.71819341191119368</v>
-          </cell>
-          <cell r="E81">
-            <v>-3.9067116434202553</v>
-          </cell>
-          <cell r="F81">
-            <v>-4.163078380836871</v>
-          </cell>
-          <cell r="G81">
-            <v>-3.6380508388922577</v>
-          </cell>
-          <cell r="H81">
-            <v>-3.986045655375551</v>
-          </cell>
-          <cell r="I81">
-            <v>-3.7911937971064713</v>
-          </cell>
-          <cell r="J81">
-            <v>-5.177638278249443</v>
-          </cell>
-          <cell r="K81">
-            <v>-1.7018483286972346</v>
-          </cell>
-          <cell r="L81">
-            <v>-3.3074839226028456</v>
-          </cell>
-          <cell r="M81">
-            <v>-2.3615759161223999</v>
-          </cell>
-          <cell r="N81">
-            <v>-2.6804123730540002</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82">
-            <v>-1.0912552409744207</v>
-          </cell>
-          <cell r="C82">
-            <v>-0.66787653761983556</v>
-          </cell>
-          <cell r="D82">
-            <v>-0.68344406822712744</v>
-          </cell>
-          <cell r="E82">
-            <v>-3.9295285021224986</v>
-          </cell>
-          <cell r="F82">
-            <v>-4.2063621892055787</v>
-          </cell>
-          <cell r="G82">
-            <v>-3.4301654354337794</v>
-          </cell>
-          <cell r="H82">
-            <v>-3.7945876288659783</v>
-          </cell>
-          <cell r="I82">
-            <v>-3.6445681365329636</v>
-          </cell>
-          <cell r="J82">
-            <v>-4.9886032570244581</v>
-          </cell>
-          <cell r="K82">
-            <v>-1.5409100459435232</v>
-          </cell>
-          <cell r="L82">
-            <v>-3.1560531752859378</v>
-          </cell>
-          <cell r="M82">
-            <v>-2.3802304442561999</v>
-          </cell>
-          <cell r="N82">
-            <v>-2.621790986313</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83">
-            <v>-1.0309173033782333</v>
-          </cell>
-          <cell r="C83">
-            <v>-0.57886109292966259</v>
-          </cell>
-          <cell r="D83">
-            <v>-0.64753082373275173</v>
-          </cell>
-          <cell r="E83">
-            <v>-3.9237674348089753</v>
-          </cell>
-          <cell r="F83">
-            <v>-4.2831511522134624</v>
-          </cell>
-          <cell r="G83">
-            <v>-3.2192364059025667</v>
-          </cell>
-          <cell r="H83">
-            <v>-3.5104868751624352</v>
-          </cell>
-          <cell r="I83">
-            <v>-3.6014684224205147</v>
-          </cell>
-          <cell r="J83">
-            <v>-4.7798803778384196</v>
-          </cell>
-          <cell r="K83">
-            <v>-1.4084186809528834</v>
-          </cell>
-          <cell r="L83">
-            <v>-3.0045342843442819</v>
-          </cell>
-          <cell r="M83">
-            <v>-2.2268764972566002</v>
-          </cell>
-          <cell r="N83">
-            <v>-2.5060305927256001</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84">
-            <v>-0.95890331065045475</v>
-          </cell>
-          <cell r="C84">
-            <v>-0.49410112301754838</v>
-          </cell>
-          <cell r="D84">
-            <v>-0.61736803832660114</v>
-          </cell>
-          <cell r="E84">
-            <v>-3.8606231049120678</v>
-          </cell>
-          <cell r="F84">
-            <v>-4.2076508489993936</v>
-          </cell>
-          <cell r="G84">
-            <v>-2.9261868993145521</v>
-          </cell>
-          <cell r="H84">
-            <v>-3.2205384215541879</v>
-          </cell>
-          <cell r="I84">
-            <v>-3.4591743914060471</v>
-          </cell>
-          <cell r="J84">
-            <v>-4.4756134820766791</v>
-          </cell>
-          <cell r="K84">
-            <v>-1.2417127392754503</v>
-          </cell>
-          <cell r="L84">
-            <v>-2.8942666097846472</v>
-          </cell>
-          <cell r="M84">
-            <v>-2.0549928015756</v>
-          </cell>
-          <cell r="N84">
-            <v>-2.2966781230655</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85">
-            <v>-0.86296039655269352</v>
-          </cell>
-          <cell r="C85">
-            <v>-0.40893046046771853</v>
-          </cell>
-          <cell r="D85">
-            <v>-0.49636180831918558</v>
-          </cell>
-          <cell r="E85">
-            <v>-3.8992828987265016</v>
-          </cell>
-          <cell r="F85">
-            <v>-4.0548309581564581</v>
-          </cell>
-          <cell r="G85">
-            <v>-2.6235470992520717</v>
-          </cell>
-          <cell r="H85">
-            <v>-2.8417915619856178</v>
-          </cell>
-          <cell r="I85">
-            <v>-3.2155202287100404</v>
-          </cell>
-          <cell r="J85">
-            <v>-4.2663115482447269</v>
-          </cell>
-          <cell r="K85">
-            <v>-1.0935663000632796</v>
-          </cell>
-          <cell r="L85">
-            <v>-2.8113675307092389</v>
-          </cell>
-          <cell r="M85">
-            <v>-1.9469961855233999</v>
-          </cell>
-          <cell r="N85">
-            <v>-2.0824068473914998</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86">
-            <v>-0.78192717560949387</v>
-          </cell>
-          <cell r="C86">
-            <v>-0.32722883998542585</v>
-          </cell>
-          <cell r="D86">
-            <v>-0.49373809971289512</v>
-          </cell>
-          <cell r="E86">
-            <v>-3.6981003638568835</v>
-          </cell>
-          <cell r="F86">
-            <v>-3.8732057307459065</v>
-          </cell>
-          <cell r="G86">
-            <v>-2.4094021629270266</v>
-          </cell>
-          <cell r="H86">
-            <v>-2.5381443298969066</v>
-          </cell>
-          <cell r="I86">
-            <v>-2.947392359005458</v>
-          </cell>
-          <cell r="J86">
-            <v>-4.0264250008422602</v>
-          </cell>
-          <cell r="K86">
-            <v>-0.96173409609249361</v>
-          </cell>
-          <cell r="L86">
-            <v>-2.5662401102853032</v>
-          </cell>
-          <cell r="M86">
-            <v>-1.8703816017498001</v>
-          </cell>
-          <cell r="N86">
-            <v>-1.8710329506023999</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87">
-            <v>-0.67028800775698882</v>
-          </cell>
-          <cell r="C87">
-            <v>-0.25090991449961664</v>
-          </cell>
-          <cell r="D87">
-            <v>-0.44342404858248857</v>
-          </cell>
-          <cell r="E87">
-            <v>-3.5909141904184363</v>
-          </cell>
-          <cell r="F87">
-            <v>-3.5667321103699208</v>
-          </cell>
-          <cell r="G87">
-            <v>-2.1464443556241615</v>
-          </cell>
-          <cell r="H87">
-            <v>-2.2911872996621323</v>
-          </cell>
-          <cell r="I87">
-            <v>-2.6230074504028416</v>
-          </cell>
-          <cell r="J87">
-            <v>-3.8046997127888948</v>
-          </cell>
-          <cell r="K87">
-            <v>-0.8067900588630792</v>
-          </cell>
-          <cell r="L87">
-            <v>-2.3492745779683246</v>
-          </cell>
-          <cell r="M87">
-            <v>-1.79264400290459</v>
-          </cell>
-          <cell r="N87">
-            <v>-1.7186173450758</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88">
-            <v>-0.59369448442370565</v>
-          </cell>
-          <cell r="C88">
-            <v>-0.15977110149102702</v>
-          </cell>
-          <cell r="D88">
-            <v>-0.38664936159824642</v>
-          </cell>
-          <cell r="E88">
-            <v>-3.420507883565798</v>
-          </cell>
-          <cell r="F88">
-            <v>-3.3452342328684046</v>
-          </cell>
-          <cell r="G88">
-            <v>-1.7414123803223256</v>
-          </cell>
-          <cell r="H88">
-            <v>-2.0948020445291511</v>
-          </cell>
-          <cell r="I88">
-            <v>-2.2685718617343844</v>
-          </cell>
-          <cell r="J88">
-            <v>-3.471848574051613</v>
-          </cell>
-          <cell r="K88">
-            <v>-0.65388530103883791</v>
-          </cell>
-          <cell r="L88">
-            <v>-2.0812738869223066</v>
-          </cell>
-          <cell r="M88">
-            <v>-1.7212701561318</v>
-          </cell>
-          <cell r="N88">
-            <v>-1.5818341093468</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89">
-            <v>-0.51863912404188983</v>
-          </cell>
-          <cell r="C89">
-            <v>-0.10763935092446419</v>
-          </cell>
-          <cell r="D89">
-            <v>-0.34479825025805527</v>
-          </cell>
-          <cell r="E89">
-            <v>-2.9833489993935718</v>
-          </cell>
-          <cell r="F89">
-            <v>-3.1565592783505152</v>
-          </cell>
-          <cell r="G89">
-            <v>-1.4040867284120768</v>
-          </cell>
-          <cell r="H89">
-            <v>-1.8644676427271936</v>
-          </cell>
-          <cell r="I89">
-            <v>-1.9369314736203758</v>
-          </cell>
-          <cell r="J89">
-            <v>-3.0431375707499488</v>
-          </cell>
-          <cell r="K89">
-            <v>-0.52744997791810599</v>
-          </cell>
-          <cell r="L89">
-            <v>-1.8215146247902183</v>
-          </cell>
-          <cell r="M89">
-            <v>-1.5900021722069999</v>
-          </cell>
-          <cell r="N89">
-            <v>-1.496529884503</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90">
-            <v>-0.43785061084096932</v>
-          </cell>
-          <cell r="C90">
-            <v>-6.5879773995600299E-2</v>
-          </cell>
-          <cell r="D90">
-            <v>-0.29497737743710201</v>
-          </cell>
-          <cell r="E90">
-            <v>-2.6793010915706494</v>
-          </cell>
-          <cell r="F90">
-            <v>-2.9494640691328078</v>
-          </cell>
-          <cell r="G90">
-            <v>-1.0496478582060753</v>
-          </cell>
-          <cell r="H90">
-            <v>-1.5884345490773626</v>
-          </cell>
-          <cell r="I90">
-            <v>-1.5863943515550547</v>
-          </cell>
-          <cell r="J90">
-            <v>-2.4936147117781817</v>
-          </cell>
-          <cell r="K90">
-            <v>-0.40253896465578615</v>
-          </cell>
-          <cell r="L90">
-            <v>-1.4486670921065621</v>
-          </cell>
-          <cell r="M90">
-            <v>-1.3738217709239999</v>
-          </cell>
-          <cell r="N90">
-            <v>-1.3365676176948</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91">
-            <v>-0.35005296873620417</v>
-          </cell>
-          <cell r="C91">
-            <v>2.6622057972450763E-3</v>
-          </cell>
-          <cell r="D91">
-            <v>-0.29877485041989088</v>
-          </cell>
-          <cell r="E91">
-            <v>-2.4779669496664649</v>
-          </cell>
-          <cell r="F91">
-            <v>-2.7699613402061853</v>
-          </cell>
-          <cell r="G91">
-            <v>-0.71169051031846653</v>
-          </cell>
-          <cell r="H91">
-            <v>-1.1847266741748244</v>
-          </cell>
-          <cell r="I91">
-            <v>-1.2570822143290303</v>
-          </cell>
-          <cell r="J91">
-            <v>-2.006629754565056</v>
-          </cell>
-          <cell r="K91">
-            <v>-0.21632597654705096</v>
-          </cell>
-          <cell r="L91">
-            <v>-1.0882478105123614</v>
-          </cell>
-          <cell r="M91">
-            <v>-1.18802516630039</v>
-          </cell>
-          <cell r="N91">
-            <v>-1.1173775360069</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92">
-            <v>-0.27482281710990353</v>
-          </cell>
-          <cell r="C92">
-            <v>8.7326929969970268E-2</v>
-          </cell>
-          <cell r="D92">
-            <v>-0.23628915861218164</v>
-          </cell>
-          <cell r="E92">
-            <v>-2.1499651303820499</v>
-          </cell>
-          <cell r="F92">
-            <v>-2.530346422073984</v>
-          </cell>
-          <cell r="G92">
-            <v>-0.46265872797103841</v>
-          </cell>
-          <cell r="H92">
-            <v>-0.88459889110283263</v>
-          </cell>
-          <cell r="I92">
-            <v>-0.8929546045222212</v>
-          </cell>
-          <cell r="J92">
-            <v>-1.6711465492554407</v>
-          </cell>
-          <cell r="K92">
-            <v>-3.6861149379070333E-2</v>
-          </cell>
-          <cell r="L92">
-            <v>-0.61976444497722372</v>
-          </cell>
-          <cell r="M92">
-            <v>-1.0153304041787901</v>
-          </cell>
-          <cell r="N92">
-            <v>-0.92850886125400001</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="B93">
-            <v>-0.20307101124885185</v>
-          </cell>
-          <cell r="C93">
-            <v>0.16903641477936793</v>
-          </cell>
-          <cell r="D93">
-            <v>-0.21869255653089453</v>
-          </cell>
-          <cell r="E93">
-            <v>-1.9218723468768955</v>
-          </cell>
-          <cell r="F93">
-            <v>-2.111380382049727</v>
-          </cell>
-          <cell r="G93">
-            <v>-0.13159260892735725</v>
-          </cell>
-          <cell r="H93">
-            <v>-0.62784154899073008</v>
-          </cell>
-          <cell r="I93">
-            <v>-0.52547539634410456</v>
-          </cell>
-          <cell r="J93">
-            <v>-1.2517004202883901</v>
-          </cell>
-          <cell r="K93">
-            <v>0.10292836402826483</v>
-          </cell>
-          <cell r="L93">
-            <v>-0.28695615383530537</v>
-          </cell>
-          <cell r="M93">
-            <v>-0.79409643507359995</v>
-          </cell>
-          <cell r="N93">
-            <v>-0.70022235748559902</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94">
-            <v>-0.17354877005535274</v>
-          </cell>
-          <cell r="C94">
-            <v>0.24296108956869417</v>
-          </cell>
-          <cell r="D94">
-            <v>-0.2049821995280981</v>
-          </cell>
-          <cell r="E94">
-            <v>-1.7106079442086115</v>
-          </cell>
-          <cell r="F94">
-            <v>-1.9163379320800487</v>
-          </cell>
-          <cell r="G94">
-            <v>0.12063785214179391</v>
-          </cell>
-          <cell r="H94">
-            <v>-0.4676254006757341</v>
-          </cell>
-          <cell r="I94">
-            <v>-0.22089902971497874</v>
-          </cell>
-          <cell r="J94">
-            <v>-0.95838292146755588</v>
-          </cell>
-          <cell r="K94">
-            <v>0.26053582375352657</v>
-          </cell>
-          <cell r="L94">
-            <v>3.5929809468740748E-2</v>
-          </cell>
-          <cell r="M94">
-            <v>-0.64797969631319996</v>
-          </cell>
-          <cell r="N94">
-            <v>-0.50793073279426004</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95">
-            <v>-0.13404420088932012</v>
-          </cell>
-          <cell r="C95">
-            <v>0.29357240356157516</v>
-          </cell>
-          <cell r="D95">
-            <v>-0.20120445367768724</v>
-          </cell>
-          <cell r="E95">
-            <v>-1.3670664038811402</v>
-          </cell>
-          <cell r="F95">
-            <v>-1.6798309581564586</v>
-          </cell>
-          <cell r="G95">
-            <v>0.40280495984710657</v>
-          </cell>
-          <cell r="H95">
-            <v>-0.26747162782638823</v>
-          </cell>
-          <cell r="I95">
-            <v>0.13849844061335875</v>
-          </cell>
-          <cell r="J95">
-            <v>-0.63890268091772773</v>
-          </cell>
-          <cell r="K95">
-            <v>0.3537865092809872</v>
-          </cell>
-          <cell r="L95">
-            <v>0.26778015569689878</v>
-          </cell>
-          <cell r="M95">
-            <v>-0.50876950024313905</v>
-          </cell>
-          <cell r="N95">
-            <v>-0.29314062415714998</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="B96">
-            <v>-9.9332407647064358E-2</v>
-          </cell>
-          <cell r="C96">
-            <v>0.34946155485620051</v>
-          </cell>
-          <cell r="D96">
-            <v>-0.18976271689837509</v>
-          </cell>
-          <cell r="E96">
-            <v>-1.2336522134627048</v>
-          </cell>
-          <cell r="F96">
-            <v>-1.5417169496664647</v>
-          </cell>
-          <cell r="G96">
-            <v>0.68866461767462372</v>
-          </cell>
-          <cell r="H96">
-            <v>-8.030191458026506E-2</v>
-          </cell>
-          <cell r="I96">
-            <v>0.4935458719570302</v>
-          </cell>
-          <cell r="J96">
-            <v>-0.32224927986658575</v>
-          </cell>
-          <cell r="K96">
-            <v>0.43498690741424317</v>
-          </cell>
-          <cell r="L96">
-            <v>0.4192329389199938</v>
-          </cell>
-          <cell r="M96">
-            <v>-0.28334918050991997</v>
-          </cell>
-          <cell r="N96">
-            <v>-2.0896166041516E-2</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="B97">
-            <v>-6.0346968477152374E-2</v>
-          </cell>
-          <cell r="C97">
-            <v>0.40998192100169351</v>
-          </cell>
-          <cell r="D97">
-            <v>-0.18418980200155483</v>
-          </cell>
-          <cell r="E97">
-            <v>-1.0771179502728927</v>
-          </cell>
-          <cell r="F97">
-            <v>-1.3537242268041239</v>
-          </cell>
-          <cell r="G97">
-            <v>0.88293984416634497</v>
-          </cell>
-          <cell r="H97">
-            <v>0.16765139045308841</v>
-          </cell>
-          <cell r="I97">
-            <v>0.77558910162002959</v>
-          </cell>
-          <cell r="J97">
-            <v>8.8916367663904025E-2</v>
-          </cell>
-          <cell r="K97">
-            <v>0.53033866869248825</v>
-          </cell>
-          <cell r="L97">
-            <v>0.44123799483830933</v>
-          </cell>
-          <cell r="M97">
-            <v>-2.3844105559116001E-2</v>
-          </cell>
-          <cell r="N97">
-            <v>0.20599690062595999</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="B98">
-            <v>5.8120419341156082E-3</v>
-          </cell>
-          <cell r="C98">
-            <v>0.46800317875596043</v>
-          </cell>
-          <cell r="D98">
-            <v>-0.19281055885079368</v>
-          </cell>
-          <cell r="E98">
-            <v>-1.0041949666464527</v>
-          </cell>
-          <cell r="F98">
-            <v>-1.2353191328077622</v>
-          </cell>
-          <cell r="G98">
-            <v>1.0384519084109742</v>
-          </cell>
-          <cell r="H98">
-            <v>0.35340790955557477</v>
-          </cell>
-          <cell r="I98">
-            <v>0.98366975656241884</v>
-          </cell>
-          <cell r="J98">
-            <v>0.32492324893875069</v>
-          </cell>
-          <cell r="K98">
-            <v>0.59940638430405779</v>
-          </cell>
-          <cell r="L98">
-            <v>0.51944783307712916</v>
-          </cell>
-          <cell r="M98">
-            <v>0.257182929341639</v>
-          </cell>
-          <cell r="N98">
-            <v>0.38934034122625999</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="B99">
-            <v>7.8841047418617971E-2</v>
-          </cell>
-          <cell r="C99">
-            <v>0.48340852174101734</v>
-          </cell>
-          <cell r="D99">
-            <v>-0.1820691352709049</v>
-          </cell>
-          <cell r="E99">
-            <v>-0.86223013947847182</v>
-          </cell>
-          <cell r="F99">
-            <v>-1.0226902668283808</v>
-          </cell>
-          <cell r="G99">
-            <v>1.2720645662201149</v>
-          </cell>
-          <cell r="H99">
-            <v>0.53502230789222893</v>
-          </cell>
-          <cell r="I99">
-            <v>1.1708502988824394</v>
-          </cell>
-          <cell r="J99">
-            <v>0.59274655093996353</v>
-          </cell>
-          <cell r="K99">
-            <v>0.67483912351359188</v>
-          </cell>
-          <cell r="L99">
-            <v>0.55285426685658678</v>
-          </cell>
-          <cell r="M99">
-            <v>0.49879962199638</v>
-          </cell>
-          <cell r="N99">
-            <v>0.52688498117384996</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="B100">
-            <v>0.13982746053184428</v>
-          </cell>
-          <cell r="C100">
-            <v>0.47163824550683031</v>
-          </cell>
-          <cell r="D100">
-            <v>-0.18011614916547053</v>
-          </cell>
-          <cell r="E100">
-            <v>-0.63286385688295943</v>
-          </cell>
-          <cell r="F100">
-            <v>-0.96727789569436018</v>
-          </cell>
-          <cell r="G100">
-            <v>1.4473314864840028</v>
-          </cell>
-          <cell r="H100">
-            <v>0.5115502902191803</v>
-          </cell>
-          <cell r="I100">
-            <v>1.3358853850818677</v>
-          </cell>
-          <cell r="J100">
-            <v>0.84142420069402324</v>
-          </cell>
-          <cell r="K100">
-            <v>0.76127161224193851</v>
-          </cell>
-          <cell r="L100">
-            <v>0.68515784760319864</v>
-          </cell>
-          <cell r="M100">
-            <v>0.73158192942120004</v>
-          </cell>
-          <cell r="N100">
-            <v>0.74577184879239999</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="B101">
-            <v>0.22497526737021825</v>
-          </cell>
-          <cell r="C101">
-            <v>0.43921100340952979</v>
-          </cell>
-          <cell r="D101">
-            <v>-0.22745140330678182</v>
-          </cell>
-          <cell r="E101">
-            <v>-0.34746361431170408</v>
-          </cell>
-          <cell r="F101">
-            <v>-0.79108020012128566</v>
-          </cell>
-          <cell r="G101">
-            <v>1.5888313854126466</v>
-          </cell>
-          <cell r="H101">
-            <v>0.61134562072251575</v>
-          </cell>
-          <cell r="I101">
-            <v>1.6400199254959715</v>
-          </cell>
-          <cell r="J101">
-            <v>1.0898386437908494</v>
-          </cell>
-          <cell r="K101">
-            <v>0.82889741312257759</v>
-          </cell>
-          <cell r="L101">
-            <v>0.71323159208540765</v>
-          </cell>
-          <cell r="M101">
-            <v>0.89872400591099899</v>
-          </cell>
-          <cell r="N101">
-            <v>0.96873526112109998</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="B102">
-            <v>0.2904870258031586</v>
-          </cell>
-          <cell r="C102">
-            <v>0.44264509291215459</v>
-          </cell>
-          <cell r="D102">
-            <v>-0.27229117520225715</v>
-          </cell>
-          <cell r="E102">
-            <v>-9.957474226804125E-2</v>
-          </cell>
-          <cell r="F102">
-            <v>-0.61308596118859915</v>
-          </cell>
-          <cell r="G102">
-            <v>1.8658587849385297</v>
-          </cell>
-          <cell r="H102">
-            <v>0.60729554708481315</v>
-          </cell>
-          <cell r="I102">
-            <v>2.0112947240751966</v>
-          </cell>
-          <cell r="J102">
-            <v>1.4202682812815843</v>
-          </cell>
-          <cell r="K102">
-            <v>0.87868466890341967</v>
-          </cell>
-          <cell r="L102">
-            <v>0.66219643335636824</v>
-          </cell>
-          <cell r="M102">
-            <v>1.0749125926998</v>
-          </cell>
-          <cell r="N102">
-            <v>1.3012600238416001</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="B103">
-            <v>0.35185623174180641</v>
-          </cell>
-          <cell r="C103">
-            <v>0.46421956360421668</v>
-          </cell>
-          <cell r="D103">
-            <v>-0.33532922671655546</v>
-          </cell>
-          <cell r="E103">
-            <v>9.4637659187386286E-2</v>
-          </cell>
-          <cell r="F103">
-            <v>-0.4088258035172832</v>
-          </cell>
-          <cell r="G103">
-            <v>2.2045052557105311</v>
-          </cell>
-          <cell r="H103">
-            <v>0.58119747899159646</v>
-          </cell>
-          <cell r="I103">
-            <v>2.3252295763666289</v>
-          </cell>
-          <cell r="J103">
-            <v>1.8404513888888885</v>
-          </cell>
-          <cell r="K103">
-            <v>0.91351720904632594</v>
-          </cell>
-          <cell r="L103">
-            <v>0.51142676322506941</v>
-          </cell>
-          <cell r="M103">
-            <v>1.1613223634868</v>
-          </cell>
-          <cell r="N103">
-            <v>1.5260427205864</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="B104">
-            <v>0.47354589615219389</v>
-          </cell>
-          <cell r="C104">
-            <v>0.50506163570413509</v>
-          </cell>
-          <cell r="D104">
-            <v>-0.42676448528916094</v>
-          </cell>
-          <cell r="E104">
-            <v>0.16529411764705881</v>
-          </cell>
-          <cell r="F104">
-            <v>-0.15216267434808975</v>
-          </cell>
-          <cell r="G104">
-            <v>2.6143036642960835</v>
-          </cell>
-          <cell r="H104">
-            <v>0.44183812700337854</v>
-          </cell>
-          <cell r="I104">
-            <v>2.6965585203153424</v>
-          </cell>
-          <cell r="J104">
-            <v>2.3036424642881204</v>
-          </cell>
-          <cell r="K104">
-            <v>0.95763979981279834</v>
-          </cell>
-          <cell r="L104">
-            <v>0.37389185834966931</v>
-          </cell>
-          <cell r="M104">
-            <v>1.2646397500740001</v>
-          </cell>
-          <cell r="N104">
-            <v>1.7499494655753001</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="B105">
-            <v>0.61049483620611267</v>
-          </cell>
-          <cell r="C105">
-            <v>0.51943587802428171</v>
-          </cell>
-          <cell r="D105">
-            <v>-0.52154349279986167</v>
-          </cell>
-          <cell r="E105">
-            <v>0.30852486355366893</v>
-          </cell>
-          <cell r="F105">
-            <v>0.20102107337780473</v>
-          </cell>
-          <cell r="G105">
-            <v>3.1797864178473634</v>
-          </cell>
-          <cell r="H105">
-            <v>0.26149073031274361</v>
-          </cell>
-          <cell r="I105">
-            <v>3.0910616824049204</v>
-          </cell>
-          <cell r="J105">
-            <v>2.7466719097432781</v>
-          </cell>
-          <cell r="K105">
-            <v>0.98559234681097907</v>
-          </cell>
-          <cell r="L105">
-            <v>0.20717700650147378</v>
-          </cell>
-          <cell r="M105">
-            <v>1.3575380523857901</v>
-          </cell>
-          <cell r="N105">
-            <v>1.8888888902419001</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="B106">
-            <v>0.77950049049856207</v>
-          </cell>
-          <cell r="C106">
-            <v>0.50429267927606336</v>
-          </cell>
-          <cell r="D106">
-            <v>-0.6174272197237356</v>
-          </cell>
-          <cell r="E106">
-            <v>0.59886749545178908</v>
-          </cell>
-          <cell r="F106">
-            <v>0.54786764705882351</v>
-          </cell>
-          <cell r="G106">
-            <v>3.7882244978591242</v>
-          </cell>
-          <cell r="H106">
-            <v>-4.4089491466689751E-2</v>
-          </cell>
-          <cell r="I106">
-            <v>3.624880880187126</v>
-          </cell>
-          <cell r="J106">
-            <v>3.2905621462502519</v>
-          </cell>
-          <cell r="K106">
-            <v>1.0097959155087404</v>
-          </cell>
-          <cell r="L106">
-            <v>1.3087565402569654E-3</v>
-          </cell>
-          <cell r="M106">
-            <v>1.5102681021233999</v>
-          </cell>
-          <cell r="N106">
-            <v>1.9987871451552</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107">
-            <v>0.95037641110699977</v>
-          </cell>
-          <cell r="C107">
-            <v>0.50523639852869606</v>
-          </cell>
-          <cell r="D107">
-            <v>-0.74858305933969604</v>
-          </cell>
-          <cell r="E107">
-            <v>1.0514448150394178</v>
-          </cell>
-          <cell r="F107">
-            <v>1.0121793511218919</v>
-          </cell>
-          <cell r="G107">
-            <v>4.2992665435433777</v>
-          </cell>
-          <cell r="H107">
-            <v>-0.27185198821796752</v>
-          </cell>
-          <cell r="I107">
-            <v>4.2721887724161824</v>
-          </cell>
-          <cell r="J107">
-            <v>3.7293276438582299</v>
-          </cell>
-          <cell r="K107">
-            <v>0.98594252610277655</v>
-          </cell>
-          <cell r="L107">
-            <v>-0.22534376013651689</v>
-          </cell>
-          <cell r="M107">
-            <v>1.6737291847673901</v>
-          </cell>
-          <cell r="N107">
-            <v>2.1452732311034</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="B108">
-            <v>1.1098734216994708</v>
-          </cell>
-          <cell r="C108">
-            <v>0.54939896429527446</v>
-          </cell>
-          <cell r="D108">
-            <v>-0.89334075673037194</v>
-          </cell>
-          <cell r="E108">
-            <v>1.625504851425106</v>
-          </cell>
-          <cell r="F108">
-            <v>1.6829646755609458</v>
-          </cell>
-          <cell r="G108">
-            <v>4.924071292059466</v>
-          </cell>
-          <cell r="H108">
-            <v>-0.60710387247682551</v>
-          </cell>
-          <cell r="I108">
-            <v>4.8937776141384379</v>
-          </cell>
-          <cell r="J108">
-            <v>4.2624264074186362</v>
-          </cell>
-          <cell r="K108">
-            <v>0.89915985808263243</v>
-          </cell>
-          <cell r="L108">
-            <v>-0.45396628682640638</v>
-          </cell>
-          <cell r="M108">
-            <v>1.9619697198113999</v>
-          </cell>
-          <cell r="N108">
-            <v>2.413583992026</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="B109">
-            <v>1.2718524679636272</v>
-          </cell>
-          <cell r="C109">
-            <v>0.63365212201615861</v>
-          </cell>
-          <cell r="D109">
-            <v>-1.0220307047990669</v>
-          </cell>
-          <cell r="E109">
-            <v>2.2568723468768956</v>
-          </cell>
-          <cell r="F109">
-            <v>2.1546899636143118</v>
-          </cell>
-          <cell r="G109">
-            <v>5.5988948766010624</v>
-          </cell>
-          <cell r="H109">
-            <v>-1.0332820757168846</v>
-          </cell>
-          <cell r="I109">
-            <v>5.2557394091657272</v>
-          </cell>
-          <cell r="J109">
-            <v>4.6014365819351779</v>
-          </cell>
-          <cell r="K109">
-            <v>0.89955123493817069</v>
-          </cell>
-          <cell r="L109">
-            <v>-0.88943986489345195</v>
-          </cell>
-          <cell r="M109">
-            <v>2.2645598918814001</v>
-          </cell>
-          <cell r="N109">
-            <v>2.7283201960113002</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="B110">
-            <v>1.4236062264254168</v>
-          </cell>
-          <cell r="C110">
-            <v>0.67909919454325773</v>
-          </cell>
-          <cell r="D110">
-            <v>-1.145522553486128</v>
-          </cell>
-          <cell r="E110">
-            <v>2.9140130382049731</v>
-          </cell>
-          <cell r="F110">
-            <v>2.7638470285021222</v>
-          </cell>
-          <cell r="G110">
-            <v>6.1919425455280521</v>
-          </cell>
-          <cell r="H110">
-            <v>-1.3465671835744604</v>
-          </cell>
-          <cell r="I110">
-            <v>5.7755349562505414</v>
-          </cell>
-          <cell r="J110">
-            <v>5.0399388728859229</v>
-          </cell>
-          <cell r="K110">
-            <v>0.93308605182323934</v>
-          </cell>
-          <cell r="L110">
-            <v>-1.262507756638978</v>
-          </cell>
-          <cell r="M110">
-            <v>2.5280940953502</v>
-          </cell>
-          <cell r="N110">
-            <v>3.1753251151374999</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="B111">
-            <v>1.5546122641668489</v>
-          </cell>
-          <cell r="C111">
-            <v>0.72389090647825893</v>
-          </cell>
-          <cell r="D111">
-            <v>-1.2404100602249066</v>
-          </cell>
-          <cell r="E111">
-            <v>3.3984733171619173</v>
-          </cell>
-          <cell r="F111">
-            <v>3.3400295633717403</v>
-          </cell>
-          <cell r="G111">
-            <v>6.6697344120403548</v>
-          </cell>
-          <cell r="H111">
-            <v>-1.6898488261283893</v>
-          </cell>
-          <cell r="I111">
-            <v>6.2509313003551936</v>
-          </cell>
-          <cell r="J111">
-            <v>5.385950344484872</v>
-          </cell>
-          <cell r="K111">
-            <v>0.95930830114430354</v>
-          </cell>
-          <cell r="L111">
-            <v>-1.5957347299984488</v>
-          </cell>
-          <cell r="M111">
-            <v>2.7473939829431999</v>
-          </cell>
-          <cell r="N111">
-            <v>3.5329155742576002</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="B112">
-            <v>1.6450492540633361</v>
-          </cell>
-          <cell r="C112">
-            <v>0.7654669824413336</v>
-          </cell>
-          <cell r="D112">
-            <v>-1.3552219706655895</v>
-          </cell>
-          <cell r="E112">
-            <v>3.9376637355973321</v>
-          </cell>
-          <cell r="F112">
-            <v>3.7744595209217704</v>
-          </cell>
-          <cell r="G112">
-            <v>6.8638373578109784</v>
-          </cell>
-          <cell r="H112">
-            <v>-1.9396755609460274</v>
-          </cell>
-          <cell r="I112">
-            <v>6.7598977735424057</v>
-          </cell>
-          <cell r="J112">
-            <v>5.7412793317498805</v>
-          </cell>
-          <cell r="K112">
-            <v>1.0327635572942759</v>
-          </cell>
-          <cell r="L112">
-            <v>-1.9009761025004583</v>
-          </cell>
-          <cell r="M112">
-            <v>2.8878332566194</v>
-          </cell>
-          <cell r="N112">
-            <v>3.8605889118685002</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="B113">
-            <v>1.6927497846832651</v>
-          </cell>
-          <cell r="C113">
-            <v>0.81825409360000001</v>
-          </cell>
-          <cell r="D113">
-            <v>-1.4229846703844471</v>
-          </cell>
-          <cell r="E113">
-            <v>4.3878608247422681</v>
-          </cell>
-          <cell r="F113">
-            <v>3.9820853547604611</v>
-          </cell>
-          <cell r="G113">
-            <v>6.9505519874303987</v>
-          </cell>
-          <cell r="H113">
-            <v>-2.0552217794334222</v>
-          </cell>
-          <cell r="I113">
-            <v>7.2098457939876974</v>
-          </cell>
-          <cell r="J113">
-            <v>5.9571087906812199</v>
-          </cell>
-          <cell r="K113">
-            <v>1.1097206063622223</v>
-          </cell>
-          <cell r="L113">
-            <v>-1.9115092656578336</v>
-          </cell>
-          <cell r="M113">
-            <v>3.0418734906072</v>
-          </cell>
-          <cell r="N113">
-            <v>4.1944612926749896</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="B114">
-            <v>1.6838179520900867</v>
-          </cell>
-          <cell r="C114">
-            <v>0.87263154646217211</v>
-          </cell>
-          <cell r="D114">
-            <v>-1.4298891667167906</v>
-          </cell>
-          <cell r="E114">
-            <v>4.5738826561552459</v>
-          </cell>
-          <cell r="F114">
-            <v>4.1506723771983021</v>
-          </cell>
-          <cell r="G114">
-            <v>6.9672057904698894</v>
-          </cell>
-          <cell r="H114">
-            <v>-2.2150047647925142</v>
-          </cell>
-          <cell r="I114">
-            <v>7.4128909295677028</v>
-          </cell>
-          <cell r="J114">
-            <v>5.9428956311906198</v>
-          </cell>
-          <cell r="K114">
-            <v>1.1063630049173414</v>
-          </cell>
-          <cell r="L114">
-            <v>-1.9305482886033818</v>
-          </cell>
-          <cell r="M114">
-            <v>3.1906729875941902</v>
-          </cell>
-          <cell r="N114">
-            <v>4.5047503569765004</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="B115">
-            <v>1.6392811429953302</v>
-          </cell>
-          <cell r="C115">
-            <v>0.94202112595413867</v>
-          </cell>
-          <cell r="D115">
-            <v>-1.4497149347568057</v>
-          </cell>
-          <cell r="E115">
-            <v>4.7887098241358403</v>
-          </cell>
-          <cell r="F115">
-            <v>4.0952600060642812</v>
-          </cell>
-          <cell r="G115">
-            <v>6.8735999320065417</v>
-          </cell>
-          <cell r="H115">
-            <v>-2.2788963007883556</v>
-          </cell>
-          <cell r="I115">
-            <v>7.3603699211643416</v>
-          </cell>
-          <cell r="J115">
-            <v>5.810239475945016</v>
-          </cell>
-          <cell r="K115">
-            <v>1.1889229226540459</v>
-          </cell>
-          <cell r="L115">
-            <v>-1.7291401060544094</v>
-          </cell>
-          <cell r="M115">
-            <v>3.2934288666456002</v>
-          </cell>
-          <cell r="N115">
-            <v>4.7775756384871997</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="B116">
-            <v>1.5798521198704687</v>
-          </cell>
-          <cell r="C116">
-            <v>1.0171691405153918</v>
-          </cell>
-          <cell r="D116">
-            <v>-1.4505040200519321</v>
-          </cell>
-          <cell r="E116">
-            <v>4.764907519708915</v>
-          </cell>
-          <cell r="F116">
-            <v>4.1860726197695577</v>
-          </cell>
-          <cell r="G116">
-            <v>6.7495578128158478</v>
-          </cell>
-          <cell r="H116">
-            <v>-2.1681148748159051</v>
-          </cell>
-          <cell r="I116">
-            <v>7.4183054665165029</v>
-          </cell>
-          <cell r="J116">
-            <v>5.6517890682905447</v>
-          </cell>
-          <cell r="K116">
-            <v>1.2712768525720464</v>
-          </cell>
-          <cell r="L116">
-            <v>-1.1777576614438632</v>
-          </cell>
-          <cell r="M116">
-            <v>3.4671842541125901</v>
-          </cell>
-          <cell r="N116">
-            <v>4.9704871674980904</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="B117">
-            <v>1.5140257371974555</v>
-          </cell>
-          <cell r="C117">
-            <v>1.0996571937082094</v>
-          </cell>
-          <cell r="D117">
-            <v>-1.4276205464933063</v>
-          </cell>
-          <cell r="E117">
-            <v>4.7925758035172832</v>
-          </cell>
-          <cell r="F117">
-            <v>4.3054631594906008</v>
-          </cell>
-          <cell r="G117">
-            <v>6.5428209474980239</v>
-          </cell>
-          <cell r="H117">
-            <v>-1.7680888850385512</v>
-          </cell>
-          <cell r="I117">
-            <v>7.4459196049553835</v>
-          </cell>
-          <cell r="J117">
-            <v>5.4491199422208734</v>
-          </cell>
-          <cell r="K117">
-            <v>1.3796470439924067</v>
-          </cell>
-          <cell r="L117">
-            <v>-0.65123171901222721</v>
-          </cell>
-          <cell r="M117">
-            <v>3.5345651584086002</v>
-          </cell>
-          <cell r="N117">
-            <v>4.8174651338328003</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="B118">
-            <v>1.4443889053946715</v>
-          </cell>
-          <cell r="C118">
-            <v>1.2005827248922181</v>
-          </cell>
-          <cell r="D118">
-            <v>-1.3739627464248092</v>
-          </cell>
-          <cell r="E118">
-            <v>4.9343283808368712</v>
-          </cell>
-          <cell r="F118">
-            <v>4.2129828684050938</v>
-          </cell>
-          <cell r="G118">
-            <v>6.1942396218093609</v>
-          </cell>
-          <cell r="H118">
-            <v>-1.0676102399722776</v>
-          </cell>
-          <cell r="I118">
-            <v>7.2244650437494586</v>
-          </cell>
-          <cell r="J118">
-            <v>5.2048641643083338</v>
-          </cell>
-          <cell r="K118">
-            <v>1.5586298596646191</v>
-          </cell>
-          <cell r="L118">
-            <v>5.4548960257802474E-2</v>
-          </cell>
-          <cell r="M118">
-            <v>3.5836034832018</v>
-          </cell>
-          <cell r="N118">
-            <v>4.6312243143476</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="B119">
-            <v>1.3928429673960745</v>
-          </cell>
-          <cell r="C119">
-            <v>1.3055278010411309</v>
-          </cell>
-          <cell r="D119">
-            <v>-1.3611401103790284</v>
-          </cell>
-          <cell r="E119">
-            <v>5.0647104305639781</v>
-          </cell>
-          <cell r="F119">
-            <v>4.1378615827774414</v>
-          </cell>
-          <cell r="G119">
-            <v>5.9329471948104446</v>
-          </cell>
-          <cell r="H119">
-            <v>-9.5955340899246289E-2</v>
-          </cell>
-          <cell r="I119">
-            <v>7.0896430737243348</v>
-          </cell>
-          <cell r="J119">
-            <v>5.0767878048985908</v>
-          </cell>
-          <cell r="K119">
-            <v>1.7772035340918082</v>
-          </cell>
-          <cell r="L119">
-            <v>1.018737395461661</v>
-          </cell>
-          <cell r="M119">
-            <v>3.7791952748387998</v>
-          </cell>
-          <cell r="N119">
-            <v>4.2828650391165999</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="B120">
-            <v>1.3204793921793263</v>
-          </cell>
-          <cell r="C120">
-            <v>1.4324056116724564</v>
-          </cell>
-          <cell r="D120">
-            <v>-1.3372702802014977</v>
-          </cell>
-          <cell r="E120">
-            <v>4.7592980594299581</v>
-          </cell>
-          <cell r="F120">
-            <v>3.8864213159490593</v>
-          </cell>
-          <cell r="G120">
-            <v>5.8020138467758233</v>
-          </cell>
-          <cell r="H120">
-            <v>1.1080589967945937</v>
-          </cell>
-          <cell r="I120">
-            <v>6.8048384302174476</v>
-          </cell>
-          <cell r="J120">
-            <v>4.9509750227410532</v>
-          </cell>
-          <cell r="K120">
-            <v>1.948070429707069</v>
-          </cell>
-          <cell r="L120">
-            <v>2.0771219696221812</v>
-          </cell>
-          <cell r="M120">
-            <v>3.9561325383420001</v>
-          </cell>
-          <cell r="N120">
-            <v>3.7971834809221998</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="B121">
-            <v>1.2557017569732225</v>
-          </cell>
-          <cell r="C121">
-            <v>1.45626073722504</v>
-          </cell>
-          <cell r="D121">
-            <v>-1.244552758024311</v>
-          </cell>
-          <cell r="E121">
-            <v>4.5901046088538511</v>
-          </cell>
-          <cell r="F121">
-            <v>3.6552963917525769</v>
-          </cell>
-          <cell r="G121">
-            <v>5.6272637686752303</v>
-          </cell>
-          <cell r="H121">
-            <v>2.5992766178636395</v>
-          </cell>
-          <cell r="I121">
-            <v>6.4610153339686391</v>
-          </cell>
-          <cell r="J121">
-            <v>4.8812252585742195</v>
-          </cell>
-          <cell r="K121">
-            <v>2.2030833492630579</v>
-          </cell>
-          <cell r="L121">
-            <v>3.62038462352095</v>
-          </cell>
-          <cell r="M121">
-            <v>4.1068661168412</v>
-          </cell>
-          <cell r="N121">
-            <v>3.3528064170637002</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="B122">
-            <v>1.2555094866042891</v>
-          </cell>
-          <cell r="C122">
-            <v>1.4954076099267164</v>
-          </cell>
-          <cell r="D122">
-            <v>-1.1993776248784058</v>
-          </cell>
-          <cell r="E122">
-            <v>4.2201076409945424</v>
-          </cell>
-          <cell r="F122">
-            <v>3.3814182838083684</v>
-          </cell>
-          <cell r="G122">
-            <v>5.63547581638091</v>
-          </cell>
-          <cell r="H122">
-            <v>4.2695529758295061</v>
-          </cell>
-          <cell r="I122">
-            <v>6.4149917699038372</v>
-          </cell>
-          <cell r="J122">
-            <v>4.9784537977562149</v>
-          </cell>
-          <cell r="K122">
-            <v>2.4494447804334643</v>
-          </cell>
-          <cell r="L122">
-            <v>5.4215114516197271</v>
-          </cell>
-          <cell r="M122">
-            <v>4.1869121355557999</v>
-          </cell>
-          <cell r="N122">
-            <v>2.7986658601004999</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="B123">
-            <v>1.2530798883059489</v>
-          </cell>
-          <cell r="C123">
-            <v>1.5583222267686927</v>
-          </cell>
-          <cell r="D123">
-            <v>-1.1344753593543782</v>
-          </cell>
-          <cell r="E123">
-            <v>4.0859354154032745</v>
-          </cell>
-          <cell r="F123">
-            <v>3.2237469678593089</v>
-          </cell>
-          <cell r="G123">
-            <v>5.7374660032710363</v>
-          </cell>
-          <cell r="H123">
-            <v>6.2429892575586923</v>
-          </cell>
-          <cell r="I123">
-            <v>6.4112015940396772</v>
-          </cell>
-          <cell r="J123">
-            <v>4.8125809623677638</v>
-          </cell>
-          <cell r="K123">
-            <v>2.7155810421994886</v>
-          </cell>
-          <cell r="L123">
-            <v>6.863981870619261</v>
-          </cell>
-          <cell r="M123">
-            <v>4.0281302823768002</v>
-          </cell>
-          <cell r="N123">
-            <v>2.1751229717083</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="B124">
-            <v>1.2915863994659724</v>
-          </cell>
-          <cell r="C124">
-            <v>1.7254828684613441</v>
-          </cell>
-          <cell r="D124">
-            <v>-1.021932069137178</v>
-          </cell>
-          <cell r="E124">
-            <v>4.0355260764099459</v>
-          </cell>
-          <cell r="F124">
-            <v>3.2467912371134018</v>
-          </cell>
-          <cell r="G124">
-            <v>6.0185132862892106</v>
-          </cell>
-          <cell r="H124">
-            <v>8.3535757602009841</v>
-          </cell>
-          <cell r="I124">
-            <v>6.2996621328943947</v>
-          </cell>
-          <cell r="J124">
-            <v>4.690084584091367</v>
-          </cell>
-          <cell r="K124">
-            <v>2.9541149362591299</v>
-          </cell>
-          <cell r="L124">
-            <v>8.3333360951669082</v>
-          </cell>
-          <cell r="M124">
-            <v>3.9528258828534</v>
-          </cell>
-          <cell r="N124">
-            <v>1.5332524773464999</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="B125">
-            <v>1.3400210533127379</v>
-          </cell>
-          <cell r="C125">
-            <v>1.9552086013468468</v>
-          </cell>
-          <cell r="D125">
-            <v>-0.86935256375857439</v>
-          </cell>
-          <cell r="E125">
-            <v>4.0730488174651311</v>
-          </cell>
-          <cell r="F125">
-            <v>3.3053115524560339</v>
-          </cell>
-          <cell r="G125">
-            <v>6.4084419850414385</v>
-          </cell>
-          <cell r="H125">
-            <v>10.457123364809837</v>
-          </cell>
-          <cell r="I125">
-            <v>6.4290695659707175</v>
-          </cell>
-          <cell r="J125">
-            <v>4.8253728059093035</v>
-          </cell>
-          <cell r="K125">
-            <v>3.2111877340021624</v>
-          </cell>
-          <cell r="L125">
-            <v>9.8507285952021668</v>
-          </cell>
-          <cell r="M125">
-            <v>4.0132815275411904</v>
-          </cell>
-          <cell r="N125">
-            <v>1.0995215963674001</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="B126">
-            <v>1.3635829130693025</v>
-          </cell>
-          <cell r="C126">
-            <v>2.1562732310043393</v>
-          </cell>
-          <cell r="D126">
-            <v>-0.72126098099599356</v>
-          </cell>
-          <cell r="E126">
-            <v>3.9166661613098848</v>
-          </cell>
-          <cell r="F126">
-            <v>3.3570853547604607</v>
-          </cell>
-          <cell r="G126">
-            <v>6.5927823566164978</v>
-          </cell>
-          <cell r="H126">
-            <v>12.50327687776141</v>
-          </cell>
-          <cell r="I126">
-            <v>6.451269167460798</v>
-          </cell>
-          <cell r="J126">
-            <v>5.3870031711138049</v>
-          </cell>
-          <cell r="K126">
-            <v>3.4787659104991171</v>
-          </cell>
-          <cell r="L126">
-            <v>11.545289780980722</v>
-          </cell>
-          <cell r="M126">
-            <v>4.2327061945865996</v>
-          </cell>
-          <cell r="N126">
-            <v>0.80917727973870002</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127">
-            <v>1.3910600967023288</v>
-          </cell>
-          <cell r="C127">
-            <v>2.1969055877147841</v>
-          </cell>
-          <cell r="D127">
-            <v>-0.50267449068018544</v>
-          </cell>
-          <cell r="E127">
-            <v>3.6570391146149186</v>
-          </cell>
-          <cell r="F127">
-            <v>3.363983474833232</v>
-          </cell>
-          <cell r="G127">
-            <v>6.6031191998823893</v>
-          </cell>
-          <cell r="H127">
-            <v>14.325810014727537</v>
-          </cell>
-          <cell r="I127">
-            <v>6.4983756389153591</v>
-          </cell>
-          <cell r="J127">
-            <v>5.4122710102082054</v>
-          </cell>
-          <cell r="K127">
-            <v>3.8553116430906744</v>
-          </cell>
-          <cell r="L127">
-            <v>13.374269994499839</v>
-          </cell>
-          <cell r="M127">
-            <v>4.6738639485467903</v>
-          </cell>
-          <cell r="N127">
-            <v>0.95802169733739995</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128">
-            <v>1.374454928476263</v>
-          </cell>
-          <cell r="C128">
-            <v>2.1756719045306196</v>
-          </cell>
-          <cell r="D128">
-            <v>-0.27882085601941636</v>
-          </cell>
-          <cell r="E128">
-            <v>3.2696073377804735</v>
-          </cell>
-          <cell r="F128">
-            <v>3.1534771073377801</v>
-          </cell>
-          <cell r="G128">
-            <v>6.4675916992851494</v>
-          </cell>
-          <cell r="H128">
-            <v>15.701643853417652</v>
-          </cell>
-          <cell r="I128">
-            <v>6.679221173005284</v>
-          </cell>
-          <cell r="J128">
-            <v>5.8681449405363502</v>
-          </cell>
-          <cell r="K128">
-            <v>4.2388609615181805</v>
-          </cell>
-          <cell r="L128">
-            <v>14.863456534615764</v>
-          </cell>
-          <cell r="M128">
-            <v>5.0882565099672004</v>
-          </cell>
-          <cell r="N128">
-            <v>1.25726029333369</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="B129">
-            <v>1.2837033143397032</v>
-          </cell>
-          <cell r="C129">
-            <v>2.2349165020568136</v>
-          </cell>
-          <cell r="D129">
-            <v>3.9692437001160763E-2</v>
-          </cell>
-          <cell r="E129">
-            <v>2.8673938750758037</v>
-          </cell>
-          <cell r="F129">
-            <v>2.8019761976955726</v>
-          </cell>
-          <cell r="G129">
-            <v>6.1735659352775789</v>
-          </cell>
-          <cell r="H129">
-            <v>16.588545005631111</v>
-          </cell>
-          <cell r="I129">
-            <v>6.5812180542320018</v>
-          </cell>
-          <cell r="J129">
-            <v>6.067129173404755</v>
-          </cell>
-          <cell r="K129">
-            <v>4.6512485745642955</v>
-          </cell>
-          <cell r="L129">
-            <v>15.938808756540256</v>
-          </cell>
-          <cell r="M129">
-            <v>5.5839428846262003</v>
-          </cell>
-          <cell r="N129">
-            <v>1.7482649429678001</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="B130">
-            <v>1.1150472425362237</v>
-          </cell>
-          <cell r="C130">
-            <v>2.423835115407313</v>
-          </cell>
-          <cell r="D130">
-            <v>0.25450216782317719</v>
-          </cell>
-          <cell r="E130">
-            <v>2.4885278956943599</v>
-          </cell>
-          <cell r="F130">
-            <v>2.2627857792601573</v>
-          </cell>
-          <cell r="G130">
-            <v>5.619109147876582</v>
-          </cell>
-          <cell r="H130">
-            <v>17.21392402321753</v>
-          </cell>
-          <cell r="I130">
-            <v>6.2319804210343932</v>
-          </cell>
-          <cell r="J130">
-            <v>6.3071736448015621</v>
-          </cell>
-          <cell r="K130">
-            <v>4.9159429215993891</v>
-          </cell>
-          <cell r="L130">
-            <v>16.306808389862777</v>
-          </cell>
-          <cell r="M130">
-            <v>6.1505039882483903</v>
-          </cell>
-          <cell r="N130">
-            <v>2.1197358683737</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="B131">
-            <v>0.89848089061943326</v>
-          </cell>
-          <cell r="C131">
-            <v>2.6580173003191288</v>
-          </cell>
-          <cell r="D131">
-            <v>0.57324330922272337</v>
-          </cell>
-          <cell r="E131">
-            <v>1.8425303214069135</v>
-          </cell>
-          <cell r="F131">
-            <v>1.3528403577926014</v>
-          </cell>
-          <cell r="G131">
-            <v>4.9200514085671756</v>
-          </cell>
-          <cell r="H131">
-            <v>17.614599757428739</v>
-          </cell>
-          <cell r="I131">
-            <v>5.8004418262150219</v>
-          </cell>
-          <cell r="J131">
-            <v>6.3034887516002946</v>
-          </cell>
-          <cell r="K131">
-            <v>5.2278084791177797</v>
-          </cell>
-          <cell r="L131">
-            <v>16.454889679439269</v>
-          </cell>
-          <cell r="M131">
-            <v>6.4117921615739899</v>
-          </cell>
-          <cell r="N131">
-            <v>2.4484873004534</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="B132">
-            <v>0.62711748355662256</v>
-          </cell>
-          <cell r="C132">
-            <v>2.8653733916608197</v>
-          </cell>
-          <cell r="D132">
-            <v>0.9240114500381531</v>
-          </cell>
-          <cell r="E132">
-            <v>1.1997922983626441</v>
-          </cell>
-          <cell r="F132">
-            <v>0.23647437841115826</v>
-          </cell>
-          <cell r="G132">
-            <v>3.7445800485142509</v>
-          </cell>
-          <cell r="H132">
-            <v>17.575073637702499</v>
-          </cell>
-          <cell r="I132">
-            <v>5.0761392185740268</v>
-          </cell>
-          <cell r="J132">
-            <v>6.2440040470655598</v>
-          </cell>
-          <cell r="K132">
-            <v>5.4354442003717685</v>
-          </cell>
-          <cell r="L132">
-            <v>16.343387994133163</v>
-          </cell>
-          <cell r="M132">
-            <v>6.5172307988519904</v>
-          </cell>
-          <cell r="N132">
-            <v>2.4442423034825</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="B133">
-            <v>0.37398480329359512</v>
-          </cell>
-          <cell r="C133">
-            <v>3.0207375426955938</v>
-          </cell>
-          <cell r="D133">
-            <v>1.2038802770866068</v>
-          </cell>
-          <cell r="E133">
-            <v>-6.4235900545785152E-3</v>
-          </cell>
-          <cell r="F133">
-            <v>-0.8431117343844754</v>
-          </cell>
-          <cell r="G133">
-            <v>2.6692612143264047</v>
-          </cell>
-          <cell r="H133">
-            <v>17.168441912847609</v>
-          </cell>
-          <cell r="I133">
-            <v>4.6038291605301911</v>
-          </cell>
-          <cell r="J133">
-            <v>5.6954813733912797</v>
-          </cell>
-          <cell r="K133">
-            <v>5.5411159513671011</v>
-          </cell>
-          <cell r="L133">
-            <v>16.216020456372434</v>
-          </cell>
-          <cell r="M133">
-            <v>6.2282415870935903</v>
-          </cell>
-          <cell r="N133">
-            <v>2.0596321017380999</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="B134">
-            <v>7.9127705059572839E-2</v>
-          </cell>
-          <cell r="C134">
-            <v>3.052456995353428</v>
-          </cell>
-          <cell r="D134">
-            <v>1.5295752326494416</v>
-          </cell>
-          <cell r="E134">
-            <v>-1.4603805336567619</v>
-          </cell>
-          <cell r="F134">
-            <v>-1.7435059126743482</v>
-          </cell>
-          <cell r="G134">
-            <v>1.4789737122590365</v>
-          </cell>
-          <cell r="H134">
-            <v>16.317276704496226</v>
-          </cell>
-          <cell r="I134">
-            <v>4.039959282682144</v>
-          </cell>
-          <cell r="J134">
-            <v>5.3459429325854044</v>
-          </cell>
-          <cell r="K134">
-            <v>5.631750591597017</v>
-          </cell>
-          <cell r="L134">
-            <v>15.602100110003244</v>
-          </cell>
-          <cell r="M134">
-            <v>5.4796896521459901</v>
-          </cell>
-          <cell r="N134">
-            <v>1.2152819899548</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="B135">
-            <v>-0.23119492248647211</v>
-          </cell>
-          <cell r="C135">
-            <v>3.0933514963007145</v>
-          </cell>
-          <cell r="D135">
-            <v>1.7552536270551693</v>
-          </cell>
-          <cell r="E135">
-            <v>-3.0219329896907219</v>
-          </cell>
-          <cell r="F135">
-            <v>-2.8062712249848394</v>
-          </cell>
-          <cell r="G135">
-            <v>0.42780863516915663</v>
-          </cell>
-          <cell r="H135">
-            <v>14.997212596378752</v>
-          </cell>
-          <cell r="I135">
-            <v>3.6168673655029018</v>
-          </cell>
-          <cell r="J135">
-            <v>5.2122339507108677</v>
-          </cell>
-          <cell r="K135">
-            <v>5.6401960921638947</v>
-          </cell>
-          <cell r="L135">
-            <v>14.835250574696433</v>
-          </cell>
-          <cell r="M135">
-            <v>4.2837409906181998</v>
-          </cell>
-          <cell r="N135">
-            <v>-2.6419378766986999E-2</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="B136">
-            <v>-0.51524817389888289</v>
-          </cell>
-          <cell r="C136">
-            <v>3.1306633593444992</v>
-          </cell>
-          <cell r="D136">
-            <v>2.0758195281996921</v>
-          </cell>
-          <cell r="E136">
-            <v>-4.4674302607641003</v>
-          </cell>
-          <cell r="F136">
-            <v>-3.8158224681625224</v>
-          </cell>
-          <cell r="G136">
-            <v>-0.7727353124942572</v>
-          </cell>
-          <cell r="H136">
-            <v>13.356066447197431</v>
-          </cell>
-          <cell r="I136">
-            <v>3.234871783765052</v>
-          </cell>
-          <cell r="J136">
-            <v>5.019829884273296</v>
-          </cell>
-          <cell r="K136">
-            <v>5.5658344896116239</v>
-          </cell>
-          <cell r="L136">
-            <v>13.685416989859958</v>
-          </cell>
-          <cell r="M136">
-            <v>2.7336058534530001</v>
-          </cell>
-          <cell r="N136">
-            <v>-1.4244323169019999</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="B137">
-            <v>-0.72068032354198519</v>
-          </cell>
-          <cell r="C137">
-            <v>3.0981574739761402</v>
-          </cell>
-          <cell r="D137">
-            <v>2.2383710989954544</v>
-          </cell>
-          <cell r="E137">
-            <v>-5.713943298969073</v>
-          </cell>
-          <cell r="F137">
-            <v>-4.7341062765312305</v>
-          </cell>
-          <cell r="G137">
-            <v>-1.7532423231710677</v>
-          </cell>
-          <cell r="H137">
-            <v>11.396004071731781</v>
-          </cell>
-          <cell r="I137">
-            <v>3.002425712553062</v>
-          </cell>
-          <cell r="J137">
-            <v>4.7325134972373819</v>
-          </cell>
-          <cell r="K137">
-            <v>5.499506411988822</v>
-          </cell>
-          <cell r="L137">
-            <v>12.261897450181223</v>
-          </cell>
-          <cell r="M137">
-            <v>0.9228064402242</v>
-          </cell>
-          <cell r="N137">
-            <v>-2.7043325940804999</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="B138">
-            <v>-0.85532201916870321</v>
-          </cell>
-          <cell r="C138">
-            <v>3.0873221788533578</v>
-          </cell>
-          <cell r="D138">
-            <v>2.3327654274247802</v>
-          </cell>
-          <cell r="E138">
-            <v>-6.6092586416009711</v>
-          </cell>
-          <cell r="F138">
-            <v>-5.7086362947240747</v>
-          </cell>
-          <cell r="G138">
-            <v>-2.5438385522906444</v>
-          </cell>
-          <cell r="H138">
-            <v>8.9145217880966801</v>
-          </cell>
-          <cell r="I138">
-            <v>2.6364571601836611</v>
-          </cell>
-          <cell r="J138">
-            <v>4.6573416759315398</v>
-          </cell>
-          <cell r="K138">
-            <v>5.417935235781898</v>
-          </cell>
-          <cell r="L138">
-            <v>10.412644202970087</v>
-          </cell>
-          <cell r="M138">
-            <v>-0.8198633919942</v>
-          </cell>
-          <cell r="N138">
-            <v>-3.7375513806166998</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="B139">
-            <v>-0.87897127454751023</v>
-          </cell>
-          <cell r="C139">
-            <v>3.0673118354411142</v>
-          </cell>
-          <cell r="D139">
-            <v>2.3380917531668737</v>
-          </cell>
-          <cell r="E139">
-            <v>-7.207575803517285</v>
-          </cell>
-          <cell r="F139">
-            <v>-6.3407618253486957</v>
-          </cell>
-          <cell r="G139">
-            <v>-2.75798348861569</v>
-          </cell>
-          <cell r="H139">
-            <v>6.2955102659620534</v>
-          </cell>
-          <cell r="I139">
-            <v>2.5957939876981717</v>
-          </cell>
-          <cell r="J139">
-            <v>4.504365966747522</v>
-          </cell>
-          <cell r="K139">
-            <v>5.2449054680702414</v>
-          </cell>
-          <cell r="L139">
-            <v>8.6784183860549735</v>
-          </cell>
-          <cell r="M139">
-            <v>-2.3565847380263998</v>
-          </cell>
-          <cell r="N139">
-            <v>-4.4744289500415002</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="B140">
-            <v>-0.85479764543524861</v>
-          </cell>
-          <cell r="C140">
-            <v>2.9722408588799007</v>
-          </cell>
-          <cell r="D140">
-            <v>2.2126271912420021</v>
-          </cell>
-          <cell r="E140">
-            <v>-7.4925970285021233</v>
-          </cell>
-          <cell r="F140">
-            <v>-6.5690820194057</v>
-          </cell>
-          <cell r="G140">
-            <v>-2.7958278203502576</v>
-          </cell>
-          <cell r="H140">
-            <v>3.5633349215975039</v>
-          </cell>
-          <cell r="I140">
-            <v>2.3512193537208694</v>
-          </cell>
-          <cell r="J140">
-            <v>4.0716015809244652</v>
-          </cell>
-          <cell r="K140">
-            <v>5.0630182241542974</v>
-          </cell>
-          <cell r="L140">
-            <v>6.3104399072023911</v>
-          </cell>
-          <cell r="M140">
-            <v>-3.63482544841199</v>
-          </cell>
-          <cell r="N140">
-            <v>-4.8201603700047997</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="B141">
-            <v>-0.87897127454751023</v>
-          </cell>
-          <cell r="C141">
-            <v>2.7619137995206757</v>
-          </cell>
-          <cell r="D141">
-            <v>2.0647723340679591</v>
-          </cell>
-          <cell r="E141">
-            <v>-7.756393268647666</v>
-          </cell>
-          <cell r="F141">
-            <v>-6.7533603699211637</v>
-          </cell>
-          <cell r="G141">
-            <v>-2.8432050186522591</v>
-          </cell>
-          <cell r="H141">
-            <v>0.91892922117300502</v>
-          </cell>
-          <cell r="I141">
-            <v>1.8346183834358485</v>
-          </cell>
-          <cell r="J141">
-            <v>3.5293958670237848</v>
-          </cell>
-          <cell r="K141">
-            <v>4.7377634584201243</v>
-          </cell>
-          <cell r="L141">
-            <v>3.4323742719336598</v>
-          </cell>
-          <cell r="M141">
-            <v>-4.4263015149851999</v>
-          </cell>
-          <cell r="N141">
-            <v>-5.0873930364586002</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="B142">
-            <v>-0.94117947845968608</v>
-          </cell>
-          <cell r="C142">
-            <v>2.6809112303366267</v>
-          </cell>
-          <cell r="D142">
-            <v>1.8271590245734493</v>
-          </cell>
-          <cell r="E142">
-            <v>-7.8253744693753804</v>
-          </cell>
-          <cell r="F142">
-            <v>-6.7983118556701028</v>
-          </cell>
-          <cell r="G142">
-            <v>-3.1114461014021351</v>
-          </cell>
-          <cell r="H142">
-            <v>-1.5556224551676339</v>
-          </cell>
-          <cell r="I142">
-            <v>1.26592956770337</v>
-          </cell>
-          <cell r="J142">
-            <v>2.479411869988545</v>
-          </cell>
-          <cell r="K142">
-            <v>4.2707890734173555</v>
-          </cell>
-          <cell r="L142">
-            <v>0.49970366113359754</v>
-          </cell>
-          <cell r="M142">
-            <v>-5.2646946556607901</v>
-          </cell>
-          <cell r="N142">
-            <v>-5.1722255949722999</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="B143">
-            <v>-1.0690917111737355</v>
-          </cell>
-          <cell r="C143">
-            <v>2.4125629132231254</v>
-          </cell>
-          <cell r="D143">
-            <v>1.5795835132279854</v>
-          </cell>
-          <cell r="E143">
-            <v>-7.559228320194058</v>
-          </cell>
-          <cell r="F143">
-            <v>-6.7714016070345657</v>
-          </cell>
-          <cell r="G143">
-            <v>-3.5983114192256092</v>
-          </cell>
-          <cell r="H143">
-            <v>-4.1306679372780026</v>
-          </cell>
-          <cell r="I143">
-            <v>0.26026596205492503</v>
-          </cell>
-          <cell r="J143">
-            <v>0.84047665672798322</v>
-          </cell>
-          <cell r="K143">
-            <v>3.7574674292061072</v>
-          </cell>
-          <cell r="L143">
-            <v>-2.9826746654068006</v>
-          </cell>
-          <cell r="M143">
-            <v>-5.9063105999015901</v>
-          </cell>
-          <cell r="N143">
-            <v>-5.3438447582244004</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="B144">
-            <v>-1.2549297623100806</v>
-          </cell>
-          <cell r="C144">
-            <v>1.9535483545135164</v>
-          </cell>
-          <cell r="D144">
-            <v>1.261878046278291</v>
-          </cell>
-          <cell r="E144">
-            <v>-7.5469481503941793</v>
-          </cell>
-          <cell r="F144">
-            <v>-6.6947642510612493</v>
-          </cell>
-          <cell r="G144">
-            <v>-4.3041455335648777</v>
-          </cell>
-          <cell r="H144">
-            <v>-6.4660118686649906</v>
-          </cell>
-          <cell r="I144">
-            <v>-1.1148964740535388</v>
-          </cell>
-          <cell r="J144">
-            <v>-1.1985326755272556</v>
-          </cell>
-          <cell r="K144">
-            <v>2.9860430481583045</v>
-          </cell>
-          <cell r="L144">
-            <v>-6.1830374645662634</v>
-          </cell>
-          <cell r="M144">
-            <v>-6.3244465448940002</v>
-          </cell>
-          <cell r="N144">
-            <v>-5.5598679374101998</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="B145">
-            <v>-1.4830148572384263</v>
-          </cell>
-          <cell r="C145">
-            <v>1.7700473887244099</v>
-          </cell>
-          <cell r="D145">
-            <v>0.96462961560471316</v>
-          </cell>
-          <cell r="E145">
-            <v>-7.4023150394178305</v>
-          </cell>
-          <cell r="F145">
-            <v>-6.8334088841722256</v>
-          </cell>
-          <cell r="G145">
-            <v>-5.099737903596302</v>
-          </cell>
-          <cell r="H145">
-            <v>-8.248477432209997</v>
-          </cell>
-          <cell r="I145">
-            <v>-2.8522589448150395</v>
-          </cell>
-          <cell r="J145">
-            <v>-3.5444936114480146</v>
-          </cell>
-          <cell r="K145">
-            <v>1.9781034536741635</v>
-          </cell>
-          <cell r="L145">
-            <v>-9.1578847998081994</v>
-          </cell>
-          <cell r="M145">
-            <v>-6.4130399560979896</v>
-          </cell>
-          <cell r="N145">
-            <v>-5.6426116878906001</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="B146">
-            <v>-1.7668758382818988</v>
-          </cell>
-          <cell r="C146">
-            <v>1.3270236284621406</v>
-          </cell>
-          <cell r="D146">
-            <v>0.76061161255014809</v>
-          </cell>
-          <cell r="E146">
-            <v>-7.4098195876288679</v>
-          </cell>
-          <cell r="F146">
-            <v>-7.1131996664645234</v>
-          </cell>
-          <cell r="G146">
-            <v>-6.1806845746733545</v>
-          </cell>
-          <cell r="H146">
-            <v>-9.9914168760287598</v>
-          </cell>
-          <cell r="I146">
-            <v>-4.8720978081954431</v>
-          </cell>
-          <cell r="J146">
-            <v>-6.5346791616130986</v>
-          </cell>
-          <cell r="K146">
-            <v>0.88047676292614763</v>
-          </cell>
-          <cell r="L146">
-            <v>-11.249533015076084</v>
-          </cell>
-          <cell r="M146">
-            <v>-6.3356766956099904</v>
-          </cell>
-          <cell r="N146">
-            <v>-5.1914965336021002</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="B147">
-            <v>-2.1152347885403038</v>
-          </cell>
-          <cell r="C147">
-            <v>0.53034107827688837</v>
-          </cell>
-          <cell r="D147">
-            <v>0.54566477815810388</v>
-          </cell>
-          <cell r="E147">
-            <v>-7.6462507580351744</v>
-          </cell>
-          <cell r="F147">
-            <v>-7.2892154335961177</v>
-          </cell>
-          <cell r="G147">
-            <v>-7.5181572394656069</v>
-          </cell>
-          <cell r="H147">
-            <v>-10.837167547431342</v>
-          </cell>
-          <cell r="I147">
-            <v>-7.152754916399549</v>
-          </cell>
-          <cell r="J147">
-            <v>-9.0935742832356308</v>
-          </cell>
-          <cell r="K147">
-            <v>-0.46176046253328762</v>
-          </cell>
-          <cell r="L147">
-            <v>-13.234527444399001</v>
-          </cell>
-          <cell r="M147">
-            <v>-6.4754296822980004</v>
-          </cell>
-          <cell r="N147">
-            <v>-5.1805134462011999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6513,68 +466,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46CEB54A-B6A9-46B5-89B1-E3597935FD7E}">
   <dimension ref="A1:AT147"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
       <c r="Q1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>320</v>
       </c>
@@ -6624,16 +577,16 @@
         <v>-5.1460109999999998E-3</v>
       </c>
       <c r="Q2">
+        <v>-1.1667013E-2</v>
+      </c>
+      <c r="R2">
         <v>-1.0779909999999999E-3</v>
-      </c>
-      <c r="R2">
-        <v>-2.9808742106199101E-3</v>
       </c>
       <c r="S2">
         <v>1.0655199999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>319</v>
       </c>
@@ -6683,16 +636,16 @@
         <v>-6.326005E-3</v>
       </c>
       <c r="Q3">
+        <v>-7.9518890000000002E-3</v>
+      </c>
+      <c r="R3">
         <v>3.439059E-3</v>
-      </c>
-      <c r="R3">
-        <v>-2.7086305323335302E-3</v>
       </c>
       <c r="S3">
         <v>1.0243540000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>318</v>
       </c>
@@ -6742,16 +695,16 @@
         <v>-8.1871919999999994E-3</v>
       </c>
       <c r="Q4">
+        <v>-5.1027549999999996E-3</v>
+      </c>
+      <c r="R4">
         <v>1.6591710000000001E-3</v>
-      </c>
-      <c r="R4">
-        <v>-1.78426606042479E-3</v>
       </c>
       <c r="S4">
         <v>8.7797999999999999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>317</v>
       </c>
@@ -6801,16 +754,16 @@
         <v>-9.2850400000000003E-4</v>
       </c>
       <c r="Q5">
+        <v>-4.4218360000000002E-3</v>
+      </c>
+      <c r="R5">
         <v>-9.9926700000000008E-4</v>
-      </c>
-      <c r="R5">
-        <v>6.7785280735319098E-4</v>
       </c>
       <c r="S5">
         <v>8.1547100000000001E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>316</v>
       </c>
@@ -6860,16 +813,16 @@
         <v>3.5212640000000001E-3</v>
       </c>
       <c r="Q6">
+        <v>-3.039005E-3</v>
+      </c>
+      <c r="R6">
         <v>-1.3247399999999999E-4</v>
-      </c>
-      <c r="R6">
-        <v>-9.3760179483677402E-4</v>
       </c>
       <c r="S6">
         <v>8.1435700000000004E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>315</v>
       </c>
@@ -6918,17 +871,17 @@
       <c r="P7">
         <v>7.7503420000000003E-3</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7">
+        <v>-1.5973789999999999E-3</v>
+      </c>
+      <c r="R7" s="1">
         <v>6.7600000000000003E-5</v>
-      </c>
-      <c r="R7">
-        <v>6.7668812140036095E-4</v>
       </c>
       <c r="S7">
         <v>8.1331199999999995E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>314</v>
       </c>
@@ -6977,17 +930,17 @@
       <c r="P8">
         <v>3.5237139999999998E-3</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
+        <v>-3.4799999999999999E-5</v>
+      </c>
+      <c r="R8">
         <v>1.681559E-3</v>
-      </c>
-      <c r="R8">
-        <v>1.7118850788273199E-3</v>
       </c>
       <c r="S8">
         <v>8.1319699999999999E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>313</v>
       </c>
@@ -7037,16 +990,16 @@
         <v>-1.863665E-3</v>
       </c>
       <c r="Q9">
+        <v>3.0121240000000001E-3</v>
+      </c>
+      <c r="R9">
         <v>-2.679304E-3</v>
-      </c>
-      <c r="R9" s="1">
-        <v>-2.01158610074029E-5</v>
       </c>
       <c r="S9">
         <v>8.1322999999999996E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>312</v>
       </c>
@@ -7096,16 +1049,16 @@
         <v>-4.9427919999999997E-3</v>
       </c>
       <c r="Q10">
+        <v>3.1390820000000001E-3</v>
+      </c>
+      <c r="R10">
         <v>-1.2164879999999999E-3</v>
-      </c>
-      <c r="R10" s="1">
-        <v>3.0240851897874998E-5</v>
       </c>
       <c r="S10">
         <v>8.1304800000000003E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>311</v>
       </c>
@@ -7155,16 +1108,16 @@
         <v>-3.67024E-3</v>
       </c>
       <c r="Q11">
+        <v>2.4526000000000001E-3</v>
+      </c>
+      <c r="R11">
         <v>8.6391599999999995E-4</v>
-      </c>
-      <c r="R11">
-        <v>4.7738959729796298E-4</v>
       </c>
       <c r="S11">
         <v>8.1457299999999997E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>310</v>
       </c>
@@ -7214,16 +1167,16 @@
         <v>1.281239E-3</v>
       </c>
       <c r="Q12">
+        <v>5.7959259999999999E-3</v>
+      </c>
+      <c r="R12">
         <v>4.3777369999999996E-3</v>
-      </c>
-      <c r="R12">
-        <v>-2.5472939549402301E-3</v>
       </c>
       <c r="S12">
         <v>8.5543700000000002E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>309</v>
       </c>
@@ -7273,16 +1226,16 @@
         <v>5.594435E-3</v>
       </c>
       <c r="Q13">
+        <v>7.8569220000000006E-3</v>
+      </c>
+      <c r="R13">
         <v>-5.3200600000000002E-4</v>
-      </c>
-      <c r="R13">
-        <v>-4.9755563215823102E-3</v>
       </c>
       <c r="S13">
         <v>9.5887800000000003E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19">
       <c r="A14">
         <v>308</v>
       </c>
@@ -7332,16 +1285,16 @@
         <v>1.4957915E-2</v>
       </c>
       <c r="Q14">
+        <v>1.6118323E-2</v>
+      </c>
+      <c r="R14">
         <v>8.6040400000000005E-4</v>
-      </c>
-      <c r="R14">
-        <v>-5.7229481506705197E-3</v>
       </c>
       <c r="S14">
         <v>9.7008700000000001E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19">
       <c r="A15">
         <v>307</v>
       </c>
@@ -7391,16 +1344,16 @@
         <v>2.4762419000000001E-2</v>
       </c>
       <c r="Q15">
+        <v>2.4865824000000002E-2</v>
+      </c>
+      <c r="R15">
         <v>-2.046225E-3</v>
-      </c>
-      <c r="R15">
-        <v>-5.5616425399938598E-3</v>
       </c>
       <c r="S15">
         <v>1.191019E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>306</v>
       </c>
@@ -7450,16 +1403,16 @@
         <v>3.0502858000000001E-2</v>
       </c>
       <c r="Q16">
+        <v>3.1007429999999999E-2</v>
+      </c>
+      <c r="R16">
         <v>-6.3155000000000004E-4</v>
-      </c>
-      <c r="R16">
-        <v>-4.0642556253912398E-4</v>
       </c>
       <c r="S16">
         <v>1.3826590000000001E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46">
       <c r="A17">
         <v>305</v>
       </c>
@@ -7509,16 +1462,16 @@
         <v>3.6210898999999998E-2</v>
       </c>
       <c r="Q17">
+        <v>3.6790528000000003E-2</v>
+      </c>
+      <c r="R17">
         <v>-3.0854E-4</v>
-      </c>
-      <c r="R17">
-        <v>1.9722089376136101E-3</v>
       </c>
       <c r="S17">
         <v>1.421145E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46">
       <c r="A18">
         <v>304</v>
       </c>
@@ -7568,16 +1521,16 @@
         <v>4.5658830999999997E-2</v>
       </c>
       <c r="Q18">
+        <v>4.3760385999999998E-2</v>
+      </c>
+      <c r="R18">
         <v>-1.9268410000000001E-3</v>
-      </c>
-      <c r="R18">
-        <v>1.0027045617470201E-3</v>
       </c>
       <c r="S18">
         <v>1.5199720000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46">
       <c r="A19">
         <v>303</v>
       </c>
@@ -7627,16 +1580,16 @@
         <v>5.7774862000000003E-2</v>
       </c>
       <c r="Q19">
+        <v>5.4559486999999997E-2</v>
+      </c>
+      <c r="R19">
         <v>-1.3824740000000001E-3</v>
-      </c>
-      <c r="R19">
-        <v>-2.4035078142269099E-3</v>
       </c>
       <c r="S19">
         <v>2.024573E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46">
       <c r="A20">
         <v>302</v>
       </c>
@@ -7685,17 +1638,17 @@
       <c r="P20">
         <v>7.6409024000000006E-2</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20">
+        <v>7.1532529999999997E-2</v>
+      </c>
+      <c r="R20" s="1">
         <v>9.2100000000000003E-5</v>
-      </c>
-      <c r="R20">
-        <v>-4.8194833242789798E-3</v>
       </c>
       <c r="S20">
         <v>2.4002960000000001E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46">
       <c r="A21">
         <v>301</v>
       </c>
@@ -7745,16 +1698,16 @@
         <v>9.6541815000000003E-2</v>
       </c>
       <c r="Q21">
+        <v>8.7702287000000004E-2</v>
+      </c>
+      <c r="R21">
         <v>-1.276669E-3</v>
-      </c>
-      <c r="R21">
-        <v>-4.5188539920706199E-3</v>
       </c>
       <c r="S21">
         <v>2.9907089999999998E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46">
       <c r="A22">
         <v>300</v>
       </c>
@@ -7804,16 +1757,16 @@
         <v>0.115214794</v>
       </c>
       <c r="Q22">
+        <v>0.102087452</v>
+      </c>
+      <c r="R22">
         <v>-2.1445040000000002E-3</v>
-      </c>
-      <c r="R22">
-        <v>-2.26149115205369E-3</v>
       </c>
       <c r="S22">
         <v>3.3726580000000002E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46">
       <c r="A23">
         <v>299</v>
       </c>
@@ -7863,16 +1816,16 @@
         <v>0.135231294</v>
       </c>
       <c r="Q23">
+        <v>0.115173373</v>
+      </c>
+      <c r="R23">
         <v>-1.43339E-4</v>
-      </c>
-      <c r="R23">
-        <v>-1.72689169787068E-3</v>
       </c>
       <c r="S23">
         <v>4.5925310000000004E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46">
       <c r="A24">
         <v>298</v>
       </c>
@@ -7922,17 +1875,17 @@
         <v>0.152415147</v>
       </c>
       <c r="Q24">
+        <v>0.124800894</v>
+      </c>
+      <c r="R24">
         <v>-1.7594299999999999E-4</v>
-      </c>
-      <c r="R24">
-        <v>-1.2963663677513901E-3</v>
       </c>
       <c r="S24">
         <v>6.3301629999999998E-3</v>
       </c>
       <c r="AT24" s="1"/>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46">
       <c r="A25">
         <v>297</v>
       </c>
@@ -7982,16 +1935,16 @@
         <v>0.16972726899999999</v>
       </c>
       <c r="Q25">
+        <v>0.13390703900000001</v>
+      </c>
+      <c r="R25">
         <v>2.251229E-3</v>
-      </c>
-      <c r="R25">
-        <v>-1.65845915516204E-3</v>
       </c>
       <c r="S25">
         <v>7.6510179999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46">
       <c r="A26">
         <v>296</v>
       </c>
@@ -8041,16 +1994,16 @@
         <v>0.18465411700000001</v>
       </c>
       <c r="Q26">
+        <v>0.13984067999999999</v>
+      </c>
+      <c r="R26">
         <v>1.620703E-3</v>
-      </c>
-      <c r="R26">
-        <v>-2.8907367131062399E-3</v>
       </c>
       <c r="S26">
         <v>8.8019190000000001E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46">
       <c r="A27">
         <v>295</v>
       </c>
@@ -8100,16 +2053,16 @@
         <v>0.19551089099999999</v>
       </c>
       <c r="Q27">
+        <v>0.14007186799999999</v>
+      </c>
+      <c r="R27">
         <v>3.2222079999999998E-3</v>
-      </c>
-      <c r="R27">
-        <v>-2.8818029258728499E-3</v>
       </c>
       <c r="S27">
         <v>1.0185791E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46">
       <c r="A28">
         <v>294</v>
       </c>
@@ -8159,16 +2112,16 @@
         <v>0.202152681</v>
       </c>
       <c r="Q28">
+        <v>0.14077066899999999</v>
+      </c>
+      <c r="R28">
         <v>6.0363650000000001E-3</v>
-      </c>
-      <c r="R28">
-        <v>-4.2561985299327497E-3</v>
       </c>
       <c r="S28">
         <v>1.1457843000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46">
       <c r="A29">
         <v>293</v>
       </c>
@@ -8218,16 +2171,16 @@
         <v>0.20362878300000001</v>
       </c>
       <c r="Q29">
+        <v>0.140854901</v>
+      </c>
+      <c r="R29">
         <v>4.1094010000000004E-3</v>
-      </c>
-      <c r="R29">
-        <v>-3.37082295493186E-3</v>
       </c>
       <c r="S29">
         <v>1.2664349E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46">
       <c r="A30">
         <v>292</v>
       </c>
@@ -8277,16 +2230,16 @@
         <v>0.19809694999999999</v>
       </c>
       <c r="Q30">
+        <v>0.13739368900000001</v>
+      </c>
+      <c r="R30">
         <v>7.0596959999999999E-3</v>
-      </c>
-      <c r="R30">
-        <v>-1.22660880509966E-3</v>
       </c>
       <c r="S30">
         <v>1.4247182000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46">
       <c r="A31">
         <v>291</v>
       </c>
@@ -8336,16 +2289,16 @@
         <v>0.18895047100000001</v>
       </c>
       <c r="Q31">
+        <v>0.13492394299999999</v>
+      </c>
+      <c r="R31">
         <v>1.1469597E-2</v>
-      </c>
-      <c r="R31">
-        <v>1.3403647337997401E-3</v>
       </c>
       <c r="S31">
         <v>1.5972101999999998E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46">
       <c r="A32">
         <v>290</v>
       </c>
@@ -8395,16 +2348,16 @@
         <v>0.17886332999999999</v>
       </c>
       <c r="Q32">
+        <v>0.13031240599999999</v>
+      </c>
+      <c r="R32">
         <v>1.5253157E-2</v>
-      </c>
-      <c r="R32">
-        <v>2.2336445438518901E-3</v>
       </c>
       <c r="S32">
         <v>1.7500911000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>289</v>
       </c>
@@ -8454,16 +2407,16 @@
         <v>0.16646555699999999</v>
       </c>
       <c r="Q33">
+        <v>0.122623046</v>
+      </c>
+      <c r="R33">
         <v>1.9977095E-2</v>
-      </c>
-      <c r="R33">
-        <v>1.98340395895961E-3</v>
       </c>
       <c r="S33">
         <v>1.9265198000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>288</v>
       </c>
@@ -8513,16 +2466,16 @@
         <v>0.156693729</v>
       </c>
       <c r="Q34">
+        <v>0.119070011</v>
+      </c>
+      <c r="R34">
         <v>2.2278144999999999E-2</v>
-      </c>
-      <c r="R34">
-        <v>1.5949656948600901E-3</v>
       </c>
       <c r="S34">
         <v>2.1309938E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>287</v>
       </c>
@@ -8572,16 +2525,16 @@
         <v>0.14697675199999999</v>
       </c>
       <c r="Q35">
+        <v>0.11453141</v>
+      </c>
+      <c r="R35">
         <v>2.7791243E-2</v>
-      </c>
-      <c r="R35">
-        <v>2.8472385061265302E-3</v>
       </c>
       <c r="S35">
         <v>2.3028244999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>286</v>
       </c>
@@ -8631,16 +2584,16 @@
         <v>0.13659191800000001</v>
       </c>
       <c r="Q36">
+        <v>0.106711707</v>
+      </c>
+      <c r="R36">
         <v>3.1108949E-2</v>
-      </c>
-      <c r="R36">
-        <v>5.3299157610115196E-3</v>
       </c>
       <c r="S36">
         <v>2.5188516000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>285</v>
       </c>
@@ -8690,16 +2643,16 @@
         <v>0.122778769</v>
       </c>
       <c r="Q37">
+        <v>9.8707085E-2</v>
+      </c>
+      <c r="R37">
         <v>3.7225622E-2</v>
-      </c>
-      <c r="R37">
-        <v>7.5506808278451897E-3</v>
       </c>
       <c r="S37">
         <v>2.7195634E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>284</v>
       </c>
@@ -8749,16 +2702,16 @@
         <v>0.10370412699999999</v>
       </c>
       <c r="Q38">
+        <v>8.7264752000000001E-2</v>
+      </c>
+      <c r="R38">
         <v>4.1813586E-2</v>
-      </c>
-      <c r="R38">
-        <v>8.4307043511767203E-3</v>
       </c>
       <c r="S38">
         <v>2.9243938000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>283</v>
       </c>
@@ -8808,16 +2761,16 @@
         <v>8.4125658000000006E-2</v>
       </c>
       <c r="Q39">
+        <v>7.3237969E-2</v>
+      </c>
+      <c r="R39">
         <v>4.4520203000000001E-2</v>
-      </c>
-      <c r="R39">
-        <v>8.9595613705780296E-3</v>
       </c>
       <c r="S39">
         <v>3.1214777999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>282</v>
       </c>
@@ -8867,16 +2820,16 @@
         <v>6.7576881000000005E-2</v>
       </c>
       <c r="Q40">
+        <v>6.3091775000000003E-2</v>
+      </c>
+      <c r="R40">
         <v>4.5762114999999999E-2</v>
-      </c>
-      <c r="R40">
-        <v>1.1978354714018201E-2</v>
       </c>
       <c r="S40">
         <v>3.3314060999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>281</v>
       </c>
@@ -8926,16 +2879,16 @@
         <v>5.4423746000000002E-2</v>
       </c>
       <c r="Q41">
+        <v>5.4224027000000001E-2</v>
+      </c>
+      <c r="R41">
         <v>4.4422471999999998E-2</v>
-      </c>
-      <c r="R41">
-        <v>1.6339881641905599E-2</v>
       </c>
       <c r="S41">
         <v>3.5520767000000002E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>280</v>
       </c>
@@ -8985,16 +2938,16 @@
         <v>4.5194882999999998E-2</v>
       </c>
       <c r="Q42">
+        <v>4.8299935000000002E-2</v>
+      </c>
+      <c r="R42">
         <v>4.2002284000000001E-2</v>
-      </c>
-      <c r="R42">
-        <v>2.11245891991311E-2</v>
       </c>
       <c r="S42">
         <v>3.8228785000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>279</v>
       </c>
@@ -9044,16 +2997,16 @@
         <v>3.4429557999999999E-2</v>
       </c>
       <c r="Q43">
+        <v>3.8016324999999997E-2</v>
+      </c>
+      <c r="R43">
         <v>4.0153725000000001E-2</v>
-      </c>
-      <c r="R43">
-        <v>2.34531801653717E-2</v>
       </c>
       <c r="S43">
         <v>4.1076985000000003E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>278</v>
       </c>
@@ -9103,16 +3056,16 @@
         <v>2.2172833999999999E-2</v>
       </c>
       <c r="Q44">
+        <v>2.8388241000000002E-2</v>
+      </c>
+      <c r="R44">
         <v>3.3934736E-2</v>
-      </c>
-      <c r="R44">
-        <v>2.3477392424972099E-2</v>
       </c>
       <c r="S44">
         <v>4.3195682999999999E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>277</v>
       </c>
@@ -9162,16 +3115,16 @@
         <v>1.3757432E-2</v>
       </c>
       <c r="Q45">
+        <v>1.8569042000000001E-2</v>
+      </c>
+      <c r="R45">
         <v>3.0449442E-2</v>
-      </c>
-      <c r="R45">
-        <v>2.43315160663648E-2</v>
       </c>
       <c r="S45">
         <v>4.5187102E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>276</v>
       </c>
@@ -9221,16 +3174,16 @@
         <v>2.7457099999999998E-4</v>
       </c>
       <c r="Q46">
+        <v>5.5722419999999998E-3</v>
+      </c>
+      <c r="R46">
         <v>2.9217381000000001E-2</v>
-      </c>
-      <c r="R46">
-        <v>2.6291599935726401E-2</v>
       </c>
       <c r="S46">
         <v>4.6881600000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>275</v>
       </c>
@@ -9280,16 +3233,16 @@
         <v>-1.0486021E-2</v>
       </c>
       <c r="Q47">
+        <v>-7.9513410000000007E-3</v>
+      </c>
+      <c r="R47">
         <v>2.9797852999999999E-2</v>
-      </c>
-      <c r="R47">
-        <v>2.9029413018591101E-2</v>
       </c>
       <c r="S47">
         <v>4.8217405999999997E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>274</v>
       </c>
@@ -9339,16 +3292,16 @@
         <v>-1.9561367999999999E-2</v>
       </c>
       <c r="Q48">
+        <v>-2.0049530999999999E-2</v>
+      </c>
+      <c r="R48">
         <v>2.8076058000000001E-2</v>
-      </c>
-      <c r="R48">
-        <v>3.2478716766348503E-2</v>
       </c>
       <c r="S48">
         <v>4.9621535000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>273</v>
       </c>
@@ -9398,16 +3351,16 @@
         <v>-2.6309183E-2</v>
       </c>
       <c r="Q49">
+        <v>-3.4071888000000002E-2</v>
+      </c>
+      <c r="R49">
         <v>2.6995584E-2</v>
-      </c>
-      <c r="R49">
-        <v>3.5479632908396598E-2</v>
       </c>
       <c r="S49">
         <v>5.0461705000000003E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>272</v>
       </c>
@@ -9457,16 +3410,16 @@
         <v>-3.1970149000000003E-2</v>
       </c>
       <c r="Q50">
+        <v>-4.4995122999999998E-2</v>
+      </c>
+      <c r="R50">
         <v>2.5301194999999999E-2</v>
-      </c>
-      <c r="R50">
-        <v>3.8471118364742103E-2</v>
       </c>
       <c r="S50">
         <v>5.1008719000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>271</v>
       </c>
@@ -9516,16 +3469,16 @@
         <v>-3.0678599000000001E-2</v>
       </c>
       <c r="Q51">
+        <v>-5.3833352000000001E-2</v>
+      </c>
+      <c r="R51">
         <v>1.9496927000000001E-2</v>
-      </c>
-      <c r="R51">
-        <v>3.92609210451779E-2</v>
       </c>
       <c r="S51">
         <v>5.1249571000000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>270</v>
       </c>
@@ -9575,16 +3528,16 @@
         <v>-3.2535685000000002E-2</v>
       </c>
       <c r="Q52">
+        <v>-6.3871730000000002E-2</v>
+      </c>
+      <c r="R52">
         <v>1.4394552999999999E-2</v>
-      </c>
-      <c r="R52">
-        <v>3.9073864240454802E-2</v>
       </c>
       <c r="S52">
         <v>5.1157178999999997E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>269</v>
       </c>
@@ -9634,16 +3587,16 @@
         <v>-3.4573423999999998E-2</v>
       </c>
       <c r="Q53">
+        <v>-7.5864608E-2</v>
+      </c>
+      <c r="R53">
         <v>1.0348400000000001E-2</v>
-      </c>
-      <c r="R53">
-        <v>3.8593593612201799E-2</v>
       </c>
       <c r="S53">
         <v>5.0652833000000001E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>268</v>
       </c>
@@ -9693,16 +3646,16 @@
         <v>-3.8136032E-2</v>
       </c>
       <c r="Q54">
+        <v>-9.0767730000000005E-2</v>
+      </c>
+      <c r="R54">
         <v>6.4221189999999996E-3</v>
-      </c>
-      <c r="R54">
-        <v>3.8280415197552299E-2</v>
       </c>
       <c r="S54">
         <v>4.9477637999999997E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>267</v>
       </c>
@@ -9752,16 +3705,16 @@
         <v>-4.1312185000000001E-2</v>
       </c>
       <c r="Q55">
+        <v>-0.10343609099999999</v>
+      </c>
+      <c r="R55">
         <v>8.3915300000000003E-4</v>
-      </c>
-      <c r="R55">
-        <v>3.75124136237555E-2</v>
       </c>
       <c r="S55">
         <v>4.7962513999999998E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>266</v>
       </c>
@@ -9811,16 +3764,16 @@
         <v>-4.5827488E-2</v>
       </c>
       <c r="Q56">
+        <v>-0.1156146</v>
+      </c>
+      <c r="R56">
         <v>-9.7063E-4</v>
-      </c>
-      <c r="R56">
-        <v>3.7467082724242803E-2</v>
       </c>
       <c r="S56">
         <v>4.6298352000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>265</v>
       </c>
@@ -9870,16 +3823,16 @@
         <v>-4.5534142999999999E-2</v>
       </c>
       <c r="Q57">
+        <v>-0.122627862</v>
+      </c>
+      <c r="R57">
         <v>-1.0991989999999999E-3</v>
-      </c>
-      <c r="R57">
-        <v>3.4776294085549102E-2</v>
       </c>
       <c r="S57">
         <v>4.3669868000000001E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>264</v>
       </c>
@@ -9929,16 +3882,16 @@
         <v>-3.9833309999999997E-2</v>
       </c>
       <c r="Q58">
+        <v>-0.12749612799999999</v>
+      </c>
+      <c r="R58">
         <v>-2.0182669999999998E-3</v>
-      </c>
-      <c r="R58">
-        <v>3.24526276003426E-2</v>
       </c>
       <c r="S58">
         <v>4.0859886999999998E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>263</v>
       </c>
@@ -9988,16 +3941,16 @@
         <v>-3.1877918999999998E-2</v>
       </c>
       <c r="Q59">
+        <v>-0.13435509100000001</v>
+      </c>
+      <c r="R59">
         <v>-4.0969400000000003E-3</v>
-      </c>
-      <c r="R59">
-        <v>2.98130677882937E-2</v>
       </c>
       <c r="S59">
         <v>3.7066081000000001E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>262</v>
       </c>
@@ -10047,16 +4000,16 @@
         <v>-2.2551379E-2</v>
       </c>
       <c r="Q60">
+        <v>-0.140057863</v>
+      </c>
+      <c r="R60">
         <v>-3.7615610000000001E-3</v>
-      </c>
-      <c r="R60">
-        <v>2.8298041502126899E-2</v>
       </c>
       <c r="S60">
         <v>3.3601899999999997E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>261</v>
       </c>
@@ -10106,16 +4059,16 @@
         <v>-1.5048384999999999E-2</v>
       </c>
       <c r="Q61">
+        <v>-0.14014581200000001</v>
+      </c>
+      <c r="R61">
         <v>-1.0191522999999999E-2</v>
-      </c>
-      <c r="R61">
-        <v>2.6420068120184301E-2</v>
       </c>
       <c r="S61">
         <v>2.9258325000000002E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>260</v>
       </c>
@@ -10165,16 +4118,16 @@
         <v>-8.0377799999999996E-3</v>
       </c>
       <c r="Q62">
+        <v>-0.13751912799999999</v>
+      </c>
+      <c r="R62">
         <v>-1.8604657E-2</v>
-      </c>
-      <c r="R62">
-        <v>2.4012726050949101E-2</v>
       </c>
       <c r="S62">
         <v>2.4880625999999999E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>259</v>
       </c>
@@ -10224,16 +4177,16 @@
         <v>1.7240459999999999E-3</v>
       </c>
       <c r="Q63">
+        <v>-0.13037505399999999</v>
+      </c>
+      <c r="R63">
         <v>-2.8325241000000001E-2</v>
-      </c>
-      <c r="R63">
-        <v>2.0231140610256701E-2</v>
       </c>
       <c r="S63">
         <v>2.0134451000000001E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>258</v>
       </c>
@@ -10283,16 +4236,16 @@
         <v>1.4525489000000001E-2</v>
       </c>
       <c r="Q64">
+        <v>-0.121198792</v>
+      </c>
+      <c r="R64">
         <v>-3.9867751E-2</v>
-      </c>
-      <c r="R64">
-        <v>1.7718196562928799E-2</v>
       </c>
       <c r="S64">
         <v>1.3977501E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>257</v>
       </c>
@@ -10342,16 +4295,16 @@
         <v>2.6004945000000002E-2</v>
       </c>
       <c r="Q65">
+        <v>-0.112496309</v>
+      </c>
+      <c r="R65">
         <v>-5.5980681999999997E-2</v>
-      </c>
-      <c r="R65">
-        <v>1.42198197806482E-2</v>
       </c>
       <c r="S65">
         <v>8.9661199999999993E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>256</v>
       </c>
@@ -10401,16 +4354,16 @@
         <v>3.7582415000000001E-2</v>
       </c>
       <c r="Q66">
+        <v>-9.9851785999999998E-2</v>
+      </c>
+      <c r="R66">
         <v>-7.2363891999999999E-2</v>
-      </c>
-      <c r="R66">
-        <v>1.27539934633375E-2</v>
       </c>
       <c r="S66">
         <v>5.1122099999999998E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>255</v>
       </c>
@@ -10460,16 +4413,16 @@
         <v>4.7251214999999999E-2</v>
       </c>
       <c r="Q67">
+        <v>-8.3280666000000003E-2</v>
+      </c>
+      <c r="R67">
         <v>-9.0895340000000005E-2</v>
-      </c>
-      <c r="R67">
-        <v>9.7963290412201795E-3</v>
       </c>
       <c r="S67">
         <v>1.8371489999999999E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>254</v>
       </c>
@@ -10519,16 +4472,16 @@
         <v>5.7420403000000002E-2</v>
       </c>
       <c r="Q68">
+        <v>-6.6213289999999994E-2</v>
+      </c>
+      <c r="R68">
         <v>-0.110201008</v>
-      </c>
-      <c r="R68">
-        <v>6.97594816881098E-3</v>
       </c>
       <c r="S68">
         <v>-2.2075720000000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>253</v>
       </c>
@@ -10578,16 +4531,16 @@
         <v>6.4962303999999998E-2</v>
       </c>
       <c r="Q69">
+        <v>-4.9332934000000002E-2</v>
+      </c>
+      <c r="R69">
         <v>-0.13104460300000001</v>
-      </c>
-      <c r="R69">
-        <v>1.29869974227316E-3</v>
       </c>
       <c r="S69">
         <v>-4.4246169999999996E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>252</v>
       </c>
@@ -10637,16 +4590,16 @@
         <v>6.9482601000000005E-2</v>
       </c>
       <c r="Q70">
+        <v>-3.4467210999999998E-2</v>
+      </c>
+      <c r="R70">
         <v>-0.151840271</v>
-      </c>
-      <c r="R70">
-        <v>-1.96503593539678E-3</v>
       </c>
       <c r="S70">
         <v>-5.938118E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>251</v>
       </c>
@@ -10696,16 +4649,16 @@
         <v>6.9133923999999999E-2</v>
       </c>
       <c r="Q71">
+        <v>-2.1610863000000001E-2</v>
+      </c>
+      <c r="R71">
         <v>-0.16526827899999999</v>
-      </c>
-      <c r="R71">
-        <v>-5.2587733583967598E-3</v>
       </c>
       <c r="S71">
         <v>-7.0901209999999996E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>250</v>
       </c>
@@ -10755,16 +4708,16 @@
         <v>7.0371937999999995E-2</v>
       </c>
       <c r="Q72">
+        <v>-8.8338889999999993E-3</v>
+      </c>
+      <c r="R72">
         <v>-0.17698999900000001</v>
-      </c>
-      <c r="R72">
-        <v>-5.9174445539500803E-3</v>
       </c>
       <c r="S72">
         <v>-8.2362029999999992E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>249</v>
       </c>
@@ -10814,16 +4767,16 @@
         <v>6.9955787000000005E-2</v>
       </c>
       <c r="Q73">
+        <v>2.9386799999999999E-3</v>
+      </c>
+      <c r="R73">
         <v>-0.18103646100000001</v>
-      </c>
-      <c r="R73">
-        <v>-7.1528821149608596E-3</v>
       </c>
       <c r="S73">
         <v>-9.6330440000000003E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>248</v>
       </c>
@@ -10873,16 +4826,16 @@
         <v>7.0082749999999999E-2</v>
       </c>
       <c r="Q74">
+        <v>1.0843096999999999E-2</v>
+      </c>
+      <c r="R74">
         <v>-0.17780404599999999</v>
-      </c>
-      <c r="R74">
-        <v>-8.0591193579520395E-3</v>
       </c>
       <c r="S74">
         <v>-1.0354385000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>247</v>
       </c>
@@ -10932,16 +4885,16 @@
         <v>6.8285947E-2</v>
       </c>
       <c r="Q75">
+        <v>1.7474851E-2</v>
+      </c>
+      <c r="R75">
         <v>-0.171272437</v>
-      </c>
-      <c r="R75">
-        <v>-9.4096861599593899E-3</v>
       </c>
       <c r="S75">
         <v>-1.0848372E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>246</v>
       </c>
@@ -10991,16 +4944,16 @@
         <v>6.5060107000000006E-2</v>
       </c>
       <c r="Q76">
+        <v>2.1566214E-2</v>
+      </c>
+      <c r="R76">
         <v>-0.16347425700000001</v>
-      </c>
-      <c r="R76">
-        <v>-1.1902158083679001E-2</v>
       </c>
       <c r="S76">
         <v>-1.1194526E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>245</v>
       </c>
@@ -11050,16 +5003,16 @@
         <v>6.1937010000000001E-2</v>
       </c>
       <c r="Q77">
+        <v>2.4251162E-2</v>
+      </c>
+      <c r="R77">
         <v>-0.15332169000000001</v>
-      </c>
-      <c r="R77">
-        <v>-1.32957503092594E-2</v>
       </c>
       <c r="S77">
         <v>-1.177545E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>244</v>
       </c>
@@ -11109,16 +5062,16 @@
         <v>5.9258107999999997E-2</v>
       </c>
       <c r="Q78">
+        <v>2.7414523999999999E-2</v>
+      </c>
+      <c r="R78">
         <v>-0.13886164400000001</v>
-      </c>
-      <c r="R78">
-        <v>-1.3347819852422799E-2</v>
       </c>
       <c r="S78">
         <v>-1.1939774E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>243</v>
       </c>
@@ -11168,16 +5121,16 @@
         <v>5.5149300999999998E-2</v>
       </c>
       <c r="Q79">
+        <v>2.7463464E-2</v>
+      </c>
+      <c r="R79">
         <v>-0.124792203</v>
-      </c>
-      <c r="R79">
-        <v>-1.43752613000005E-2</v>
       </c>
       <c r="S79">
         <v>-1.1820450999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>242</v>
       </c>
@@ -11227,16 +5180,16 @@
         <v>5.0618396000000003E-2</v>
       </c>
       <c r="Q80">
+        <v>2.6147526000000001E-2</v>
+      </c>
+      <c r="R80">
         <v>-0.110065596</v>
-      </c>
-      <c r="R80">
-        <v>-1.54074511345166E-2</v>
       </c>
       <c r="S80">
         <v>-1.1730422000000001E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>241</v>
       </c>
@@ -11286,16 +5239,16 @@
         <v>4.7054534000000002E-2</v>
       </c>
       <c r="Q81">
+        <v>2.3651834E-2</v>
+      </c>
+      <c r="R81">
         <v>-9.4008388999999998E-2</v>
-      </c>
-      <c r="R81">
-        <v>-1.55322340430517E-2</v>
       </c>
       <c r="S81">
         <v>-1.1584989E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>240</v>
       </c>
@@ -11345,16 +5298,16 @@
         <v>4.3868847000000002E-2</v>
       </c>
       <c r="Q82">
+        <v>2.2029205E-2</v>
+      </c>
+      <c r="R82">
         <v>-7.7818094000000004E-2</v>
-      </c>
-      <c r="R82">
-        <v>-1.87490261270255E-2</v>
       </c>
       <c r="S82">
         <v>-1.1914976000000001E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>239</v>
       </c>
@@ -11404,16 +5357,16 @@
         <v>4.2691778E-2</v>
       </c>
       <c r="Q83">
+        <v>1.8530825000000001E-2</v>
+      </c>
+      <c r="R83">
         <v>-6.2939558000000007E-2</v>
-      </c>
-      <c r="R83">
-        <v>-1.9966638165768401E-2</v>
       </c>
       <c r="S83">
         <v>-1.2026452999999999E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>238</v>
       </c>
@@ -11463,16 +5416,16 @@
         <v>3.8048239999999997E-2</v>
       </c>
       <c r="Q84">
+        <v>1.1088516E-2</v>
+      </c>
+      <c r="R84">
         <v>-5.0797523999999997E-2</v>
-      </c>
-      <c r="R84">
-        <v>-1.9299386013275799E-2</v>
       </c>
       <c r="S84">
         <v>-1.2005854E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>237</v>
       </c>
@@ -11522,16 +5475,16 @@
         <v>3.6505009999999997E-2</v>
       </c>
       <c r="Q85">
+        <v>1.6219069999999999E-3</v>
+      </c>
+      <c r="R85">
         <v>-3.8407706999999999E-2</v>
-      </c>
-      <c r="R85">
-        <v>-2.0514845556898701E-2</v>
       </c>
       <c r="S85">
         <v>-1.2214961999999999E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>236</v>
       </c>
@@ -11581,16 +5534,16 @@
         <v>3.1806710000000002E-2</v>
       </c>
       <c r="Q86">
+        <v>-6.7315129999999997E-3</v>
+      </c>
+      <c r="R86">
         <v>-2.8435453999999999E-2</v>
-      </c>
-      <c r="R86">
-        <v>-1.96810576414891E-2</v>
       </c>
       <c r="S86">
         <v>-1.2301576999999999E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>235</v>
       </c>
@@ -11640,16 +5593,16 @@
         <v>2.6229288E-2</v>
       </c>
       <c r="Q87">
+        <v>-1.1922924E-2</v>
+      </c>
+      <c r="R87">
         <v>-1.4256381E-2</v>
-      </c>
-      <c r="R87">
-        <v>-2.1292276408846698E-2</v>
       </c>
       <c r="S87">
         <v>-1.2378640999999999E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>234</v>
       </c>
@@ -11699,16 +5652,16 @@
         <v>1.9804136E-2</v>
       </c>
       <c r="Q88">
+        <v>-1.2530405E-2</v>
+      </c>
+      <c r="R88">
         <v>-4.5485070000000002E-3</v>
-      </c>
-      <c r="R88">
-        <v>-2.3599368635182E-2</v>
       </c>
       <c r="S88">
         <v>-1.2468788999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19">
       <c r="A89">
         <v>233</v>
       </c>
@@ -11758,16 +5711,16 @@
         <v>1.6687507000000001E-2</v>
       </c>
       <c r="Q89">
+        <v>-1.2052966E-2</v>
+      </c>
+      <c r="R89">
         <v>3.8999299999999998E-3</v>
-      </c>
-      <c r="R89">
-        <v>-2.6186746837217001E-2</v>
       </c>
       <c r="S89">
         <v>-1.2868558E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19">
       <c r="A90">
         <v>232</v>
       </c>
@@ -11817,16 +5770,16 @@
         <v>1.3598733999999999E-2</v>
       </c>
       <c r="Q90">
+        <v>-1.4526188000000001E-2</v>
+      </c>
+      <c r="R90">
         <v>1.2040354E-2</v>
-      </c>
-      <c r="R90">
-        <v>-2.7115829382948299E-2</v>
       </c>
       <c r="S90">
         <v>-1.3446629E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19">
       <c r="A91">
         <v>231</v>
       </c>
@@ -11876,16 +5829,16 @@
         <v>1.545415E-2</v>
       </c>
       <c r="Q91">
+        <v>-1.6710905000000002E-2</v>
+      </c>
+      <c r="R91">
         <v>2.1269691E-2</v>
-      </c>
-      <c r="R91">
-        <v>-2.77527009615091E-2</v>
       </c>
       <c r="S91">
         <v>-1.403546E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19">
       <c r="A92">
         <v>230</v>
       </c>
@@ -11935,16 +5888,16 @@
         <v>1.3744022999999999E-2</v>
       </c>
       <c r="Q92">
+        <v>-1.9146045E-2</v>
+      </c>
+      <c r="R92">
         <v>2.8217180000000001E-2</v>
-      </c>
-      <c r="R92">
-        <v>-2.5770635856907202E-2</v>
       </c>
       <c r="S92">
         <v>-1.5292821E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19">
       <c r="A93">
         <v>229</v>
       </c>
@@ -11994,16 +5947,16 @@
         <v>1.1179211999999999E-2</v>
       </c>
       <c r="Q93">
+        <v>-1.9441785999999999E-2</v>
+      </c>
+      <c r="R93">
         <v>3.5949518999999999E-2</v>
-      </c>
-      <c r="R93">
-        <v>-2.4083116637283099E-2</v>
       </c>
       <c r="S93">
         <v>-1.6545798E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19">
       <c r="A94">
         <v>228</v>
       </c>
@@ -12053,16 +6006,16 @@
         <v>1.0718735E-2</v>
       </c>
       <c r="Q94">
+        <v>-1.718981E-2</v>
+      </c>
+      <c r="R94">
         <v>4.6111701999999997E-2</v>
-      </c>
-      <c r="R94">
-        <v>-2.2377447274523801E-2</v>
       </c>
       <c r="S94">
         <v>-1.8163156999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19">
       <c r="A95">
         <v>227</v>
       </c>
@@ -12112,16 +6065,16 @@
         <v>1.5252473000000001E-2</v>
       </c>
       <c r="Q95">
+        <v>-1.3953561999999999E-2</v>
+      </c>
+      <c r="R95">
         <v>5.4211885000000001E-2</v>
-      </c>
-      <c r="R95">
-        <v>-2.2215091556417502E-2</v>
       </c>
       <c r="S95">
         <v>-2.0030623000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19">
       <c r="A96">
         <v>226</v>
       </c>
@@ -12171,16 +6124,16 @@
         <v>2.3488743999999999E-2</v>
       </c>
       <c r="Q96">
+        <v>-9.1183299999999991E-3</v>
+      </c>
+      <c r="R96">
         <v>6.1877485000000003E-2</v>
-      </c>
-      <c r="R96">
-        <v>-2.2895750603855101E-2</v>
       </c>
       <c r="S96">
         <v>-2.3263951000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19">
       <c r="A97">
         <v>225</v>
       </c>
@@ -12230,16 +6183,16 @@
         <v>3.0322735999999999E-2</v>
       </c>
       <c r="Q97">
+        <v>-3.274992E-3</v>
+      </c>
+      <c r="R97">
         <v>6.9577298999999995E-2</v>
-      </c>
-      <c r="R97">
-        <v>-2.27509061959341E-2</v>
       </c>
       <c r="S97">
         <v>-2.8363293000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19">
       <c r="A98">
         <v>224</v>
       </c>
@@ -12289,16 +6242,16 @@
         <v>3.5419957000000002E-2</v>
       </c>
       <c r="Q98">
+        <v>3.3716549999999999E-3</v>
+      </c>
+      <c r="R98">
         <v>8.3214906000000005E-2</v>
-      </c>
-      <c r="R98">
-        <v>-2.11238510301094E-2</v>
       </c>
       <c r="S98">
         <v>-3.5084506000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19">
       <c r="A99">
         <v>223</v>
       </c>
@@ -12348,16 +6301,16 @@
         <v>3.8785042999999998E-2</v>
       </c>
       <c r="Q99">
+        <v>8.5799670000000008E-3</v>
+      </c>
+      <c r="R99">
         <v>9.6585779999999996E-2</v>
-      </c>
-      <c r="R99">
-        <v>-1.91877159477222E-2</v>
       </c>
       <c r="S99">
         <v>-4.1066544000000003E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19">
       <c r="A100">
         <v>222</v>
       </c>
@@ -12407,16 +6360,16 @@
         <v>4.3520271999999999E-2</v>
       </c>
       <c r="Q100">
+        <v>1.3433080999999999E-2</v>
+      </c>
+      <c r="R100">
         <v>0.110175052</v>
-      </c>
-      <c r="R100">
-        <v>-1.9501966197315999E-2</v>
       </c>
       <c r="S100">
         <v>-4.8421325000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19">
       <c r="A101">
         <v>221</v>
       </c>
@@ -12466,16 +6419,16 @@
         <v>4.9261039999999999E-2</v>
       </c>
       <c r="Q101">
+        <v>1.7435922E-2</v>
+      </c>
+      <c r="R101">
         <v>0.123540465</v>
-      </c>
-      <c r="R101">
-        <v>-2.02438308578494E-2</v>
       </c>
       <c r="S101">
         <v>-5.5695436000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19">
       <c r="A102">
         <v>220</v>
       </c>
@@ -12525,16 +6478,16 @@
         <v>5.5369373E-2</v>
       </c>
       <c r="Q102">
+        <v>2.2183120000000001E-2</v>
+      </c>
+      <c r="R102">
         <v>0.13334220899999999</v>
-      </c>
-      <c r="R102">
-        <v>-2.0862375285181901E-2</v>
       </c>
       <c r="S102">
         <v>-6.1107437000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19">
       <c r="A103">
         <v>219</v>
       </c>
@@ -12584,16 +6537,16 @@
         <v>6.0407503000000001E-2</v>
       </c>
       <c r="Q103">
+        <v>2.6681377999999999E-2</v>
+      </c>
+      <c r="R103">
         <v>0.14055020500000001</v>
-      </c>
-      <c r="R103">
-        <v>-2.2619624036727501E-2</v>
       </c>
       <c r="S103">
         <v>-6.6744504999999996E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19">
       <c r="A104">
         <v>218</v>
       </c>
@@ -12643,16 +6596,16 @@
         <v>6.7688453999999995E-2</v>
       </c>
       <c r="Q104">
+        <v>3.0025626999999999E-2</v>
+      </c>
+      <c r="R104">
         <v>0.14297470600000001</v>
-      </c>
-      <c r="R104">
-        <v>-2.4838416668673698E-2</v>
       </c>
       <c r="S104">
         <v>-7.1810946E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19">
       <c r="A105">
         <v>217</v>
       </c>
@@ -12702,16 +6655,16 @@
         <v>7.7831042000000003E-2</v>
       </c>
       <c r="Q105">
+        <v>3.2776553999999999E-2</v>
+      </c>
+      <c r="R105">
         <v>0.14193006399999999</v>
-      </c>
-      <c r="R105">
-        <v>-2.9348178910900101E-2</v>
       </c>
       <c r="S105">
         <v>-7.5910140000000001E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19">
       <c r="A106">
         <v>216</v>
       </c>
@@ -12761,16 +6714,16 @@
         <v>9.0350987999999993E-2</v>
       </c>
       <c r="Q106">
+        <v>3.4153595000000002E-2</v>
+      </c>
+      <c r="R106">
         <v>0.13445679999999999</v>
-      </c>
-      <c r="R106">
-        <v>-3.6570705474199397E-2</v>
       </c>
       <c r="S106">
         <v>-7.9059972000000006E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19">
       <c r="A107">
         <v>215</v>
       </c>
@@ -12820,16 +6773,16 @@
         <v>0.10288842400000001</v>
       </c>
       <c r="Q107">
+        <v>3.3492413999999998E-2</v>
+      </c>
+      <c r="R107">
         <v>0.122587512</v>
-      </c>
-      <c r="R107">
-        <v>-4.3576137171069403E-2</v>
       </c>
       <c r="S107">
         <v>-8.1154708000000006E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19">
       <c r="A108">
         <v>214</v>
       </c>
@@ -12879,16 +6832,16 @@
         <v>0.1131664</v>
       </c>
       <c r="Q108">
+        <v>3.3125344000000001E-2</v>
+      </c>
+      <c r="R108">
         <v>0.105333815</v>
-      </c>
-      <c r="R108">
-        <v>-4.9735996488261901E-2</v>
       </c>
       <c r="S108">
         <v>-8.1551489000000005E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19">
       <c r="A109">
         <v>213</v>
       </c>
@@ -12938,16 +6891,16 @@
         <v>0.12422403899999999</v>
       </c>
       <c r="Q109">
+        <v>3.0672475000000001E-2</v>
+      </c>
+      <c r="R109">
         <v>8.5277203999999995E-2</v>
-      </c>
-      <c r="R109">
-        <v>-6.0237692214029998E-2</v>
       </c>
       <c r="S109">
         <v>-8.0407390999999995E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19">
       <c r="A110">
         <v>212</v>
       </c>
@@ -12997,16 +6950,16 @@
         <v>0.13425199900000001</v>
       </c>
       <c r="Q110">
+        <v>2.7284949999999999E-2</v>
+      </c>
+      <c r="R110">
         <v>6.2975838000000006E-2</v>
-      </c>
-      <c r="R110">
-        <v>-7.0267577803644093E-2</v>
       </c>
       <c r="S110">
         <v>-7.6742747E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19">
       <c r="A111">
         <v>211</v>
       </c>
@@ -13056,16 +7009,16 @@
         <v>0.14409160800000001</v>
       </c>
       <c r="Q111">
+        <v>2.5128833E-2</v>
+      </c>
+      <c r="R111">
         <v>4.0622357999999997E-2</v>
-      </c>
-      <c r="R111">
-        <v>-8.1200293323905104E-2</v>
       </c>
       <c r="S111">
         <v>-6.8474424000000006E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19">
       <c r="A112">
         <v>210</v>
       </c>
@@ -13115,16 +7068,16 @@
         <v>0.15225433499999999</v>
       </c>
       <c r="Q112">
+        <v>2.4014226999999999E-2</v>
+      </c>
+      <c r="R112">
         <v>2.4235310999999999E-2</v>
-      </c>
-      <c r="R112">
-        <v>-9.1058873767499104E-2</v>
       </c>
       <c r="S112">
         <v>-5.5677983E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19">
       <c r="A113">
         <v>209</v>
       </c>
@@ -13174,16 +7127,16 @@
         <v>0.158344656</v>
       </c>
       <c r="Q113">
+        <v>2.6053359000000002E-2</v>
+      </c>
+      <c r="R113">
         <v>8.9094650000000001E-3</v>
-      </c>
-      <c r="R113">
-        <v>-9.7749984860508704E-2</v>
       </c>
       <c r="S113">
         <v>-3.6656842000000002E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19">
       <c r="A114">
         <v>208</v>
       </c>
@@ -13233,16 +7186,16 @@
         <v>0.15919040100000001</v>
       </c>
       <c r="Q114">
+        <v>3.2940311E-2</v>
+      </c>
+      <c r="R114">
         <v>5.5983699999999999E-4</v>
-      </c>
-      <c r="R114">
-        <v>-0.10228456440964601</v>
       </c>
       <c r="S114">
         <v>-1.4621366E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19">
       <c r="A115">
         <v>207</v>
       </c>
@@ -13292,16 +7245,16 @@
         <v>0.157467465</v>
       </c>
       <c r="Q115">
+        <v>4.1696244E-2</v>
+      </c>
+      <c r="R115">
         <v>2.5529390000000002E-3</v>
-      </c>
-      <c r="R115">
-        <v>-0.104431478190461</v>
       </c>
       <c r="S115">
         <v>5.2435260000000001E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19">
       <c r="A116">
         <v>206</v>
       </c>
@@ -13351,16 +7304,16 @@
         <v>0.15105518400000001</v>
       </c>
       <c r="Q116">
+        <v>5.0890393999999999E-2</v>
+      </c>
+      <c r="R116">
         <v>8.7727989999999995E-3</v>
-      </c>
-      <c r="R116">
-        <v>-9.9832461942938294E-2</v>
       </c>
       <c r="S116">
         <v>1.9332301E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19">
       <c r="A117">
         <v>205</v>
       </c>
@@ -13410,16 +7363,16 @@
         <v>0.13825796700000001</v>
       </c>
       <c r="Q117">
+        <v>6.2377378999999997E-2</v>
+      </c>
+      <c r="R117">
         <v>1.8924750000000001E-2</v>
-      </c>
-      <c r="R117">
-        <v>-9.3407145586557799E-2</v>
       </c>
       <c r="S117">
         <v>3.7309599999999998E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19">
       <c r="A118">
         <v>204</v>
       </c>
@@ -13469,16 +7422,16 @@
         <v>0.12379440799999999</v>
       </c>
       <c r="Q118">
+        <v>7.2079915999999994E-2</v>
+      </c>
+      <c r="R118">
         <v>3.1644686999999998E-2</v>
-      </c>
-      <c r="R118">
-        <v>-8.1727633548370704E-2</v>
       </c>
       <c r="S118">
         <v>5.4284764999999999E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19">
       <c r="A119">
         <v>203</v>
       </c>
@@ -13528,16 +7481,16 @@
         <v>0.108004356</v>
       </c>
       <c r="Q119">
+        <v>8.0239716000000003E-2</v>
+      </c>
+      <c r="R119">
         <v>4.9687230999999998E-2</v>
-      </c>
-      <c r="R119">
-        <v>-6.6534894487638094E-2</v>
       </c>
       <c r="S119">
         <v>6.9127153999999996E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19">
       <c r="A120">
         <v>202</v>
       </c>
@@ -13587,16 +7540,16 @@
         <v>8.4755709999999998E-2</v>
       </c>
       <c r="Q120">
+        <v>8.1538243999999996E-2</v>
+      </c>
+      <c r="R120">
         <v>6.6414804999999993E-2</v>
-      </c>
-      <c r="R120">
-        <v>-4.7511834104049903E-2</v>
       </c>
       <c r="S120">
         <v>8.8620308999999994E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19">
       <c r="A121">
         <v>201</v>
       </c>
@@ -13646,16 +7599,16 @@
         <v>5.9076191E-2</v>
       </c>
       <c r="Q121">
+        <v>7.7519647999999997E-2</v>
+      </c>
+      <c r="R121">
         <v>8.1463444999999995E-2</v>
-      </c>
-      <c r="R121">
-        <v>-2.47415894657145E-2</v>
       </c>
       <c r="S121">
         <v>0.116855375</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19">
       <c r="A122">
         <v>200</v>
       </c>
@@ -13705,16 +7658,16 @@
         <v>3.5099096000000003E-2</v>
       </c>
       <c r="Q122">
+        <v>6.5039107999999998E-2</v>
+      </c>
+      <c r="R122">
         <v>9.6466470999999998E-2</v>
-      </c>
-      <c r="R122">
-        <v>1.12419564599655E-3</v>
       </c>
       <c r="S122">
         <v>0.134466804</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19">
       <c r="A123">
         <v>199</v>
       </c>
@@ -13764,16 +7717,16 @@
         <v>1.3964597E-2</v>
       </c>
       <c r="Q123">
+        <v>4.9044327999999998E-2</v>
+      </c>
+      <c r="R123">
         <v>0.110854651</v>
-      </c>
-      <c r="R123">
-        <v>2.6475375012142699E-2</v>
       </c>
       <c r="S123">
         <v>0.15485141899999999</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19">
       <c r="A124">
         <v>198</v>
       </c>
@@ -13823,16 +7776,16 @@
         <v>1.1145759999999999E-3</v>
       </c>
       <c r="Q124">
+        <v>2.5620349000000001E-2</v>
+      </c>
+      <c r="R124">
         <v>0.122520412</v>
-      </c>
-      <c r="R124">
-        <v>5.2473970955103297E-2</v>
       </c>
       <c r="S124">
         <v>0.171856338</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19">
       <c r="A125">
         <v>197</v>
       </c>
@@ -13882,16 +7835,16 @@
         <v>-6.4553559999999998E-3</v>
       </c>
       <c r="Q125">
+        <v>4.3498549999999997E-3</v>
+      </c>
+      <c r="R125">
         <v>0.13654095199999999</v>
-      </c>
-      <c r="R125">
-        <v>7.7861553271008105E-2</v>
       </c>
       <c r="S125">
         <v>0.19215064900000001</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19">
       <c r="A126">
         <v>196</v>
       </c>
@@ -13941,16 +7894,16 @@
         <v>-7.4528090000000003E-3</v>
       </c>
       <c r="Q126">
+        <v>-1.1429620999999999E-2</v>
+      </c>
+      <c r="R126">
         <v>0.14904392</v>
-      </c>
-      <c r="R126">
-        <v>0.105856444593507</v>
       </c>
       <c r="S126">
         <v>0.21062313699999999</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19">
       <c r="A127">
         <v>195</v>
       </c>
@@ -14000,16 +7953,16 @@
         <v>-6.9644699999999999E-4</v>
       </c>
       <c r="Q127">
+        <v>-1.3942838000000001E-2</v>
+      </c>
+      <c r="R127">
         <v>0.155824771</v>
-      </c>
-      <c r="R127">
-        <v>0.13371485936656</v>
       </c>
       <c r="S127">
         <v>0.23020179700000001</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19">
       <c r="A128">
         <v>194</v>
       </c>
@@ -14059,16 +8012,16 @@
         <v>1.6611811000000001E-2</v>
       </c>
       <c r="Q128">
+        <v>-7.7225299999999998E-4</v>
+      </c>
+      <c r="R128">
         <v>0.16502972699999999</v>
-      </c>
-      <c r="R128">
-        <v>0.162812690466385</v>
       </c>
       <c r="S128">
         <v>0.246796079</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19">
       <c r="A129">
         <v>193</v>
       </c>
@@ -14118,16 +8071,16 @@
         <v>4.6372005000000001E-2</v>
       </c>
       <c r="Q129">
+        <v>2.8335991000000001E-2</v>
+      </c>
+      <c r="R129">
         <v>0.167603485</v>
-      </c>
-      <c r="R129">
-        <v>0.19236028418155199</v>
       </c>
       <c r="S129">
         <v>0.26031352200000002</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19">
       <c r="A130">
         <v>192</v>
       </c>
@@ -14177,16 +8130,16 @@
         <v>7.7490890000000007E-2</v>
       </c>
       <c r="Q130">
+        <v>6.7219461999999994E-2</v>
+      </c>
+      <c r="R130">
         <v>0.16370201000000001</v>
-      </c>
-      <c r="R130">
-        <v>0.223468292050513</v>
       </c>
       <c r="S130">
         <v>0.26675639000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19">
       <c r="A131">
         <v>191</v>
       </c>
@@ -14236,16 +8189,16 @@
         <v>0.10645892999999999</v>
       </c>
       <c r="Q131">
+        <v>0.117792917</v>
+      </c>
+      <c r="R131">
         <v>0.15285469600000001</v>
-      </c>
-      <c r="R131">
-        <v>0.25347555239021402</v>
       </c>
       <c r="S131">
         <v>0.26719009300000002</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19">
       <c r="A132">
         <v>190</v>
       </c>
@@ -14295,16 +8248,16 @@
         <v>0.1270511</v>
       </c>
       <c r="Q132">
+        <v>0.169950247</v>
+      </c>
+      <c r="R132">
         <v>0.13585070299999999</v>
-      </c>
-      <c r="R132">
-        <v>0.27919099856760099</v>
       </c>
       <c r="S132">
         <v>0.263589199</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19">
       <c r="A133">
         <v>189</v>
       </c>
@@ -14354,16 +8307,16 @@
         <v>0.13619176099999999</v>
       </c>
       <c r="Q133">
+        <v>0.213789064</v>
+      </c>
+      <c r="R133">
         <v>0.11398103800000001</v>
-      </c>
-      <c r="R133">
-        <v>0.30224150450395199</v>
       </c>
       <c r="S133">
         <v>0.25679396999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19">
       <c r="A134">
         <v>188</v>
       </c>
@@ -14413,16 +8366,16 @@
         <v>0.13652397999999999</v>
       </c>
       <c r="Q134">
+        <v>0.242128913</v>
+      </c>
+      <c r="R134">
         <v>9.0986968000000001E-2</v>
-      </c>
-      <c r="R134">
-        <v>0.31486056167347098</v>
       </c>
       <c r="S134">
         <v>0.24519437999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19">
       <c r="A135">
         <v>187</v>
       </c>
@@ -14472,16 +8425,16 @@
         <v>0.12775681999999999</v>
       </c>
       <c r="Q135">
+        <v>0.24655117900000001</v>
+      </c>
+      <c r="R135">
         <v>6.6459639000000001E-2</v>
-      </c>
-      <c r="R135">
-        <v>0.31673534965572298</v>
       </c>
       <c r="S135">
         <v>0.22634396400000001</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19">
       <c r="A136">
         <v>186</v>
       </c>
@@ -14531,16 +8484,16 @@
         <v>0.107709966</v>
       </c>
       <c r="Q136">
+        <v>0.22895913600000001</v>
+      </c>
+      <c r="R136">
         <v>5.1234771999999998E-2</v>
-      </c>
-      <c r="R136">
-        <v>0.30263659705187201</v>
       </c>
       <c r="S136">
         <v>0.203925984</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19">
       <c r="A137">
         <v>185</v>
       </c>
@@ -14590,16 +8543,16 @@
         <v>8.5189395000000001E-2</v>
       </c>
       <c r="Q137">
+        <v>0.193860752</v>
+      </c>
+      <c r="R137">
         <v>4.0395963999999999E-2</v>
-      </c>
-      <c r="R137">
-        <v>0.27181838335591302</v>
       </c>
       <c r="S137">
         <v>0.170245547</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19">
       <c r="A138">
         <v>184</v>
       </c>
@@ -14649,16 +8602,16 @@
         <v>5.9743242000000002E-2</v>
       </c>
       <c r="Q138">
+        <v>0.14730190700000001</v>
+      </c>
+      <c r="R138">
         <v>4.5700044000000002E-2</v>
-      </c>
-      <c r="R138">
-        <v>0.22163280144933001</v>
       </c>
       <c r="S138">
         <v>0.14603162</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19">
       <c r="A139">
         <v>183</v>
       </c>
@@ -14708,16 +8661,16 @@
         <v>3.8752622E-2</v>
       </c>
       <c r="Q139">
+        <v>9.5727568999999998E-2</v>
+      </c>
+      <c r="R139">
         <v>6.1161203999999997E-2</v>
-      </c>
-      <c r="R139">
-        <v>0.16277781163615501</v>
       </c>
       <c r="S139">
         <v>0.12917347500000001</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19">
       <c r="A140">
         <v>182</v>
       </c>
@@ -14767,16 +8720,16 @@
         <v>2.2180858000000001E-2</v>
       </c>
       <c r="Q140">
+        <v>4.4603043000000002E-2</v>
+      </c>
+      <c r="R140">
         <v>8.4389892999999994E-2</v>
-      </c>
-      <c r="R140">
-        <v>9.5484436002522405E-2</v>
       </c>
       <c r="S140">
         <v>6.7822610000000005E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19">
       <c r="A141">
         <v>181</v>
       </c>
@@ -14826,16 +8779,16 @@
         <v>9.6587400000000007E-3</v>
       </c>
       <c r="Q141">
+        <v>-5.3211359999999997E-3</v>
+      </c>
+      <c r="R141">
         <v>0.114381568</v>
-      </c>
-      <c r="R141">
-        <v>3.1972144659880797E-2</v>
       </c>
       <c r="S141">
         <v>3.7263834000000003E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19">
       <c r="A142">
         <v>180</v>
       </c>
@@ -14885,16 +8838,16 @@
         <v>9.1202600000000003E-4</v>
       </c>
       <c r="Q142">
+        <v>-4.6523882000000003E-2</v>
+      </c>
+      <c r="R142">
         <v>0.140866925</v>
-      </c>
-      <c r="R142">
-        <v>-2.3701707283596701E-2</v>
       </c>
       <c r="S142">
         <v>1.6407614000000001E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19">
       <c r="A143">
         <v>179</v>
       </c>
@@ -14944,16 +8897,16 @@
         <v>-4.8888059999999999E-3</v>
       </c>
       <c r="Q143">
+        <v>-8.2859916000000006E-2</v>
+      </c>
+      <c r="R143">
         <v>0.16311848400000001</v>
-      </c>
-      <c r="R143">
-        <v>-6.2847754665783795E-2</v>
       </c>
       <c r="S143">
         <v>-9.5242160000000003E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19">
       <c r="A144">
         <v>178</v>
       </c>
@@ -15003,16 +8956,16 @@
         <v>-1.0203099E-2</v>
       </c>
       <c r="Q144">
+        <v>-0.11245112</v>
+      </c>
+      <c r="R144">
         <v>0.175805341</v>
-      </c>
-      <c r="R144">
-        <v>-8.5793191918450695E-2</v>
       </c>
       <c r="S144">
         <v>-2.4109592999999999E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19">
       <c r="A145">
         <v>177</v>
       </c>
@@ -15062,16 +9015,16 @@
         <v>-1.7864891000000001E-2</v>
       </c>
       <c r="Q145">
+        <v>-0.130866653</v>
+      </c>
+      <c r="R145">
         <v>0.17293240900000001</v>
-      </c>
-      <c r="R145">
-        <v>-9.0724453790459694E-2</v>
       </c>
       <c r="S145">
         <v>-3.4559904000000002E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19">
       <c r="A146">
         <v>176</v>
       </c>
@@ -15121,16 +9074,16 @@
         <v>-2.5516266999999999E-2</v>
       </c>
       <c r="Q146">
+        <v>-0.13919029899999999</v>
+      </c>
+      <c r="R146">
         <v>0.148579828</v>
-      </c>
-      <c r="R146">
-        <v>-8.4183686381827494E-2</v>
       </c>
       <c r="S146">
         <v>-4.1112216E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19">
       <c r="A147">
         <v>175</v>
       </c>
@@ -15180,10 +9133,10 @@
         <v>-3.4176087000000001E-2</v>
       </c>
       <c r="Q147">
+        <v>-0.143614889</v>
+      </c>
+      <c r="R147">
         <v>0.101072918</v>
-      </c>
-      <c r="R147">
-        <v>-7.8797497468873406E-2</v>
       </c>
       <c r="S147">
         <v>-4.5573780000000001E-2</v>
@@ -15198,8 +9151,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000EED487577094149BA9333400BFC4041" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e6025b77c969027991e2360f70240149">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e6c990de-d349-4e6b-93bf-db88ca71061a" xmlns:ns3="b455622e-9c6b-49e1-9942-78506eba3624" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="591c6b40685b70dff520200c2a3b5e4f" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000EED487577094149BA9333400BFC4041" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07c5b15ced29969648857dc4b7dd40cd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e6c990de-d349-4e6b-93bf-db88ca71061a" xmlns:ns3="b455622e-9c6b-49e1-9942-78506eba3624" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="382c7e20b0d8081a5207132cccf176ee" ns2:_="" ns3:_="">
     <xsd:import namespace="e6c990de-d349-4e6b-93bf-db88ca71061a"/>
     <xsd:import namespace="b455622e-9c6b-49e1-9942-78506eba3624"/>
     <xsd:element name="properties">
@@ -15230,7 +9183,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e6c990de-d349-4e6b-93bf-db88ca71061a" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -15249,7 +9202,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -15281,7 +9234,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fb0b088-da3c-47ed-872c-fc1360427ae0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fb0b088-da3c-47ed-872c-fc1360427ae0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -15330,8 +9283,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -15421,15 +9374,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b455622e-9c6b-49e1-9942-78506eba3624">
@@ -15440,14 +9384,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E293C23-FB23-429F-B297-B13DC6D01A9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6584AFA6-A5D8-488E-876A-B5E0EC131082}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25349DA-7D22-4E54-AEC4-B6FC3060CE50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20AA7A26-312F-458F-A9AB-40C035227C94}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20AA7A26-312F-458F-A9AB-40C035227C94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25349DA-7D22-4E54-AEC4-B6FC3060CE50}"/>
 </file>